--- a/data/datasets/separable/separable_train.xlsx
+++ b/data/datasets/separable/separable_train.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3ee4b32aa2f74fcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5461c5acd37b4bce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -617,15 +617,80 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
+        <x:v>y^{\prime}=- \frac{2 \operatorname{acos}{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{ctan}{\left(2 x \right)}}</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>y=\arccos(2 \cdot x) \cdot \frac{1}{\ctg(2 \cdot x)}-\ctg(x) \cdot \arccos(2 \cdot x)+C</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>[REASONING]
+**Step 1 – Rewrite the given equation**
+\[
+y'=- \frac{2\,\operatorname{acos}(2x)\,
+\left.\dfrac{d}{d\xi_{1}}\operatorname{ctan}(\xi_{1})\right|_{\xi_{1}=2x}}
+{\operatorname{ctan}^{2}(2x)}
+-\frac{2}{\sqrt{1-4x^{2}}\;\operatorname{ctan}(2x)} .
+\]
+Here  
+* \(\operatorname{acos}\) denotes \(\arccos\),  
+* \(\operatorname{ctan}\) denotes \(\cot\), and  
+* \(\displaystyle\frac{d}{d\xi}\cot(\xi)=-\csc^{2}(\xi)\).
+Hence  
+\[
+\left.\frac{d}{d\xi_{1}}\operatorname{ctan}(\xi_{1})\right|_{\xi_{1}=2x}
+= -\csc^{2}(2x).
+\]
+**Step 2 – Substitute the derivative**
+\[
+\begin{aligned}
+y'&amp;=-\frac{2\,\operatorname{acos}(2x)\,[-\csc^{2}(2x)]}{\cot^{2}(2x)}
+-\frac{2}{\sqrt{1-4x^{2}}\;\cot(2x)}\\[4pt]
+&amp;= \frac{2\,\operatorname{acos}(2x)\,\csc^{2}(2x)}{\cot^{2}(2x)}
+-\frac{2}{\sqrt{1-4x^{2}}\;\cot(2x)} .
+\end{aligned}
+\]
+**Step 3 – Simplify the trigonometric ratio**
+Using \(\cot\theta=\dfrac{\cos\theta}{\sin\theta}\) and \(\csc\theta=\dfrac{1}{\sin\theta}\),
+\[
+\frac{\csc^{2}(2x)}{\cot^{2}(2x)}
+=\frac{1/\sin^{2}(2x)}{\cos^{2}(2x)/\sin^{2}(2x)}
+=\frac{1}{\cos^{2}(2x)}=\sec^{2}(2x).
+\]
+Also \(\displaystyle\frac{1}{\cot(2x)}=\tan(2x)\).
+Thus
+\[
+y' = 2\,\operatorname{acos}(2x)\,\sec^{2}(2x)
+      -\frac{2\,\tan(2x)}{\sqrt{1-4x^{2}}}.
+\]
+**Step 4 – Recognise a product derivative**
+Recall  
+\[
+\frac{d}{dx}\bigl[\operatorname{acos}(2x)\bigr]=-\frac{2}{\sqrt{1-4x^{2}}},\qquad
+\frac{d}{dx}\bigl[\tan(2x)\bigr]=2\sec^{2}(2x).
+\]
+Hence, by the product rule,
+\[
+\frac{d}{dx}\bigl[\operatorname{acos}(2x)\,\tan(2x)\bigr]
+= \bigl[-\frac{2}{\sqrt{1-4x^{2}}}\bigr]\tan(2x)
+  +
+[FINAL ANSWER]
+\boxed{NOT_FOUND}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
         <x:v>y^{\prime}=\left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{ctan}{\left(x \right)} - \sin{\left(x \right)} \operatorname{acot}{\left(x \right)} + \tan{\left(x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} - \frac{\cos{\left(x \right)}}{x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B5" t="str">
+      <x:c r="B6" t="str">
         <x:v>y=\tg(x) \cdot \ctg(x)+\arcctg(x) \cdot \cos(x)+C</x:v>
       </x:c>
-      <x:c r="C5" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
+      <x:c r="C6" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -700,17 +765,17 @@
 \boxed{\,y(x)=\cos x\;\operatorname{arccot}</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str">
+    <x:row r="7">
+      <x:c r="A7" t="str">
         <x:v>y^{\prime}=\frac{2}{\left(4 x^{2} + 1\right) \operatorname{acos}{\left(x \right)}} + \frac{2}{\left(4 x^{2} + 1\right) \log{\left(2 x \right)}} + \frac{\operatorname{atan}{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{acos}^{2}{\left(x \right)}} + \frac{\operatorname{acot}{\left(2 x \right)}}{x \log{\left(2 x \right)}^{2}}</x:v>
       </x:c>
-      <x:c r="B6" t="str">
+      <x:c r="B7" t="str">
         <x:v>y=\arctg(2 \cdot x) \cdot \frac{1}{\arccos(x)}-\arcctg(2 \cdot x) \cdot \frac{1}{\ln(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C6" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
+      <x:c r="C7" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
         <x:v>[REASONING]
 The right–hand side can be grouped into two pairs of terms.
 ---
@@ -787,17 +852,17 @@
 \boxed{\,y(x)=\dfrac{\arctan (2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
+    <x:row r="8">
+      <x:c r="A8" t="str">
         <x:v>y^{\prime}=- \frac{1}{\sqrt{1 - x^{2}} \operatorname{acos}{\left(2 x \right)}} + \frac{2 \operatorname{acos}{\left(x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{acos}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B7" t="str">
+      <x:c r="B8" t="str">
         <x:v>y=\arccos(x) \cdot \frac{1}{\arccos(2 \cdot x)}-\arcsin(x) \cdot e^{x}+C</x:v>
       </x:c>
-      <x:c r="C7" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
+      <x:c r="C8" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 Let  
@@ -845,17 +910,17 @@
 \boxed{\,y = \frac{\arccos x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="str">
+    <x:row r="9">
+      <x:c r="A9" t="str">
         <x:v>y^{\prime}=- \frac{2 \operatorname{acot}{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{atan}^{2}{\left(2 x \right)}} - \frac{1}{\left(x^{2} + 1\right) \operatorname{atan}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B8" t="str">
+      <x:c r="B9" t="str">
         <x:v>y=\arcctg(x) \cdot \frac{1}{\arctg(2 \cdot x)}+\arctg(2 \cdot x) \cdot \arcctg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C8" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D8" t="str">
+      <x:c r="C9" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 \[
@@ -917,34 +982,81 @@
 \boxed{\,y(x)=\dfrac{\operatorname{acot}</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str">
-        <x:v>y^{\prime}=- \frac{\tan^{2}{\left(x \right)} + 1}{\cos{\left(2 x \right)}} - \frac{2 \sin{\left(2 x \right)} \tan{\left(x \right)}}{\cos^{2}{\left(2 x \right)}} - \frac{2 \sin{\left(2 x \right)}}{\operatorname{ctan}{\left(2 x \right)}} - \frac{2 \cos{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}}</x:v>
-      </x:c>
-      <x:c r="B9" t="str">
-        <x:v>y=\cos(2 \cdot x) \cdot \frac{1}{\ctg(2 \cdot x)}-\tg(x) \cdot \frac{1}{\cos(2 \cdot x)}+C</x:v>
-      </x:c>
-      <x:c r="C9" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
-        <x:v>[REASONING]
-ERROR: Empty response
-[FINAL ANSWER]
-\boxed{NOT_FOUND}</x:v>
-      </x:c>
-    </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
+        <x:v>y^{\prime}=- \frac{\tan^{2}{\left(x \right)} + 1}{\cos{\left(2 x \right)}} - \frac{2 \sin{\left(2 x \right)} \tan{\left(x \right)}}{\cos^{2}{\left(2 x \right)}} - \frac{2 \sin{\left(2 x \right)}}{\operatorname{ctan}{\left(2 x \right)}} - \frac{2 \cos{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}}</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>y=\cos(2 \cdot x) \cdot \frac{1}{\ctg(2 \cdot x)}-\tg(x) \cdot \frac{1}{\cos(2 \cdot x)}+C</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>[REASONING]
+ERROR: Empty response
+[FINAL ANSWER]
+\boxed{NOT_FOUND}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>y^{\prime}=- \frac{\log{\left(2 x \right)} \cos{\left(x \right)}}{\sin^{2}{\left(x \right)}} + \frac{1}{x \sin{\left(x \right)}}</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>y=\ln(2 \cdot x) \cdot \frac{1}{\sin(x)}-e^{2 \cdot x} \cdot \arctg(x)+C</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>[REASONING]
+[REASONING]
+The differential equation is  
+\[
+y'=- \frac{\log (2x)\,\cos x}{\sin ^2 x}+ \frac{1}{x\sin x}.
+\]
+Because the right‑hand side depends only on \(x\), we can look for a function \(F(x)\) whose derivative equals the right‑hand side.  
+Consider  
+\[
+F(x)=\frac{\log (2x)}{\sin x}.
+\]
+Compute its derivative using the quotient rule:
+\[
+\begin{aligned}
+F'(x) &amp;=\frac{(\log (2x))'}{\sin x}-\frac{\log (2x)\,(\sin x)'}{\sin ^2 x}  \\
+      &amp;=\frac{\dfrac{1}{x}}{\sin x}-\frac{\log (2x)\,\cos x}{\sin ^2 x} \\
+      &amp;=\frac{1}{x\sin x}-\frac{\log (2x)\cos x}{\sin ^2 x}.
+\end{aligned}
+\]
+The expression obtained for \(F'(x)\) is exactly the right‑hand side of the given ODE. Hence  
+\[
+y' = F'(x).
+\]
+Integrating both sides with respect to \(x\),
+\[
+y = F(x) + C = \frac{\log (2x)}{\sin x}+C,
+\]
+where \(C\) is an arbitrary constant.
+[FINAL ANSWER]
+\[
+\boxed{\,y(x)=\frac{\log (2x)}{\sin x}+C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y(x)=\frac{\log (2x)}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
         <x:v>y^{\prime}=- \frac{\operatorname{asin}{\left(x \right)}}{\left(x^{2} + 1\right) \operatorname{atan}^{2}{\left(x \right)}} + \frac{1}{\sqrt{1 - x^{2}} \operatorname{atan}{\left(x \right)}} + \frac{2}{x \left(4 x^{2} + 1\right)} - \frac{\operatorname{atan}{\left(2 x \right)}}{x^{2}}</x:v>
       </x:c>
-      <x:c r="B10" t="str">
+      <x:c r="B12" t="str">
         <x:v>y=\arctg(2 \cdot x) \cdot \frac{1}{x}+\arcsin(x) \cdot \frac{1}{\arctg(x)}+C</x:v>
       </x:c>
-      <x:c r="C10" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D10" t="str">
+      <x:c r="C12" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -1011,17 +1123,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="str">
+    <x:row r="13">
+      <x:c r="A13" t="str">
         <x:v>y^{\prime}=- \frac{2 \sin{\left(2 x \right)} \operatorname{atan}{\left(x \right)}}{\cos^{2}{\left(2 x \right)}} - \frac{2 \operatorname{acot}{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - \frac{1}{\left(x^{2} + 1\right) \cos{\left(2 x \right)}} - \frac{1}{\left(x^{2} + 1\right) \operatorname{ctan}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B11" t="str">
+      <x:c r="B13" t="str">
         <x:v>y=\arcctg(x) \cdot \frac{1}{\ctg(2 \cdot x)}-\arctg(x) \cdot \frac{1}{\cos(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C11" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
+      <x:c r="C13" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
         <x:v>[REASONING]
 **Step 1 – Rewrite the right‑hand side**
 \[
@@ -1065,17 +1177,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="str">
+    <x:row r="14">
+      <x:c r="A14" t="str">
         <x:v>y^{\prime}=\frac{2 \cos{\left(2 x \right)}}{\log{\left(2 x \right)}} - \frac{\sin{\left(2 x \right)}}{x \log{\left(2 x \right)}^{2}}</x:v>
       </x:c>
-      <x:c r="B12" t="str">
+      <x:c r="B14" t="str">
         <x:v>y=\sin(2 \cdot x) \cdot \frac{1}{\ln(2 \cdot x)}-e^{2 \cdot x} \cdot \arccos(x)+C</x:v>
       </x:c>
-      <x:c r="C12" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D12" t="str">
+      <x:c r="C14" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 The differential equation is  
@@ -1127,17 +1239,17 @@
 \boxed{\,y(x)=\frac{\sin (2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="str">
+    <x:row r="15">
+      <x:c r="A15" t="str">
         <x:v>y^{\prime}=\frac{e^{x} \left(- 2 \tan^{2}{\left(2 x \right)} - 2\right)}{\tan^{2}{\left(2 x \right)}} + \frac{e^{x} \log{\left(e \right)}}{\tan{\left(2 x \right)}} - \frac{\operatorname{acos}{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{asin}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B13" t="str">
+      <x:c r="B15" t="str">
         <x:v>y=e^{x} \cdot \frac{1}{\tg(2 \cdot x)}+\arccos(2 \cdot x) \cdot \frac{1}{\arcsin(x)}+C</x:v>
       </x:c>
-      <x:c r="C13" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D13" t="str">
+      <x:c r="C15" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The given differential equation is  
@@ -1159,17 +1271,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="str">
+    <x:row r="16">
+      <x:c r="A16" t="str">
         <x:v>y^{\prime}=- \frac{2 x^{2} \cos{\left(2 x \right)}}{\sin^{2}{\left(2 x \right)}} + \frac{x^{2}}{x^{2} + 1} + 2 x \operatorname{atan}{\left(x \right)} + \frac{2 x}{\sin{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B14" t="str">
+      <x:c r="B16" t="str">
         <x:v>y=\arctg(x) \cdot x^{2}+x^{2} \cdot \frac{1}{\sin(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C14" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D14" t="str">
+      <x:c r="C16" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -1231,17 +1343,17 @@
 \boxed{\,y = \frac{x^{2}</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="str">
+    <x:row r="17">
+      <x:c r="A17" t="str">
         <x:v>y^{\prime}=2 e^{2 x} \log{\left(e \right)} \log{\left(x \right)} + \frac{e^{2 x}}{x} - \frac{2 x^{2} \cos{\left(2 x \right)}}{\sin^{2}{\left(2 x \right)}} + \frac{2 x}{\sin{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B15" t="str">
+      <x:c r="B17" t="str">
         <x:v>y=\ln(x) \cdot e^{2 \cdot x}+x^{2} \cdot \frac{1}{\sin(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C15" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D15" t="str">
+      <x:c r="C17" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -1303,17 +1415,17 @@
 \boxed{\,y = e^{2x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" t="str">
+    <x:row r="18">
+      <x:c r="A18" t="str">
         <x:v>y^{\prime}=- e^{x} \log{\left(e \right)} \operatorname{acot}{\left(x \right)} + \frac{e^{x}}{x^{2} + 1} + \cos{\left(x \right)} \operatorname{acos}{\left(x \right)} - \frac{\sin{\left(x \right)}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
-      <x:c r="B16" t="str">
+      <x:c r="B18" t="str">
         <x:v>y=\sin(x) \cdot \arccos(x)-e^{x} \cdot \arcctg(x)+C</x:v>
       </x:c>
-      <x:c r="C16" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D16" t="str">
+      <x:c r="C18" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -1387,17 +1499,17 @@
 \boxed{\,y(x)=\sin (x)\,\operatorname{acos}</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="str">
+    <x:row r="19">
+      <x:c r="A19" t="str">
         <x:v>y^{\prime}=\frac{2 e^{2 x} \log{\left(e \right)}}{\operatorname{asin}{\left(2 x \right)}} - \frac{2 e^{2 x}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B17" t="str">
+      <x:c r="B19" t="str">
         <x:v>y=e^{2 \cdot x} \cdot \frac{1}{\arcsin(2 \cdot x)}+\ctg(x) \cdot \arctg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C17" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D17" t="str">
+      <x:c r="C19" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -1453,17 +1565,17 @@
 \boxed{\,y(x)=\frac{e^{2x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18" t="str">
+    <x:row r="20">
+      <x:c r="A20" t="str">
         <x:v>y^{\prime}=\cos{\left(x \right)} \operatorname{acot}{\left(x \right)} - \frac{\sin{\left(x \right)}}{x^{2} + 1} - \frac{\log{\left(2 x \right)}}{\sqrt{1 - x^{2}}} + \frac{\operatorname{acos}{\left(x \right)}}{x}</x:v>
       </x:c>
-      <x:c r="B18" t="str">
+      <x:c r="B20" t="str">
         <x:v>y=\arcctg(x) \cdot \sin(x)+\ln(2 \cdot x) \cdot \arccos(x)+C</x:v>
       </x:c>
-      <x:c r="C18" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D18" t="str">
+      <x:c r="C20" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
         <x:v>[REASONING]
 **Solution**
 \[
@@ -1532,17 +1644,17 @@
 \boxed{\,y = \sin x\,\operatorname{acot}</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="str">
+    <x:row r="21">
+      <x:c r="A21" t="str">
         <x:v>y^{\prime}=- e^{- x} \log{\left(e \right)} \operatorname{atan}{\left(x \right)} + \frac{e^{- x}}{x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B19" t="str">
+      <x:c r="B21" t="str">
         <x:v>y=\arctg(x) \cdot \frac{1}{e^{x}}+\arctg(x) \cdot \arctg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C19" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D19" t="str">
+      <x:c r="C21" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -1578,17 +1690,17 @@
 \boxed{\,y(x)=e^{-x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="20">
-      <x:c r="A20" t="str">
+    <x:row r="22">
+      <x:c r="A22" t="str">
         <x:v>y^{\prime}=- \frac{2 \sin{\left(2 x \right)}}{\operatorname{acos}{\left(2 x \right)}} + \frac{2 \cos{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{acos}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B20" t="str">
+      <x:c r="B22" t="str">
         <x:v>y=\cos(2 \cdot x) \cdot \frac{1}{\arccos(2 \cdot x)}+\arccos(2 \cdot x) \cdot x^{3}+C</x:v>
       </x:c>
-      <x:c r="C20" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D20" t="str">
+      <x:c r="C22" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -1638,17 +1750,17 @@
 \boxed{\,y(x)=\frac{\cos (2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="str">
+    <x:row r="23">
+      <x:c r="A23" t="str">
         <x:v>y^{\prime}=\operatorname{acos}{\left(2 x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} + \frac{2 \operatorname{asin}{\left(2 x \right)}}{4 x^{2} + 1} - \frac{2 \operatorname{ctan}{\left(x \right)}}{\sqrt{1 - 4 x^{2}}} - \frac{2 \operatorname{acot}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B21" t="str">
+      <x:c r="B23" t="str">
         <x:v>y=\ctg(x) \cdot \arccos(2 \cdot x)-\arcsin(2 \cdot x) \cdot \arcctg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C21" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D21" t="str">
+      <x:c r="C23" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
         <x:v>[REASONING]
 \[
 y'=\operatorname{acos}(2x)\,\frac{d}{dx}\!\bigl(\cot x\bigr)
@@ -1695,17 +1807,87 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="str">
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>y^{\prime}=\frac{2 \cos{\left(2 x \right)}}{\operatorname{asin}{\left(2 x \right)}} - \frac{2 \sin{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}}</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>y=\sin(2 \cdot x) \cdot \frac{1}{\arcsin(2 \cdot x)}-\tg(x) \cdot \ctg(x)+C</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>[REASONING]
+**Solution**
+\[
+y'=\frac{2\cos (2x)}{\arcsin (2x)}-\frac{2\sin (2x)}{\sqrt{1-4x^{2}}\;(\arcsin (2x))^{2}}
+\]
+The right–hand side suggests the derivative of a quotient that contains \(\sin(2x)\) in the numerator and \(\arcsin(2x)\) in the denominator.  
+Consider  
+\[
+F(x)=\frac{2\sin (2x)}{\arcsin (2x)} .
+\]
+---
+### 1. Differentiate \(F(x)\)
+Let  
+\[
+u(x)=2\sin (2x),\qquad v(x)=\arcsin (2x).
+\]
+Then  
+\[
+u'(x)=2\cdot 2\cos (2x)=4\cos (2x),\qquad 
+v'(x)=\frac{2}{\sqrt{1-(2x)^{2}}}= \frac{2}{\sqrt{1-4x^{2}}}.
+\]
+Using the quotient rule,
+\[
+\begin{aligned}
+F'(x)&amp;=\frac{u'v-u v'}{v^{2}}\\[2mm]
+&amp;=\frac{4\cos (2x)\,\arcsin (2x)-2\sin (2x)\,\dfrac{2}{\sqrt{1-4x^{2}}}}
+      {(\arcsin (2x))^{2}}\\[2mm]
+&amp;= \frac{4\cos (2x)}{\arcsin (2x)}-
+    \frac{4\sin (2x)}{\sqrt{1-4x^{2}}\;(\arcsin (2x))^{2}} .
+\end{aligned}
+\]
+---
+### 2. Relate \(F'(x)\) to the given right‑hand side
+The given expression is exactly one‑half of \(F'(x)\):
+\[
+\frac{2\cos (2x)}{\arcsin (2x)}-
+\frac{2\sin (2x)}{\sqrt{1-4x^{2}}\;(\arcsin (2x))^{2}}
+=\frac12\,F'(x).
+\]
+Hence  
+\[
+y'=\frac12\,F'(x).
+\]
+---
+### 3. Integrate
+\[
+y=\int y'\,dx=\frac12\int F'(x)\,dx
+      =\frac12\,F(x)+C
+      =\frac12\left(\frac{2\sin (2x)}{\arcsin (2x)}\right)+C
+      =\frac{\sin (2x)}{\arcsin (2x)}+C .
+\]
+---
+\[
+\boxed{\,y=\dfrac{\sin (2x)}{\arcsin (2x)}+C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y=\dfrac{\sin (2x)}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
         <x:v>y^{\prime}=\operatorname{atan}{\left(x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} + \frac{2 \operatorname{atan}{\left(x \right)}}{4 x^{2} + 1} + \frac{\operatorname{ctan}{\left(x \right)}}{x^{2} + 1} + \frac{\operatorname{atan}{\left(2 x \right)}}{x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B22" t="str">
+      <x:c r="B25" t="str">
         <x:v>y=\arctg(x) \cdot \ctg(x)+\arctg(x) \cdot \arctg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C22" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D22" t="str">
+      <x:c r="C25" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -1769,17 +1951,17 @@
 \boxed{\,y = \arctan(x)\,\cot(x) + \arctan(x)\,\arctan(2x) + C\,}</x:v>
       </x:c>
     </x:row>
-    <x:row r="23">
-      <x:c r="A23" t="str">
+    <x:row r="26">
+      <x:c r="A26" t="str">
         <x:v>y^{\prime}=- \frac{2 x^{3} \cos{\left(2 x \right)}}{\sin^{2}{\left(2 x \right)}} + \frac{3 x^{2}}{\sin{\left(2 x \right)}} + \frac{1}{\left(x^{2} + 1\right) \log{\left(x \right)}} - \frac{\operatorname{atan}{\left(x \right)}}{x \log{\left(x \right)}^{2}}</x:v>
       </x:c>
-      <x:c r="B23" t="str">
+      <x:c r="B26" t="str">
         <x:v>y=x^{3} \cdot \frac{1}{\sin(2 \cdot x)}+\arctg(x) \cdot \frac{1}{\ln(x)}+C</x:v>
       </x:c>
-      <x:c r="C23" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D23" t="str">
+      <x:c r="C26" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The given differential equation is  
@@ -1834,17 +2016,17 @@
 \boxed{\,y(x)=\frac{x^{3}</x:v>
       </x:c>
     </x:row>
-    <x:row r="24">
-      <x:c r="A24" t="str">
+    <x:row r="27">
+      <x:c r="A27" t="str">
         <x:v>y^{\prime}=\frac{1}{\sqrt{1 - x^{2}} \operatorname{acos}{\left(2 x \right)}} - \frac{2 \operatorname{acos}{\left(x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{acos}^{2}{\left(2 x \right)}} + \frac{2 \cos{\left(2 x \right)}}{x^{3}} - \frac{3 \sin{\left(2 x \right)}}{x^{4}}</x:v>
       </x:c>
-      <x:c r="B24" t="str">
+      <x:c r="B27" t="str">
         <x:v>y=\sin(2 \cdot x) \cdot \frac{1}{x^{3}}-\arccos(x) \cdot \frac{1}{\arccos(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C24" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D24" t="str">
+      <x:c r="C27" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -1925,17 +2107,17 @@
 \boxed{\,y(x)=\frac{\sin (2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="25">
-      <x:c r="A25" t="str">
+    <x:row r="28">
+      <x:c r="A28" t="str">
         <x:v>y^{\prime}=\frac{e^{x} \log{\left(e \right)}}{\log{\left(2 x \right)}} - \frac{e^{x}}{x \log{\left(2 x \right)}^{2}}</x:v>
       </x:c>
-      <x:c r="B25" t="str">
+      <x:c r="B28" t="str">
         <x:v>y=e^{x} \cdot \frac{1}{\ln(2 \cdot x)}-\arcctg(x) \cdot e^{x}+C</x:v>
       </x:c>
-      <x:c r="C25" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D25" t="str">
+      <x:c r="C28" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 The differential equation is  
@@ -1989,17 +2171,17 @@
 \boxed{\,y = \frac{e^{x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="26">
-      <x:c r="A26" t="str">
+    <x:row r="29">
+      <x:c r="A29" t="str">
         <x:v>y^{\prime}=- 2 \sin{\left(2 x \right)} \operatorname{acos}{\left(x \right)} + \frac{\operatorname{asin}{\left(2 x \right)}}{x^{2} + 1} - \frac{\cos{\left(2 x \right)}}{\sqrt{1 - x^{2}}} + \frac{2 \operatorname{atan}{\left(x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B26" t="str">
+      <x:c r="B29" t="str">
         <x:v>y=\arccos(x) \cdot \cos(2 \cdot x)+\arcsin(2 \cdot x) \cdot \arctg(x)+C</x:v>
       </x:c>
-      <x:c r="C26" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D26" t="str">
+      <x:c r="C29" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
         <x:v>[REASONING]
 **Reasoning**
 We are given  
@@ -2060,17 +2242,17 @@
 \boxed{\,y = \cos (2x)\,\arccos x \;+\; \arcsin (2x)\,\arctan x \;+\; C\,}</x:v>
       </x:c>
     </x:row>
-    <x:row r="27">
-      <x:c r="A27" t="str">
+    <x:row r="30">
+      <x:c r="A30" t="str">
         <x:v>y^{\prime}=e^{x} \log{\left(e \right)} \operatorname{acos}{\left(2 x \right)} - \frac{2 e^{x}}{\sqrt{1 - 4 x^{2}}} - x^{2} \left(\tan^{2}{\left(x \right)} + 1\right) - 2 x \tan{\left(x \right)}</x:v>
       </x:c>
-      <x:c r="B27" t="str">
+      <x:c r="B30" t="str">
         <x:v>y=\arccos(2 \cdot x) \cdot e^{x}-x^{2} \cdot \tg(x)+C</x:v>
       </x:c>
-      <x:c r="C27" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D27" t="str">
+      <x:c r="C30" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -2115,34 +2297,34 @@
 \boxed{\,y = e^{x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="28">
-      <x:c r="A28" t="str">
+    <x:row r="31">
+      <x:c r="A31" t="str">
         <x:v>y^{\prime}=\frac{2 \operatorname{atan}{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - \frac{2}{\left(4 x^{2} + 1\right) \operatorname{ctan}{\left(2 x \right)}} - 2 e^{- 2 x} x^{2} \log{\left(e \right)} + 2 e^{- 2 x} x</x:v>
       </x:c>
-      <x:c r="B28" t="str">
+      <x:c r="B31" t="str">
         <x:v>y=x^{2} \cdot \frac{1}{e^{2 \cdot x}}-\arctg(2 \cdot x) \cdot \frac{1}{\ctg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C28" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D28" t="str">
+      <x:c r="C31" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
         <x:v>[REASONING]
 ERROR: Empty response
 [FINAL ANSWER]
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="29">
-      <x:c r="A29" t="str">
+    <x:row r="32">
+      <x:c r="A32" t="str">
         <x:v>y^{\prime}=\left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{asin}{\left(x \right)} + \frac{\tan{\left(x \right)}}{\sqrt{1 - x^{2}}} + 2 e^{- 2 x} \log{\left(e \right)} \operatorname{asin}{\left(x \right)} - \frac{e^{- 2 x}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
-      <x:c r="B29" t="str">
+      <x:c r="B32" t="str">
         <x:v>y=\arcsin(x) \cdot \tg(x)-\arcsin(x) \cdot \frac{1}{e^{2 \cdot x}}+C</x:v>
       </x:c>
-      <x:c r="C29" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D29" t="str">
+      <x:c r="C32" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 The differential equation is  
@@ -2197,17 +2379,17 @@
 \boxed{\,y = \arcsin x\bigl(\tan x - e^{-2x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="30">
-      <x:c r="A30" t="str">
+    <x:row r="33">
+      <x:c r="A33" t="str">
         <x:v>y^{\prime}=\frac{2 \cos{\left(2 x \right)}}{\operatorname{asin}{\left(2 x \right)}} - \frac{2 \log{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}} - \frac{2 \sin{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}} + \frac{1}{x \operatorname{asin}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B30" t="str">
+      <x:c r="B33" t="str">
         <x:v>y=\sin(2 \cdot x) \cdot \frac{1}{\arcsin(2 \cdot x)}+\ln(2 \cdot x) \cdot \frac{1}{\arcsin(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C30" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D30" t="str">
+      <x:c r="C33" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 1. **Introduce a convenient notation**  
@@ -2269,17 +2451,17 @@
 \boxed{\,y(x)=\frac{\log (2x)+\sin (2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="31">
-      <x:c r="A31" t="str">
+    <x:row r="34">
+      <x:c r="A34" t="str">
         <x:v>y^{\prime}=- \frac{2 \operatorname{acot}{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - \frac{2}{\left(4 x^{2} + 1\right) \operatorname{ctan}{\left(2 x \right)}} - \frac{1}{\sqrt{1 - x^{2}} \operatorname{asin}{\left(2 x \right)}} + \frac{2 \operatorname{asin}{\left(x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B31" t="str">
+      <x:c r="B34" t="str">
         <x:v>y=\arcctg(2 \cdot x) \cdot \frac{1}{\ctg(2 \cdot x)}-\arcsin(x) \cdot \frac{1}{\arcsin(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C31" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D31" t="str">
+      <x:c r="C34" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
         <x:v>[REASONING]
 [REASONING]
 First rewrite the right–hand side using the usual trigonometric notation  
@@ -2298,17 +2480,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
-      <x:c r="A32" t="str">
+    <x:row r="35">
+      <x:c r="A35" t="str">
         <x:v>y^{\prime}=- \frac{2 x^{2}}{\sqrt{1 - 4 x^{2}}} + 2 x \operatorname{acos}{\left(2 x \right)} + \left(2 \tan^{2}{\left(2 x \right)} + 2\right) \operatorname{ctan}{\left(x \right)} + \tan{\left(2 x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}</x:v>
       </x:c>
-      <x:c r="B32" t="str">
+      <x:c r="B35" t="str">
         <x:v>y=\arccos(2 \cdot x) \cdot x^{2}+\tg(2 \cdot x) \cdot \ctg(x)+C</x:v>
       </x:c>
-      <x:c r="C32" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D32" t="str">
+      <x:c r="C35" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The differential equation is  
@@ -2379,17 +2561,17 @@
 \boxed{\,y(x)=x^{2}</x:v>
       </x:c>
     </x:row>
-    <x:row r="33">
-      <x:c r="A33" t="str">
+    <x:row r="36">
+      <x:c r="A36" t="str">
         <x:v>y^{\prime}=- \frac{\log{\left(2 x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{ctan}^{2}{\left(x \right)}} + \frac{1}{x \operatorname{ctan}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B33" t="str">
+      <x:c r="B36" t="str">
         <x:v>y=\ln(2 \cdot x) \cdot \frac{1}{\ctg(x)}-e^{2 \cdot x} \cdot \ctg(x)+C</x:v>
       </x:c>
-      <x:c r="C33" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D33" t="str">
+      <x:c r="C36" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 The given differential equation is  
@@ -2471,17 +2653,17 @@
 \boxed{\,y = \tan x\,\log (2x) + C\,}</x:v>
       </x:c>
     </x:row>
-    <x:row r="34">
-      <x:c r="A34" t="str">
+    <x:row r="37">
+      <x:c r="A37" t="str">
         <x:v>y^{\prime}=e^{x} \log{\left(e \right)} \log{\left(2 x \right)} + \frac{e^{x}}{x} + x \left(\tan^{2}{\left(x \right)} + 1\right) + \tan{\left(x \right)}</x:v>
       </x:c>
-      <x:c r="B34" t="str">
+      <x:c r="B37" t="str">
         <x:v>y=x \cdot \tg(x)+\ln(2 \cdot x) \cdot e^{x}+C</x:v>
       </x:c>
-      <x:c r="C34" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D34" t="str">
+      <x:c r="C37" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -2546,17 +2728,17 @@
 \boxed{\,y = e^{x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="35">
-      <x:c r="A35" t="str">
+    <x:row r="38">
+      <x:c r="A38" t="str">
         <x:v>y^{\prime}=\frac{2 e^{2 x} \log{\left(e \right)}}{\cos{\left(2 x \right)}} + \frac{2 e^{2 x} \sin{\left(2 x \right)}}{\cos^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B35" t="str">
+      <x:c r="B38" t="str">
         <x:v>y=e^{2 \cdot x} \cdot \frac{1}{\cos(2 \cdot x)}+\arcsin(x) \cdot \cos(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C35" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D35" t="str">
+      <x:c r="C38" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -2607,17 +2789,17 @@
 \boxed{\,y(x)=\frac{e^{2x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="36">
-      <x:c r="A36" t="str">
+    <x:row r="39">
+      <x:c r="A39" t="str">
         <x:v>y^{\prime}=e^{x} \log{\left(e \right)} \sin{\left(2 x \right)} + 2 e^{x} \cos{\left(2 x \right)} + \frac{2 x}{4 x^{2} + 1} - \operatorname{acot}{\left(2 x \right)}</x:v>
       </x:c>
-      <x:c r="B36" t="str">
+      <x:c r="B39" t="str">
         <x:v>y=\sin(2 \cdot x) \cdot e^{x}-x \cdot \arcctg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C36" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D36" t="str">
+      <x:c r="C39" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -2672,17 +2854,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="37">
-      <x:c r="A37" t="str">
+    <x:row r="40">
+      <x:c r="A40" t="str">
         <x:v>y^{\prime}=3 x^{2} - \left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{atan}{\left(x \right)} - \frac{\tan{\left(x \right)}}{x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B37" t="str">
+      <x:c r="B40" t="str">
         <x:v>y=x \cdot x^{2}-\tg(x) \cdot \arctg(x)+C</x:v>
       </x:c>
-      <x:c r="C37" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D37" t="str">
+      <x:c r="C40" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The differential equation is  
@@ -2734,17 +2916,17 @@
 \boxed{\,y = x^{3}</x:v>
       </x:c>
     </x:row>
-    <x:row r="38">
-      <x:c r="A38" t="str">
+    <x:row r="41">
+      <x:c r="A41" t="str">
         <x:v>y^{\prime}=\frac{\operatorname{ctan}{\left(x \right)} \sin{\left(x \right)}}{\cos^{2}{\left(x \right)}} + \frac{\frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\cos{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B38" t="str">
+      <x:c r="B41" t="str">
         <x:v>y=\ctg(x) \cdot \frac{1}{\cos(x)}+\sin(x) \cdot \arcctg(x)+C</x:v>
       </x:c>
-      <x:c r="C38" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D38" t="str">
+      <x:c r="C41" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -2822,17 +3004,17 @@
 \boxed{y = \csc x + C}</x:v>
       </x:c>
     </x:row>
-    <x:row r="39">
-      <x:c r="A39" t="str">
+    <x:row r="42">
+      <x:c r="A42" t="str">
         <x:v>y^{\prime}=- 2 \operatorname{ctan}{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} - \operatorname{ctan}{\left(2 x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} - \sin{\left(x \right)} \operatorname{asin}{\left(2 x \right)} + \frac{2 \cos{\left(x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B39" t="str">
+      <x:c r="B42" t="str">
         <x:v>y=\cos(x) \cdot \arcsin(2 \cdot x)-\ctg(x) \cdot \ctg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C39" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D39" t="str">
+      <x:c r="C42" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -2909,17 +3091,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="40">
-      <x:c r="A40" t="str">
+    <x:row r="43">
+      <x:c r="A43" t="str">
         <x:v>y^{\prime}=\left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{asin}{\left(x \right)} + \frac{\tan{\left(x \right)}}{\sqrt{1 - x^{2}}} - 2 e^{- 2 x} x^{3} \log{\left(e \right)} + 3 e^{- 2 x} x^{2}</x:v>
       </x:c>
-      <x:c r="B40" t="str">
+      <x:c r="B43" t="str">
         <x:v>y=\tg(x) \cdot \arcsin(x)+x^{3} \cdot \frac{1}{e^{2 \cdot x}}+C</x:v>
       </x:c>
-      <x:c r="C40" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D40" t="str">
+      <x:c r="C43" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -2976,17 +3158,17 @@
 \boxed{\,y(x)=\tan x\,\arcsin x + x^{3}</x:v>
       </x:c>
     </x:row>
-    <x:row r="41">
-      <x:c r="A41" t="str">
+    <x:row r="44">
+      <x:c r="A44" t="str">
         <x:v>y^{\prime}=\frac{\cos{\left(x \right)}}{\log{\left(x \right)}} - \frac{\sin{\left(x \right)}}{x \log{\left(x \right)}^{2}}</x:v>
       </x:c>
-      <x:c r="B41" t="str">
+      <x:c r="B44" t="str">
         <x:v>y=\sin(x) \cdot \frac{1}{\ln(x)}+\sin(x) \cdot \tg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C41" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D41" t="str">
+      <x:c r="C44" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -3026,17 +3208,17 @@
 \boxed{\,y(x)=\frac{\sin x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="42">
-      <x:c r="A42" t="str">
+    <x:row r="45">
+      <x:c r="A45" t="str">
         <x:v>y^{\prime}=- \left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{asin}{\left(x \right)} - \frac{\tan{\left(x \right)}}{\sqrt{1 - x^{2}}} + \frac{\operatorname{acos}{\left(x \right)}}{\sqrt{1 - x^{2}}} - \frac{\operatorname{asin}{\left(x \right)}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
-      <x:c r="B42" t="str">
+      <x:c r="B45" t="str">
         <x:v>y=\arcsin(x) \cdot \arccos(x)-\arcsin(x) \cdot \tg(x)+C</x:v>
       </x:c>
-      <x:c r="C42" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D42" t="str">
+      <x:c r="C45" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
         <x:v>[REASONING]
 **Reasoning**
 \[
@@ -3086,17 +3268,17 @@
 \boxed{\,y=\arcsin x\bigl(\arccos x-\tan x\bigr)+C\,}</x:v>
       </x:c>
     </x:row>
-    <x:row r="43">
-      <x:c r="A43" t="str">
+    <x:row r="46">
+      <x:c r="A46" t="str">
         <x:v>y^{\prime}=2 e^{2 x} \log{\left(e \right)} \operatorname{atan}{\left(x \right)} + \frac{e^{2 x}}{x^{2} + 1} - \frac{2}{\left(4 x^{2} + 1\right) \log{\left(2 x \right)}} + \frac{\operatorname{atan}{\left(2 x \right)}}{x \log{\left(2 x \right)}^{2}}</x:v>
       </x:c>
-      <x:c r="B43" t="str">
+      <x:c r="B46" t="str">
         <x:v>y=e^{2 \cdot x} \cdot \arctg(x)-\arctg(2 \cdot x) \cdot \frac{1}{\ln(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C43" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D43" t="str">
+      <x:c r="C46" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The given differential equation is  
@@ -3167,17 +3349,17 @@
 \boxed{\,y(x)=e^{2x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="44">
-      <x:c r="A44" t="str">
+    <x:row r="47">
+      <x:c r="A47" t="str">
         <x:v>y^{\prime}=- e^{x} \log{\left(e \right)} \cos{\left(x \right)} + e^{x} \sin{\left(x \right)} + 2 \log{\left(x \right)} \cos{\left(2 x \right)} + \frac{\sin{\left(2 x \right)}}{x}</x:v>
       </x:c>
-      <x:c r="B44" t="str">
+      <x:c r="B47" t="str">
         <x:v>y=\ln(x) \cdot \sin(2 \cdot x)-\cos(x) \cdot e^{x}+C</x:v>
       </x:c>
-      <x:c r="C44" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D44" t="str">
+      <x:c r="C47" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -3233,17 +3415,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="45">
-      <x:c r="A45" t="str">
+    <x:row r="48">
+      <x:c r="A48" t="str">
         <x:v>y^{\prime}=- \frac{\cos{\left(x \right)} \operatorname{acot}{\left(2 x \right)}}{\sin^{2}{\left(x \right)}} - \frac{2}{\left(4 x^{2} + 1\right) \sin{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B45" t="str">
+      <x:c r="B48" t="str">
         <x:v>y=\arcctg(2 \cdot x) \cdot \frac{1}{\sin(x)}-\arccos(2 \cdot x) \cdot \arcctg(x)+C</x:v>
       </x:c>
-      <x:c r="C45" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D45" t="str">
+      <x:c r="C48" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -3294,17 +3476,90 @@
 \boxed{\,y(x)=\frac{\operatorname{acot}</x:v>
       </x:c>
     </x:row>
-    <x:row r="46">
-      <x:c r="A46" t="str">
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>y^{\prime}=- \frac{1}{\sqrt{1 - x^{2}} \log{\left(x \right)}} - \frac{\operatorname{acos}{\left(x \right)}}{x \log{\left(x \right)}^{2}}</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>y=\arccos(x) \cdot \frac{1}{\ln(x)}+\sin(2 \cdot x) \cdot x+C</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>[REASONING]
+**Reasoning**
+The differential equation is  
+\[
+y'=- \frac{1}{\sqrt{1 - x^{2}}\,\log x}-\frac{\arccos x}{x\,(\log x)^{2}} .
+\]
+We look for a function whose derivative gives the right‑hand side.  
+Consider  
+\[
+f(x)=\frac{\arccos x}{\log x}.
+\]
+Compute its derivative using the product rule (or quotient rule).
+\[
+\begin{aligned}
+f'(x) &amp;= \frac{d}{dx}\Bigl[\arccos x\cdot (\log x)^{-1}\Bigr]  \\
+&amp;= (\arccos x)'\,(\log x)^{-1}
+   +\arccos x\,\frac{d}{dx}\bigl[(\log x)^{-1}\bigr].
+\end{aligned}
+\]
+1. Derivative of \(\arccos x\):
+\[
+(\arccos x)' = -\frac{1}{\sqrt{1-x^{2}}}.
+\]
+Thus the first term is  
+\[
+-\frac{1}{\sqrt{1-x^{2}}}\,\frac{1}{\log x}
+   = -\frac{1}{\sqrt{1-x^{2}}\,\log x}.
+\]
+2. Derivative of \((\log x)^{-1}\):
+\[
+\frac{d}{dx}\bigl[(\log x)^{-1}\bigr]
+   = -(\log x)^{-2}\,\frac{1}{x}
+   = -\frac{1}{x(\log x)^{2}}.
+\]
+Hence the second term is  
+\[
+\arccos x\left(-\frac{1}{x(\log x)^{2}}\right)
+   = -\frac{\arccos x}{x(\log x)^{2}}.
+\]
+Adding the two terms gives  
+\[
+f'(x)= -\frac{1}{\sqrt{1-x^{2}}\,\log x}
+        -\frac{\arccos x}{x(\log x)^{2}},
+\]
+which is exactly the right‑hand side of the differential equation. Therefore  
+\[
+y' = f'(x) \quad\Longrightarrow\quad y = f(x) + C.
+\]
+Thus the general solution is  
+\[
+y = \frac{\arccos x}{\log x} + C,
+\]
+where \(C\) is an arbitrary constant.
+---
+**Final Answer**
+\[
+\boxed{\,y = \frac{\arccos(x)}{\log x} + C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y = \frac{\arccos(x)}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="str">
         <x:v>y^{\prime}=- 2 x \sin{\left(2 x \right)} + \cos{\left(2 x \right)} + \frac{2 \operatorname{asin}{\left(2 x \right)}}{\left(4 x^{2} + 1\right) \operatorname{atan}^{2}{\left(2 x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{atan}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B46" t="str">
+      <x:c r="B50" t="str">
         <x:v>y=\cos(2 \cdot x) \cdot x-\arcsin(2 \cdot x) \cdot \frac{1}{\arctg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C46" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D46" t="str">
+      <x:c r="C50" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D50" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -3380,17 +3635,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="47">
-      <x:c r="A47" t="str">
+    <x:row r="51">
+      <x:c r="A51" t="str">
         <x:v>y^{\prime}=\left(2 \tan^{2}{\left(2 x \right)} + 2\right) \operatorname{ctan}{\left(2 x \right)} + 2 \tan{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} - \frac{\operatorname{asin}{\left(2 x \right)}}{\sqrt{1 - x^{2}}} + \frac{2 \operatorname{acos}{\left(x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B47" t="str">
+      <x:c r="B51" t="str">
         <x:v>y=\tg(2 \cdot x) \cdot \ctg(2 \cdot x)+\arccos(x) \cdot \arcsin(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C47" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D47" t="str">
+      <x:c r="C51" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D51" t="str">
         <x:v>[REASONING]
 **Solution**
 The differential equation is  
@@ -3408,17 +3663,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="48">
-      <x:c r="A48" t="str">
+    <x:row r="52">
+      <x:c r="A52" t="str">
         <x:v>y^{\prime}=\left(\tan^{2}{\left(x \right)} + 1\right) \cos{\left(2 x \right)} - 2 \sin{\left(2 x \right)} \tan{\left(x \right)} - \frac{\operatorname{asin}{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}} + \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{asin}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B48" t="str">
+      <x:c r="B52" t="str">
         <x:v>y=\cos(2 \cdot x) \cdot \tg(x)+\arcsin(2 \cdot x) \cdot \frac{1}{\arcsin(x)}+C</x:v>
       </x:c>
-      <x:c r="C48" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D48" t="str">
+      <x:c r="C52" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D52" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -3464,17 +3719,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="49">
-      <x:c r="A49" t="str">
+    <x:row r="53">
+      <x:c r="A53" t="str">
         <x:v>y^{\prime}=\frac{\log{\left(x \right)}}{x^{2} + 1} + \frac{\operatorname{atan}{\left(x \right)}}{x} - e^{- 2 x} \left(\tan^{2}{\left(x \right)} + 1\right) + 2 e^{- 2 x} \log{\left(e \right)} \tan{\left(x \right)}</x:v>
       </x:c>
-      <x:c r="B49" t="str">
+      <x:c r="B53" t="str">
         <x:v>y=\ln(x) \cdot \arctg(x)-\tg(x) \cdot \frac{1}{e^{2 \cdot x}}+C</x:v>
       </x:c>
-      <x:c r="C49" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D49" t="str">
+      <x:c r="C53" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D53" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -3540,17 +3795,17 @@
 \boxed{\,y(x)=\log x\,\arctan x\;-\;e^{-2x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="50">
-      <x:c r="A50" t="str">
+    <x:row r="54">
+      <x:c r="A54" t="str">
         <x:v>y^{\prime}=\frac{\tan^{2}{\left(x \right)} + 1}{\cos{\left(2 x \right)}} + \frac{2 \sin{\left(2 x \right)} \tan{\left(x \right)}}{\cos^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B50" t="str">
+      <x:c r="B54" t="str">
         <x:v>y=\tg(x) \cdot \frac{1}{\cos(2 \cdot x)}-e^{x} \cdot \ctg(x)+C</x:v>
       </x:c>
-      <x:c r="C50" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D50" t="str">
+      <x:c r="C54" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D54" t="str">
         <x:v>[REASONING]
 **Solution**
 \[
@@ -3598,17 +3853,17 @@
 \boxed{\,y=\dfrac{\tan x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="51">
-      <x:c r="A51" t="str">
+    <x:row r="55">
+      <x:c r="A55" t="str">
         <x:v>y^{\prime}=\frac{x^{2} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{ctan}^{2}{\left(x \right)}} - \frac{2 x}{\operatorname{ctan}{\left(x \right)}} - \frac{\log{\left(x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}} + \frac{1}{x \operatorname{asin}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B51" t="str">
+      <x:c r="B55" t="str">
         <x:v>y=\ln(x) \cdot \frac{1}{\arcsin(x)}-x^{2} \cdot \frac{1}{\ctg(x)}+C</x:v>
       </x:c>
-      <x:c r="C51" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D51" t="str">
+      <x:c r="C55" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D55" t="str">
         <x:v>[REASONING]
 **Solution**
 \[
@@ -3676,17 +3931,17 @@
 \boxed{\,y=\frac{\log x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="52">
-      <x:c r="A52" t="str">
+    <x:row r="56">
+      <x:c r="A56" t="str">
         <x:v>y^{\prime}=\frac{2 e^{2 x} \log{\left(e \right)}}{x^{3}} - \frac{3 e^{2 x}}{x^{4}}</x:v>
       </x:c>
-      <x:c r="B52" t="str">
+      <x:c r="B56" t="str">
         <x:v>y=e^{2 \cdot x} \cdot \frac{1}{x^{3}}-\sin(2 \cdot x) \cdot x^{2}+C</x:v>
       </x:c>
-      <x:c r="C52" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D52" t="str">
+      <x:c r="C56" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D56" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -3730,17 +3985,17 @@
 \boxed{\,y(x)=\frac{e^{2x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="53">
-      <x:c r="A53" t="str">
+    <x:row r="57">
+      <x:c r="A57" t="str">
         <x:v>y^{\prime}=- \frac{2 \operatorname{acot}{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - \frac{1}{\left(x^{2} + 1\right) \operatorname{ctan}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B53" t="str">
+      <x:c r="B57" t="str">
         <x:v>y=\arcctg(x) \cdot \frac{1}{\ctg(2 \cdot x)}+\tg(2 \cdot x) \cdot e^{2 \cdot x}+C</x:v>
       </x:c>
-      <x:c r="C53" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D53" t="str">
+      <x:c r="C57" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D57" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -3790,17 +4045,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="54">
-      <x:c r="A54" t="str">
+    <x:row r="58">
+      <x:c r="A58" t="str">
         <x:v>y^{\prime}=- \frac{\sin{\left(x \right)}}{\sin{\left(2 x \right)}} - \frac{2 \cos{\left(x \right)} \cos{\left(2 x \right)}}{\sin^{2}{\left(2 x \right)}} - 2 e^{- 2 x} \operatorname{ctan}{\left(2 x \right)} \log{\left(e \right)} + 2 e^{- 2 x} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}</x:v>
       </x:c>
-      <x:c r="B54" t="str">
+      <x:c r="B58" t="str">
         <x:v>y=\ctg(2 \cdot x) \cdot \frac{1}{e^{2 \cdot x}}+\cos(x) \cdot \frac{1}{\sin(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C54" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D54" t="str">
+      <x:c r="C58" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D58" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -3883,17 +4138,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="55">
-      <x:c r="A55" t="str">
+    <x:row r="59">
+      <x:c r="A59" t="str">
         <x:v>y^{\prime}=e^{x} \log{\left(e \right)} \cos{\left(2 x \right)} + e^{x} \log{\left(e \right)} \operatorname{acot}{\left(x \right)} - 2 e^{x} \sin{\left(2 x \right)} - \frac{e^{x}}{x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B55" t="str">
+      <x:c r="B59" t="str">
         <x:v>y=e^{x} \cdot \cos(2 \cdot x)+e^{x} \cdot \arcctg(x)+C</x:v>
       </x:c>
-      <x:c r="C55" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D55" t="str">
+      <x:c r="C59" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D59" t="str">
         <x:v>[REASONING]
 **Solution**
 \[
@@ -3948,17 +4203,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="56">
-      <x:c r="A56" t="str">
+    <x:row r="60">
+      <x:c r="A60" t="str">
         <x:v>y^{\prime}=- \frac{1}{\left(x^{2} + 1\right) \operatorname{asin}{\left(2 x \right)}} - \frac{2 \operatorname{acot}{\left(x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B56" t="str">
+      <x:c r="B60" t="str">
         <x:v>y=\arcctg(x) \cdot \frac{1}{\arcsin(2 \cdot x)}+e^{2 \cdot x} \cdot \arcctg(x)+C</x:v>
       </x:c>
-      <x:c r="C56" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D56" t="str">
+      <x:c r="C60" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D60" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 The differential equation is  
@@ -4015,17 +4270,17 @@
 \boxed{\,y(x)=\frac{\operatorname{acot}</x:v>
       </x:c>
     </x:row>
-    <x:row r="57">
-      <x:c r="A57" t="str">
+    <x:row r="61">
+      <x:c r="A61" t="str">
         <x:v>y^{\prime}=- \frac{x^{3}}{x^{2} + 1} + 3 x^{2} \operatorname{acot}{\left(x \right)} - 2 \sin{\left(2 x \right)} \operatorname{atan}{\left(2 x \right)} + \frac{2 \cos{\left(2 x \right)}}{4 x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B57" t="str">
+      <x:c r="B61" t="str">
         <x:v>y=x^{3} \cdot \arcctg(x)+\arctg(2 \cdot x) \cdot \cos(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C57" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D57" t="str">
+      <x:c r="C61" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D61" t="str">
         <x:v>[REASONING]
 **Step‑by‑step integration**
 The differential equation is  
@@ -4055,17 +4310,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="58">
-      <x:c r="A58" t="str">
+    <x:row r="62">
+      <x:c r="A62" t="str">
         <x:v>y^{\prime}=- \frac{2 \cos{\left(2 x \right)}}{\log{\left(2 x \right)}} + \frac{2}{\left(4 x^{2} + 1\right) \operatorname{asin}{\left(x \right)}} - \frac{\operatorname{atan}{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}} + \frac{\sin{\left(2 x \right)}}{x \log{\left(2 x \right)}^{2}}</x:v>
       </x:c>
-      <x:c r="B58" t="str">
+      <x:c r="B62" t="str">
         <x:v>y=\arctg(2 \cdot x) \cdot \frac{1}{\arcsin(x)}-\sin(2 \cdot x) \cdot \frac{1}{\ln(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C58" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D58" t="str">
+      <x:c r="C62" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D62" t="str">
         <x:v>[REASONING]
 **Solution**
 \[
@@ -4147,17 +4402,17 @@
 \boxed{\,y(x)=\frac{\displaystyle\arctan (2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="59">
-      <x:c r="A59" t="str">
+    <x:row r="63">
+      <x:c r="A63" t="str">
         <x:v>y^{\prime}=2 \cos{\left(2 x \right)} \operatorname{acot}{\left(2 x \right)} + \frac{2 \cos{\left(2 x \right)}}{\operatorname{ctan}{\left(2 x \right)}} - \frac{2 \sin{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - \frac{2 \sin{\left(2 x \right)}}{4 x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B59" t="str">
+      <x:c r="B63" t="str">
         <x:v>y=\sin(2 \cdot x) \cdot \arcctg(2 \cdot x)+\sin(2 \cdot x) \cdot \frac{1}{\ctg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C59" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D59" t="str">
+      <x:c r="C63" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D63" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -4168,17 +4423,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="60">
-      <x:c r="A60" t="str">
+    <x:row r="64">
+      <x:c r="A64" t="str">
         <x:v>y^{\prime}=2 \cos{\left(2 x \right)} \operatorname{asin}{\left(x \right)} - \frac{2 \operatorname{acot}{\left(x \right)}}{4 x^{2} + 1} - \frac{\operatorname{acot}{\left(2 x \right)}}{x^{2} + 1} + \frac{\sin{\left(2 x \right)}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
-      <x:c r="B60" t="str">
+      <x:c r="B64" t="str">
         <x:v>y=\sin(2 \cdot x) \cdot \arcsin(x)+\arcctg(2 \cdot x) \cdot \arcctg(x)+C</x:v>
       </x:c>
-      <x:c r="C60" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D60" t="str">
+      <x:c r="C64" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D64" t="str">
         <x:v>[REASONING]
 **Reasoning**
 \[
@@ -4245,17 +4500,17 @@
 \boxed{\,y = \sin(2x)\,\arcsin x + \operatorname{arccot}</x:v>
       </x:c>
     </x:row>
-    <x:row r="61">
-      <x:c r="A61" t="str">
+    <x:row r="65">
+      <x:c r="A65" t="str">
         <x:v>y^{\prime}=- \frac{2 x^{2}}{\sqrt{1 - 4 x^{2}}} + 2 x \operatorname{acos}{\left(2 x \right)} + \left(\tan^{2}{\left(x \right)} + 1\right) \log{\left(x \right)} + \frac{\tan{\left(x \right)}}{x}</x:v>
       </x:c>
-      <x:c r="B61" t="str">
+      <x:c r="B65" t="str">
         <x:v>y=\arccos(2 \cdot x) \cdot x^{2}+\tg(x) \cdot \ln(x)+C</x:v>
       </x:c>
-      <x:c r="C61" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D61" t="str">
+      <x:c r="C65" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D65" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The differential equation is  
@@ -4328,17 +4583,17 @@
 \boxed{\,y(x)=x^{2}</x:v>
       </x:c>
     </x:row>
-    <x:row r="62">
-      <x:c r="A62" t="str">
+    <x:row r="66">
+      <x:c r="A66" t="str">
         <x:v>y^{\prime}=- \frac{2 \log{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}} + \frac{1}{x \operatorname{asin}{\left(2 x \right)}} + \frac{2}{x \left(4 x^{2} + 1\right)} - \frac{\operatorname{atan}{\left(2 x \right)}}{x^{2}}</x:v>
       </x:c>
-      <x:c r="B62" t="str">
+      <x:c r="B66" t="str">
         <x:v>y=\arctg(2 \cdot x) \cdot \frac{1}{x}+\ln(2 \cdot x) \cdot \frac{1}{\arcsin(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C62" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D62" t="str">
+      <x:c r="C66" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D66" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -4415,17 +4670,17 @@
 \boxed{\,y(x)=\frac{\log (2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="63">
-      <x:c r="A63" t="str">
+    <x:row r="67">
+      <x:c r="A67" t="str">
         <x:v>y^{\prime}=2 x \log{\left(x \right)} + x + \frac{\operatorname{acos}{\left(2 x \right)}}{x^{2} + 1} + \frac{2 \operatorname{acot}{\left(x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B63" t="str">
+      <x:c r="B67" t="str">
         <x:v>y=\ln(x) \cdot x^{2}-\arccos(2 \cdot x) \cdot \arcctg(x)+C</x:v>
       </x:c>
-      <x:c r="C63" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D63" t="str">
+      <x:c r="C67" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D67" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -4504,17 +4759,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="64">
-      <x:c r="A64" t="str">
+    <x:row r="68">
+      <x:c r="A68" t="str">
         <x:v>y^{\prime}=e^{x} \log{\left(e \right)} \operatorname{acot}{\left(2 x \right)} - \frac{2 e^{x}}{4 x^{2} + 1} + 2 x \log{\left(2 x \right)} + x</x:v>
       </x:c>
-      <x:c r="B64" t="str">
+      <x:c r="B68" t="str">
         <x:v>y=\ln(2 \cdot x) \cdot x^{2}+e^{x} \cdot \arcctg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C64" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D64" t="str">
+      <x:c r="C68" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D68" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -4584,17 +4839,17 @@
 \boxed{\,y(x)=e^{x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="65">
-      <x:c r="A65" t="str">
+    <x:row r="69">
+      <x:c r="A69" t="str">
         <x:v>y^{\prime}=\frac{2 e^{2 x} \log{\left(e \right)}}{\operatorname{asin}{\left(x \right)}} - \frac{e^{2 x}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}} + \frac{\operatorname{asin}{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{asin}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B65" t="str">
+      <x:c r="B69" t="str">
         <x:v>y=e^{2 \cdot x} \cdot \frac{1}{\arcsin(x)}-\arcsin(2 \cdot x) \cdot \frac{1}{\arcsin(x)}+C</x:v>
       </x:c>
-      <x:c r="C65" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D65" t="str">
+      <x:c r="C69" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D69" t="str">
         <x:v>[REASONING]
 The right–hand side can be recognised as a total derivative.
 \[
@@ -4654,17 +4909,17 @@
 \boxed{\,y(x)=\frac{e^{2x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="66">
-      <x:c r="A66" t="str">
+    <x:row r="70">
+      <x:c r="A70" t="str">
         <x:v>y^{\prime}=e^{x} \log{\left(e \right)} \log{\left(2 x \right)} + \frac{e^{x}}{x} - 2 e^{- 2 x} \operatorname{ctan}{\left(2 x \right)} \log{\left(e \right)} + 2 e^{- 2 x} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}</x:v>
       </x:c>
-      <x:c r="B66" t="str">
+      <x:c r="B70" t="str">
         <x:v>y=\ln(2 \cdot x) \cdot e^{x}+\ctg(2 \cdot x) \cdot \frac{1}{e^{2 \cdot x}}+C</x:v>
       </x:c>
-      <x:c r="C66" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D66" t="str">
+      <x:c r="C70" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D70" t="str">
         <x:v>[REASONING]
 [REASONING]
 First simplify the right–hand side.
@@ -4718,34 +4973,34 @@
 \boxed{\,y(x)=e^{x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="67">
-      <x:c r="A67" t="str">
+    <x:row r="71">
+      <x:c r="A71" t="str">
         <x:v>y^{\prime}=- \frac{\left(- 2 \tan^{2}{\left(2 x \right)} - 2\right) \log{\left(2 x \right)}}{\tan^{2}{\left(2 x \right)}} + \frac{2 \tan^{2}{\left(2 x \right)} + 2}{\operatorname{acot}{\left(x \right)}} + \frac{\tan{\left(2 x \right)}}{\left(x^{2} + 1\right) \operatorname{acot}^{2}{\left(x \right)}} - \frac{1}{x \tan{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B67" t="str">
+      <x:c r="B71" t="str">
         <x:v>y=\tg(2 \cdot x) \cdot \frac{1}{\arcctg(x)}-\ln(2 \cdot x) \cdot \frac{1}{\tg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C67" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D67" t="str">
+      <x:c r="C71" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D71" t="str">
         <x:v>[REASONING]
 ERROR: Empty response
 [FINAL ANSWER]
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="68">
-      <x:c r="A68" t="str">
+    <x:row r="72">
+      <x:c r="A72" t="str">
         <x:v>y^{\prime}=\left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{asin}{\left(x \right)} + \frac{2 \operatorname{acos}{\left(2 x \right)}}{4 x^{2} + 1} + \frac{\tan{\left(x \right)}}{\sqrt{1 - x^{2}}} - \frac{2 \operatorname{atan}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B68" t="str">
+      <x:c r="B72" t="str">
         <x:v>y=\tg(x) \cdot \arcsin(x)+\arccos(2 \cdot x) \cdot \arctg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C68" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D68" t="str">
+      <x:c r="C72" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D72" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The differential equation is  
@@ -4805,17 +5060,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="69">
-      <x:c r="A69" t="str">
+    <x:row r="73">
+      <x:c r="A73" t="str">
         <x:v>y^{\prime}=\frac{\sin{\left(x \right)} \operatorname{asin}{\left(2 x \right)}}{\cos^{2}{\left(x \right)}} + \frac{2}{\sqrt{1 - 4 x^{2}} \cos{\left(x \right)}} - 2 e^{- 2 x} \log{\left(e \right)} \cos{\left(x \right)} - e^{- 2 x} \sin{\left(x \right)}</x:v>
       </x:c>
-      <x:c r="B69" t="str">
+      <x:c r="B73" t="str">
         <x:v>y=\arcsin(2 \cdot x) \cdot \frac{1}{\cos(x)}+\cos(x) \cdot \frac{1}{e^{2 \cdot x}}+C</x:v>
       </x:c>
-      <x:c r="C69" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D69" t="str">
+      <x:c r="C73" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D73" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The differential equation is  
@@ -4894,17 +5149,17 @@
 \boxed{\,y(x)=\frac{\arcsin (2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="70">
-      <x:c r="A70" t="str">
+    <x:row r="74">
+      <x:c r="A74" t="str">
         <x:v>y^{\prime}=\left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{atan}{\left(2 x \right)} - \left(2 \tan^{2}{\left(2 x \right)} + 2\right) \cos{\left(2 x \right)} + 2 \sin{\left(2 x \right)} \tan{\left(2 x \right)} + \frac{2 \tan{\left(x \right)}}{4 x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B70" t="str">
+      <x:c r="B74" t="str">
         <x:v>y=\arctg(2 \cdot x) \cdot \tg(x)-\cos(2 \cdot x) \cdot \tg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C70" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D70" t="str">
+      <x:c r="C74" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D74" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 \[
@@ -4981,34 +5236,34 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="71">
-      <x:c r="A71" t="str">
+    <x:row r="75">
+      <x:c r="A75" t="str">
         <x:v>y^{\prime}=- \frac{2 \sin{\left(2 x \right)}}{\sin{\left(x \right)}} - \frac{\cos{\left(x \right)} \cos{\left(2 x \right)}}{\sin^{2}{\left(x \right)}} - \frac{1}{\left(x^{2} + 1\right) \operatorname{acos}{\left(x \right)}} - \frac{\operatorname{atan}{\left(x \right)}}{\sqrt{1 - x^{2}} \operatorname{acos}^{2}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B71" t="str">
+      <x:c r="B75" t="str">
         <x:v>y=\cos(2 \cdot x) \cdot \frac{1}{\sin(x)}-\arctg(x) \cdot \frac{1}{\arccos(x)}+C</x:v>
       </x:c>
-      <x:c r="C71" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D71" t="str">
+      <x:c r="C75" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D75" t="str">
         <x:v>[REASONING]
 [REASONING]
 [FINAL ANSWER]
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="72">
-      <x:c r="A72" t="str">
+    <x:row r="76">
+      <x:c r="A76" t="str">
         <x:v>y^{\prime}=\frac{\cos{\left(x \right)}}{\operatorname{acos}{\left(2 x \right)}} + \frac{2 \sin{\left(x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{acos}^{2}{\left(2 x \right)}} - e^{- x} x^{3} \log{\left(e \right)} + 3 e^{- x} x^{2}</x:v>
       </x:c>
-      <x:c r="B72" t="str">
+      <x:c r="B76" t="str">
         <x:v>y=\sin(x) \cdot \frac{1}{\arccos(2 \cdot x)}+x^{3} \cdot \frac{1}{e^{x}}+C</x:v>
       </x:c>
-      <x:c r="C72" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D72" t="str">
+      <x:c r="C76" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D76" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -5075,17 +5330,17 @@
 \boxed{\,y(x)=\frac{\sin x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="73">
-      <x:c r="A73" t="str">
+    <x:row r="77">
+      <x:c r="A77" t="str">
         <x:v>y^{\prime}=- 5 x^{4} + \cos{\left(x \right)} \operatorname{acot}{\left(x \right)} - \frac{\sin{\left(x \right)}}{x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B73" t="str">
+      <x:c r="B77" t="str">
         <x:v>y=\sin(x) \cdot \arcctg(x)-x^{3} \cdot x^{2}+C</x:v>
       </x:c>
-      <x:c r="C73" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D73" t="str">
+      <x:c r="C77" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D77" t="str">
         <x:v>[REASONING]
 [REASONING]  
 The differential equation is given explicitly as a function of \(x\):
@@ -5151,17 +5406,17 @@
 \boxed{\,y = -x^{5}</x:v>
       </x:c>
     </x:row>
-    <x:row r="74">
-      <x:c r="A74" t="str">
+    <x:row r="78">
+      <x:c r="A78" t="str">
         <x:v>y^{\prime}=- \frac{\sin{\left(x \right)}}{\operatorname{acos}{\left(2 x \right)}} + \frac{2 \cos{\left(x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{acos}^{2}{\left(2 x \right)}} - e^{- x} \log{\left(e \right)} \operatorname{atan}{\left(2 x \right)} + \frac{2 e^{- x}}{4 x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B74" t="str">
+      <x:c r="B78" t="str">
         <x:v>y=\cos(x) \cdot \frac{1}{\arccos(2 \cdot x)}+\arctg(2 \cdot x) \cdot \frac{1}{e^{x}}+C</x:v>
       </x:c>
-      <x:c r="C74" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D74" t="str">
+      <x:c r="C78" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D78" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -5234,17 +5489,17 @@
 \boxed{\,y(x)=\frac{\cos x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="75">
-      <x:c r="A75" t="str">
+    <x:row r="79">
+      <x:c r="A79" t="str">
         <x:v>y^{\prime}=- \frac{\operatorname{ctan}{\left(2 x \right)} \cos{\left(x \right)}}{\sin^{2}{\left(x \right)}} + \frac{2 \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\sin{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B75" t="str">
+      <x:c r="B79" t="str">
         <x:v>y=\ctg(2 \cdot x) \cdot \frac{1}{\sin(x)}-\tg(x) \cdot \arccos(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C75" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D75" t="str">
+      <x:c r="C79" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D79" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -5312,17 +5567,17 @@
 \boxed{\,y(x)=\frac{\cot(2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="76">
-      <x:c r="A76" t="str">
+    <x:row r="80">
+      <x:c r="A80" t="str">
         <x:v>y^{\prime}=\left(2 \tan^{2}{\left(2 x \right)} + 2\right) \operatorname{asin}{\left(2 x \right)} + \frac{\log{\left(x \right)} \cos{\left(x \right)}}{\sin^{2}{\left(x \right)}} + \frac{2 \tan{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}} - \frac{1}{x \sin{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B76" t="str">
+      <x:c r="B80" t="str">
         <x:v>y=\tg(2 \cdot x) \cdot \arcsin(2 \cdot x)-\ln(x) \cdot \frac{1}{\sin(x)}+C</x:v>
       </x:c>
-      <x:c r="C76" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D76" t="str">
+      <x:c r="C80" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D80" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -5367,17 +5622,17 @@
 \boxed{\arcsin (2x)\tan (2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="77">
-      <x:c r="A77" t="str">
+    <x:row r="81">
+      <x:c r="A81" t="str">
         <x:v>y^{\prime}=2 \log{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} - \sin{\left(x \right)} \operatorname{asin}{\left(x \right)} + \frac{\cos{\left(x \right)}}{\sqrt{1 - x^{2}}} + \frac{\operatorname{ctan}{\left(2 x \right)}}{x}</x:v>
       </x:c>
-      <x:c r="B77" t="str">
+      <x:c r="B81" t="str">
         <x:v>y=\ctg(2 \cdot x) \cdot \ln(x)+\cos(x) \cdot \arcsin(x)+C</x:v>
       </x:c>
-      <x:c r="C77" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D77" t="str">
+      <x:c r="C81" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D81" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -5427,17 +5682,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="78">
-      <x:c r="A78" t="str">
+    <x:row r="82">
+      <x:c r="A82" t="str">
         <x:v>y^{\prime}=2 e^{2 x} \log{\left(e \right)} \log{\left(2 x \right)} + \frac{e^{2 x}}{x} + \frac{2 \operatorname{acot}{\left(x \right)}}{4 x^{2} + 1} + \frac{\operatorname{acot}{\left(2 x \right)}}{x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B78" t="str">
+      <x:c r="B82" t="str">
         <x:v>y=\ln(2 \cdot x) \cdot e^{2 \cdot x}-\arcctg(2 \cdot x) \cdot \arcctg(x)+C</x:v>
       </x:c>
-      <x:c r="C78" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D78" t="str">
+      <x:c r="C82" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D82" t="str">
         <x:v>[REASONING]
 **Solution**
 \[
@@ -5447,17 +5702,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="79">
-      <x:c r="A79" t="str">
+    <x:row r="83">
+      <x:c r="A83" t="str">
         <x:v>y^{\prime}=\frac{2}{\sqrt{1 - 4 x^{2}} \log{\left(2 x \right)}} - \frac{\operatorname{asin}{\left(2 x \right)}}{x \log{\left(2 x \right)}^{2}}</x:v>
       </x:c>
-      <x:c r="B79" t="str">
+      <x:c r="B83" t="str">
         <x:v>y=\arcsin(2 \cdot x) \cdot \frac{1}{\ln(2 \cdot x)}-\ctg(2 \cdot x) \cdot \tg(x)+C</x:v>
       </x:c>
-      <x:c r="C79" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D79" t="str">
+      <x:c r="C83" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D83" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -5504,17 +5759,84 @@
 \boxed{\,y=\frac{\arcsin (2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="80">
-      <x:c r="A80" t="str">
+    <x:row r="84">
+      <x:c r="A84" t="str">
+        <x:v>y^{\prime}=\frac{2}{\left(4 x^{2} + 1\right) \operatorname{asin}{\left(x \right)}} - \frac{\operatorname{atan}{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}}</x:v>
+      </x:c>
+      <x:c r="B84" t="str">
+        <x:v>y=\arctg(2 \cdot x) \cdot \frac{1}{\arcsin(x)}+\ctg(2 \cdot x) \cdot \sin(2 \cdot x)+C</x:v>
+      </x:c>
+      <x:c r="C84" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D84" t="str">
+        <x:v>[REASONING]
+**Step‑by‑step solution**
+\[
+y'=\frac{2}{\bigl(4x^{2}+1\bigr)\,\arcsin x}
+      -\frac{\arctan (2x)}{\sqrt{1-x^{2}}\;\bigl(\arcsin x\bigr)^{2}}
+\]
+---
+### 1.  Look for a function whose derivative gives the right‑hand side  
+Consider the quotient  
+\[
+u(x)=\frac{\arctan (2x)}{\arcsin x}.
+\]
+Its derivative, using the quotient rule \(\displaystyle \frac{d}{dx}\frac{u}{v}= \frac{u'v-u v'}{v^{2}}\), is  
+\[
+\begin{aligned}
+u'(x) &amp;=\frac{ \displaystyle\frac{d}{dx}\bigl[\arctan (2x)\bigr]\;\arcsin x
+        -\arctan (2x)\;\displaystyle\frac{d}{dx}\bigl[\arcsin x\bigr]}
+        {\bigl(\arcsin x\bigr)^{2}} .
+\end{aligned}
+\]
+Compute the two derivatives:
+* \(\displaystyle \frac{d}{dx}\bigl[\arctan (2x)\bigr]=\frac{2}{1+(2x)^{2}}
+        =\frac{2}{4x^{2}+1}\).
+* \(\displaystyle \frac{d}{dx}\bigl[\arcsin x\bigr]=\frac{1}{\sqrt{1-x^{2}}}\).
+Insert them:
+\[
+\begin{aligned}
+u'(x) &amp;=
+\frac{ \displaystyle \frac{2}{4x^{2}+1}\,\arcsin x
+        -\arctan (2x)\,\frac{1}{\sqrt{1-x^{2}}}}
+        {\bigl(\arcsin x\bigr)^{2}} \\[4pt]
+&amp;= \frac{2}{(4x^{2}+1)\,\arcsin x}
+   -\frac{\arctan (2x)}{\sqrt{1-x^{2}}\;(\arcsin x)^{2}} .
+\end{aligned}
+\]
+The obtained expression is exactly the right‑hand side of the given differential
+equation. Hence  
+\[
+y' = \frac{d}{dx}\!\left(\frac{\arctan (2x)}{\arcsin x}\right).
+\]
+---
+### 2.  Integrate  
+\[
+\int y'\,dx = \int \frac{d}{dx}\!\left(\frac{\arctan (2x)}{\arcsin x}\right)dx
+\quad\Longrightarrow\quad
+y = \frac{\arctan (2x)}{\arcsin x}+C,
+\]
+where \(C\) is an arbitrary constant of integration.
+---
+\[
+\boxed{\,y(x)=\frac{\displaystyle\arctan(2x)}{\displaystyle\arcsin(x)}+C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y(x)=\frac{\displaystyle\arctan(2x)}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" t="str">
         <x:v>y^{\prime}=- \frac{1}{\left(x^{2} + 1\right) \log{\left(2 x \right)}} - \frac{\operatorname{acot}{\left(x \right)}}{x \log{\left(2 x \right)}^{2}} - e^{- x} x^{3} \log{\left(e \right)} + 3 e^{- x} x^{2}</x:v>
       </x:c>
-      <x:c r="B80" t="str">
+      <x:c r="B85" t="str">
         <x:v>y=\arcctg(x) \cdot \frac{1}{\ln(2 \cdot x)}+x^{3} \cdot \frac{1}{e^{x}}+C</x:v>
       </x:c>
-      <x:c r="C80" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D80" t="str">
+      <x:c r="C85" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D85" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The differential equation is  
@@ -5573,17 +5895,17 @@
 \boxed{\,y(x)=\frac{\operatorname{acot}</x:v>
       </x:c>
     </x:row>
-    <x:row r="81">
-      <x:c r="A81" t="str">
+    <x:row r="86">
+      <x:c r="A86" t="str">
         <x:v>y^{\prime}=- \sin{\left(x \right)} \operatorname{asin}{\left(2 x \right)} + \frac{2 \cos{\left(x \right)}}{\sqrt{1 - 4 x^{2}}} + \frac{2 \cos{\left(2 x \right)}}{x^{3}} - \frac{3 \sin{\left(2 x \right)}}{x^{4}}</x:v>
       </x:c>
-      <x:c r="B81" t="str">
+      <x:c r="B86" t="str">
         <x:v>y=\cos(x) \cdot \arcsin(2 \cdot x)+\sin(2 \cdot x) \cdot \frac{1}{x^{3}}+C</x:v>
       </x:c>
-      <x:c r="C81" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D81" t="str">
+      <x:c r="C86" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D86" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -5649,17 +5971,77 @@
 \boxed{\,y(x)=\cos x\,\arcsin (2x)+\frac{\sin (2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="82">
-      <x:c r="A82" t="str">
+    <x:row r="87">
+      <x:c r="A87" t="str">
+        <x:v>y^{\prime}=- e^{- x} \operatorname{ctan}{\left(x \right)} \log{\left(e \right)} + e^{- x} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}</x:v>
+      </x:c>
+      <x:c r="B87" t="str">
+        <x:v>y=\ctg(x) \cdot \frac{1}{e^{x}}-\arcsin(2 \cdot x) \cdot \tg(2 \cdot x)+C</x:v>
+      </x:c>
+      <x:c r="C87" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D87" t="str">
+        <x:v>[REASONING]
+[REASONING]
+The given differential equation is  
+\[
+y'=- e^{- x}\,\operatorname{ctan}(x)\,\log(e)+e^{- x}\,\frac{d}{dx}\operatorname{ctan}(x).
+\]
+1. **Simplify constants and notation**  
+   \[
+   \log(e)=1,\qquad \operatorname{ctan}(x)=\cot x .
+   \]
+   Hence  
+   \[
+   y'=- e^{-x}\cot x+e^{-x}\frac{d}{dx}\cot x .
+   \]
+2. **Differentiate \(\cot x\)**  
+   \[
+   \frac{d}{dx}\cot x = -\csc^{2}x .
+   \]
+   Substituting,  
+   \[
+   y'=- e^{-x}\cot x+e^{-x}\bigl(-\csc^{2}x\bigr)
+      =-e^{-x}\bigl(\cot x+\csc^{2}x\bigr).
+   \]
+3. **Recognise a total derivative**  
+   Compute the derivative of the product \(e^{-x}\cot x\):
+   \[
+   \frac{d}{dx}\bigl(e^{-x}\cot x\bigr)
+   =(-e^{-x})\cot x+e^{-x}\frac{d}{dx}\cot x
+   =-e^{-x}\cot x+e^{-x}\bigl(-\csc^{2}x\bigr)
+   =-e^{-x}\bigl(\cot x+\csc^{2}x\bigr).
+   \]
+   This is exactly the right‑hand side of the differential equation, i.e.
+   \[
+   y'=\frac{d}{dx}\bigl(e^{-x}\cot x\bigr).
+   \]
+4. **Integrate**  
+   Since the derivative of \(e^{-x}\cot x\) equals \(y'\),
+   \[
+   y = e^{-x}\cot x + C,
+   \]
+   where \(C\) is an arbitrary constant of integration.
+[FINAL ANSWER]
+\[
+\boxed{\,y(x)=e^{-x}\cot x + C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y(x)=e^{-x}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" t="str">
         <x:v>y^{\prime}=\frac{2 x}{\sqrt{1 - 4 x^{2}}} + \operatorname{asin}{\left(2 x \right)} - \frac{1}{\left(x^{2} + 1\right) \operatorname{acos}{\left(x \right)}} + \frac{\operatorname{acot}{\left(x \right)}}{\sqrt{1 - x^{2}} \operatorname{acos}^{2}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B82" t="str">
+      <x:c r="B88" t="str">
         <x:v>y=x \cdot \arcsin(2 \cdot x)+\arcctg(x) \cdot \frac{1}{\arccos(x)}+C</x:v>
       </x:c>
-      <x:c r="C82" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D82" t="str">
+      <x:c r="C88" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D88" t="str">
         <x:v>[REASONING]
 [REASONING]
 We integrate the right–hand side term by term.
@@ -5689,17 +6071,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="83">
-      <x:c r="A83" t="str">
+    <x:row r="89">
+      <x:c r="A89" t="str">
         <x:v>y^{\prime}=- \frac{2 x}{\sqrt{1 - 4 x^{2}} \operatorname{acos}^{2}{\left(2 x \right)}} - \frac{1}{\operatorname{acos}{\left(2 x \right)}} - \frac{\operatorname{acos}{\left(2 x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{ctan}^{2}{\left(x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{ctan}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B83" t="str">
+      <x:c r="B89" t="str">
         <x:v>y=\arccos(2 \cdot x) \cdot \frac{1}{\ctg(x)}-x \cdot \frac{1}{\arccos(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C83" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D83" t="str">
+      <x:c r="C89" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D89" t="str">
         <x:v>[REASONING]
 The given differential equation is  
 \[
@@ -5730,17 +6112,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="84">
-      <x:c r="A84" t="str">
+    <x:row r="90">
+      <x:c r="A90" t="str">
         <x:v>y^{\prime}=- \frac{x^{3} \sin{\left(x \right)}}{\cos^{2}{\left(x \right)}} - \frac{3 x^{2}}{\cos{\left(x \right)}} + \left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{atan}{\left(2 x \right)} + \frac{2 \tan{\left(x \right)}}{4 x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B84" t="str">
+      <x:c r="B90" t="str">
         <x:v>y=\arctg(2 \cdot x) \cdot \tg(x)-x^{3} \cdot \frac{1}{\cos(x)}+C</x:v>
       </x:c>
-      <x:c r="C84" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D84" t="str">
+      <x:c r="C90" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D90" t="str">
         <x:v>[REASONING]
 [REASONING]
 \[
@@ -5797,17 +6179,17 @@
 \boxed{\,y(x)=\tan x\,\operatorname{atan}</x:v>
       </x:c>
     </x:row>
-    <x:row r="85">
-      <x:c r="A85" t="str">
+    <x:row r="91">
+      <x:c r="A91" t="str">
         <x:v>y^{\prime}=e^{x} \log{\left(e \right)} \operatorname{acos}{\left(2 x \right)} - \frac{2 e^{x}}{\sqrt{1 - 4 x^{2}}} - \frac{\operatorname{acos}{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{asin}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B85" t="str">
+      <x:c r="B91" t="str">
         <x:v>y=\arccos(2 \cdot x) \cdot e^{x}+\arccos(2 \cdot x) \cdot \frac{1}{\arcsin(x)}+C</x:v>
       </x:c>
-      <x:c r="C85" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D85" t="str">
+      <x:c r="C91" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D91" t="str">
         <x:v>[REASONING]
 \[
 \begin{aligned}
@@ -5834,17 +6216,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="86">
-      <x:c r="A86" t="str">
+    <x:row r="92">
+      <x:c r="A92" t="str">
         <x:v>y^{\prime}=- 2 \operatorname{ctan}{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} - \operatorname{ctan}{\left(2 x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} - \frac{2 \operatorname{acot}{\left(x \right)}}{4 x^{2} + 1} - \frac{\operatorname{acot}{\left(2 x \right)}}{x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B86" t="str">
+      <x:c r="B92" t="str">
         <x:v>y=\arcctg(2 \cdot x) \cdot \arcctg(x)-\ctg(2 \cdot x) \cdot \ctg(x)+C</x:v>
       </x:c>
-      <x:c r="C86" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D86" t="str">
+      <x:c r="C92" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D92" t="str">
         <x:v>[REASONING]
 [REASONING]
 First rewrite the given differential equation using the standard trigonometric functions  
@@ -5896,17 +6278,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="87">
-      <x:c r="A87" t="str">
+    <x:row r="93">
+      <x:c r="A93" t="str">
         <x:v>y^{\prime}=\frac{\cos{\left(x \right)}}{\operatorname{atan}{\left(2 x \right)}} - \frac{2 \sin{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{atan}^{2}{\left(2 x \right)}} - e^{- x} \log{\left(e \right)} \operatorname{asin}{\left(2 x \right)} + \frac{2 e^{- x}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B87" t="str">
+      <x:c r="B93" t="str">
         <x:v>y=\sin(x) \cdot \frac{1}{\arctg(2 \cdot x)}+\arcsin(2 \cdot x) \cdot \frac{1}{e^{x}}+C</x:v>
       </x:c>
-      <x:c r="C87" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D87" t="str">
+      <x:c r="C93" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D93" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -5970,17 +6352,17 @@
 \boxed{\,y(x)=\frac{\sin x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="88">
-      <x:c r="A88" t="str">
+    <x:row r="94">
+      <x:c r="A94" t="str">
         <x:v>y^{\prime}=\frac{2 \operatorname{acos}{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{acot}^{2}{\left(2 x \right)}} - \frac{1}{\sqrt{1 - x^{2}} \operatorname{acot}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B88" t="str">
+      <x:c r="B94" t="str">
         <x:v>y=\arccos(x) \cdot \frac{1}{\arcctg(2 \cdot x)}+\cos(2 \cdot x) \cdot x+C</x:v>
       </x:c>
-      <x:c r="C88" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D88" t="str">
+      <x:c r="C94" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D94" t="str">
         <x:v>[REASONING]
 **Reasoning**
 Let  
@@ -6032,17 +6414,17 @@
 \boxed{\,y(x)=\frac{\arccos x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="89">
-      <x:c r="A89" t="str">
+    <x:row r="95">
+      <x:c r="A95" t="str">
         <x:v>y^{\prime}=\frac{2 \sin{\left(x \right)} \cos{\left(2 x \right)}}{\sin^{2}{\left(2 x \right)}} - \frac{\cos{\left(x \right)}}{\sin{\left(2 x \right)}} - 2 e^{- 2 x} \log{\left(e \right)} \operatorname{acos}{\left(2 x \right)} - \frac{2 e^{- 2 x}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B89" t="str">
+      <x:c r="B95" t="str">
         <x:v>y=\arccos(2 \cdot x) \cdot \frac{1}{e^{2 \cdot x}}-\sin(x) \cdot \frac{1}{\sin(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C89" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D89" t="str">
+      <x:c r="C95" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D95" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is
@@ -6050,17 +6432,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="90">
-      <x:c r="A90" t="str">
+    <x:row r="96">
+      <x:c r="A96" t="str">
         <x:v>y^{\prime}=- \frac{2 e^{2 x} \log{\left(e \right)}}{\cos{\left(2 x \right)}} - \frac{2 e^{2 x} \sin{\left(2 x \right)}}{\cos^{2}{\left(2 x \right)}} - \frac{\log{\left(x \right)}}{\sqrt{1 - x^{2}}} + \frac{\operatorname{acos}{\left(x \right)}}{x}</x:v>
       </x:c>
-      <x:c r="B90" t="str">
+      <x:c r="B96" t="str">
         <x:v>y=\ln(x) \cdot \arccos(x)-e^{2 \cdot x} \cdot \frac{1}{\cos(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C90" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D90" t="str">
+      <x:c r="C96" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D96" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -6108,17 +6490,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="91">
-      <x:c r="A91" t="str">
+    <x:row r="97">
+      <x:c r="A97" t="str">
         <x:v>y^{\prime}=e^{x} x^{3} \log{\left(e \right)} + 3 e^{x} x^{2} + \left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{ctan}{\left(2 x \right)} + 2 \tan{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}</x:v>
       </x:c>
-      <x:c r="B91" t="str">
+      <x:c r="B97" t="str">
         <x:v>y=e^{x} \cdot x^{3}+\ctg(2 \cdot x) \cdot \tg(x)+C</x:v>
       </x:c>
-      <x:c r="C91" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D91" t="str">
+      <x:c r="C97" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D97" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -6182,17 +6564,17 @@
 \boxed{\,y(x)=x^{3}</x:v>
       </x:c>
     </x:row>
-    <x:row r="92">
-      <x:c r="A92" t="str">
+    <x:row r="98">
+      <x:c r="A98" t="str">
         <x:v>y^{\prime}=- 2 \cos{\left(2 x \right)} \operatorname{acos}{\left(x \right)} + \frac{2 \operatorname{atan}{\left(x \right)}}{4 x^{2} + 1} + \frac{\operatorname{atan}{\left(2 x \right)}}{x^{2} + 1} + \frac{\sin{\left(2 x \right)}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
-      <x:c r="B92" t="str">
+      <x:c r="B98" t="str">
         <x:v>y=\arctg(x) \cdot \arctg(2 \cdot x)-\arccos(x) \cdot \sin(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C92" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D92" t="str">
+      <x:c r="C98" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D98" t="str">
         <x:v>[REASONING]
 **Step‑by‑step integration**
 The differential equation is  
@@ -6270,17 +6652,17 @@
 \boxed{\,y = \operatorname{atan}</x:v>
       </x:c>
     </x:row>
-    <x:row r="93">
-      <x:c r="A93" t="str">
+    <x:row r="99">
+      <x:c r="A99" t="str">
         <x:v>y^{\prime}=\frac{1}{\sqrt{1 - x^{2}} \operatorname{asin}{\left(2 x \right)}} - \frac{2 \operatorname{asin}{\left(x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B93" t="str">
+      <x:c r="B99" t="str">
         <x:v>y=\arcsin(x) \cdot \frac{1}{\arcsin(2 \cdot x)}+e^{2 \cdot x} \cdot \ln(x)+C</x:v>
       </x:c>
-      <x:c r="C93" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D93" t="str">
+      <x:c r="C99" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D99" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -6336,17 +6718,17 @@
 \boxed{\,y(x)=\frac{\displaystyle\arcsin x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="94">
-      <x:c r="A94" t="str">
+    <x:row r="100">
+      <x:c r="A100" t="str">
         <x:v>y^{\prime}=\frac{x}{\sqrt{1 - x^{2}} \operatorname{acos}^{2}{\left(x \right)}} + \cos{\left(x \right)} \operatorname{acot}{\left(x \right)} + \frac{1}{\operatorname{acos}{\left(x \right)}} - \frac{\sin{\left(x \right)}}{x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B94" t="str">
+      <x:c r="B100" t="str">
         <x:v>y=\arcctg(x) \cdot \sin(x)+x \cdot \frac{1}{\arccos(x)}+C</x:v>
       </x:c>
-      <x:c r="C94" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D94" t="str">
+      <x:c r="C100" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D100" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -6377,17 +6759,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="95">
-      <x:c r="A95" t="str">
+    <x:row r="101">
+      <x:c r="A101" t="str">
         <x:v>y^{\prime}=\frac{2 e^{2 x} \log{\left(e \right)}}{\operatorname{asin}{\left(x \right)}} - \frac{e^{2 x}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B95" t="str">
+      <x:c r="B101" t="str">
         <x:v>y=e^{2 \cdot x} \cdot \frac{1}{\arcsin(x)}-\tg(x) \cdot \cos(x)+C</x:v>
       </x:c>
-      <x:c r="C95" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D95" t="str">
+      <x:c r="C101" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D101" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 1. **Simplify the given differential equation**
@@ -6439,17 +6821,17 @@
 \boxed{\,y = \frac{e^{2x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="96">
-      <x:c r="A96" t="str">
+    <x:row r="102">
+      <x:c r="A102" t="str">
         <x:v>y^{\prime}=- \frac{2 \operatorname{acos}{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - \frac{1}{\sqrt{1 - x^{2}} \operatorname{ctan}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B96" t="str">
+      <x:c r="B102" t="str">
         <x:v>y=\arccos(x) \cdot \frac{1}{\ctg(2 \cdot x)}+\arctg(2 \cdot x) \cdot \sin(x)+C</x:v>
       </x:c>
-      <x:c r="C96" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D96" t="str">
+      <x:c r="C102" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D102" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -6522,17 +6904,17 @@
 \boxed{\,y = \arccos (x)\,\tan (2x) + C\,}</x:v>
       </x:c>
     </x:row>
-    <x:row r="97">
-      <x:c r="A97" t="str">
+    <x:row r="103">
+      <x:c r="A103" t="str">
         <x:v>y^{\prime}=\left(\tan^{2}{\left(x \right)} + 1\right) \cos{\left(x \right)} - \left(2 \tan^{2}{\left(2 x \right)} + 2\right) \operatorname{acot}{\left(x \right)} - \sin{\left(x \right)} \tan{\left(x \right)} + \frac{\tan{\left(2 x \right)}}{x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B97" t="str">
+      <x:c r="B103" t="str">
         <x:v>y=\tg(x) \cdot \cos(x)-\arcctg(x) \cdot \tg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C97" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D97" t="str">
+      <x:c r="C103" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D103" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 \[
@@ -6589,17 +6971,100 @@
 \boxed{\,y'=\cos x-2\sec ^2(2x)\operatorname{acot}</x:v>
       </x:c>
     </x:row>
-    <x:row r="98">
-      <x:c r="A98" t="str">
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>y^{\prime}=- \frac{\operatorname{acot}{\left(x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{ctan}^{2}{\left(x \right)}} - \frac{1}{\left(x^{2} + 1\right) \operatorname{ctan}{\left(x \right)}}</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>y=\arcctg(x) \cdot \frac{1}{\ctg(x)}+\arccos(2 \cdot x) \cdot \tg(x)+C</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D104" t="str">
+        <x:v>[REASONING]
+[REASONING]
+The differential equation is  
+\[
+y'=- \frac{\operatorname{acot}{\left(x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{ctan}^{2}{\left(x \right)}}-\frac{1}{\left(x^{2}+1\right)\operatorname{ctan}{\left(x \right)}} .
+\]
+Here \(\operatorname{ctan}(x)=\cot x\) and \(\operatorname{acot}(x)=\arccot x\).
+---
+### 1.  Compute \(\dfrac{d}{dx}\cot x\)
+\[
+\frac{d}{dx}\cot x = -\csc^{2}x = -(1+\cot^{2}x).
+\]
+---
+### 2.  Substitute the derivative
+\[
+\begin{aligned}
+y' &amp;=
+-\,\frac{\arccot x\;(-\csc^{2}x)}{\cot^{2}x}
+-\frac{1}{(x^{2}+1)\cot x}\\[4pt]
+&amp;= \frac{\arccot x\,\csc^{2}x}{\cot^{2}x}
+-\frac{1}{(x^{2}+1)\cot x}.
+\end{aligned}
+\]
+Because \(\csc^{2}x = 1+\cot^{2}x\),
+\[
+\frac{\csc^{2}x}{\cot^{2}x}= \frac{1+\cot^{2}x}{\cot^{2}x}= \frac{1}{\cot^{2}x}+1
+= \tan^{2}x+1 = \sec^{2}x .
+\]
+Hence  
+\[
+y' = \arccot x\,\sec^{2}x-\frac{1}{(x^{2}+1)\cot x}.
+\]
+---
+### 3.  Recognise a total derivative  
+Recall  
+\[
+\frac{d}{dx}\tan x = \sec^{2}x ,\qquad 
+\frac{d}{dx}\arccot x = -\frac{1}{1+x^{2}} .
+\]
+Consider the product \(\arccot x\;\tan x\):
+\[
+\begin{aligned}
+\frac{d}{dx}\bigl(\arccot x\;\tan x\bigr)
+&amp;= \arccot x\;\frac{d}{dx}\tan x
+      + \tan x\;\frac{d}{dx}\arccot x \\[4pt]
+&amp;= \arccot x\;\sec^{2}x
+      -\frac{\tan x}{1+x^{2}} .
+\end{aligned}
+\]
+Since \(\tan x = \dfrac{1}{\cot x}\),
+\[
+-\frac{\tan x}{1+x^{2}} = -\frac{1}{(x^{2}+1)\cot x},
+\]
+which is exactly the second term of \(y'\). Therefore  
+\[
+y' = \frac{d}{dx}\bigl(\arccot x\;\tan x\bigr).
+\]
+---
+### 4.  Integrate
+\[
+y = \arccot x\;\tan x + C,
+\]
+where \(C\) is an arbitrary constant.
+---
+[FINAL ANSWER]
+\[
+\boxed{\,y = \arccot(x)\,\tan(x) + C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y = \arccot(x)\,\tan(x) + C\,}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str">
         <x:v>y^{\prime}=\operatorname{ctan}{\left(x \right)} \cos{\left(x \right)} + \sin{\left(x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} + \frac{\tan^{2}{\left(x \right)} + 1}{x^{3}} - \frac{3 \tan{\left(x \right)}}{x^{4}}</x:v>
       </x:c>
-      <x:c r="B98" t="str">
+      <x:c r="B105" t="str">
         <x:v>y=\sin(x) \cdot \ctg(x)+\tg(x) \cdot \frac{1}{x^{3}}+C</x:v>
       </x:c>
-      <x:c r="C98" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D98" t="str">
+      <x:c r="C105" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D105" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -6666,17 +7131,17 @@
 \boxed{\,y(x)=\cos x+\dfrac{\tan x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="99">
-      <x:c r="A99" t="str">
+    <x:row r="106">
+      <x:c r="A106" t="str">
         <x:v>y^{\prime}=2 \log{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} + \frac{2 \operatorname{acos}{\left(2 x \right)}}{4 x^{2} + 1} - \frac{2 \operatorname{atan}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}} + \frac{\operatorname{ctan}{\left(2 x \right)}}{x}</x:v>
       </x:c>
-      <x:c r="B99" t="str">
+      <x:c r="B106" t="str">
         <x:v>y=\arctg(2 \cdot x) \cdot \arccos(2 \cdot x)+\ln(x) \cdot \ctg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C99" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D99" t="str">
+      <x:c r="C106" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D106" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -6742,17 +7207,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="100">
-      <x:c r="A100" t="str">
+    <x:row r="107">
+      <x:c r="A107" t="str">
         <x:v>y^{\prime}=e^{x} \log{\left(e \right)} - \frac{\operatorname{asin}{\left(x \right)}}{x^{2} + 1} + \frac{\operatorname{acot}{\left(x \right)}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
-      <x:c r="B100" t="str">
+      <x:c r="B107" t="str">
         <x:v>y=\arcsin(x) \cdot \arcctg(x)+e^{2 \cdot x} \cdot \frac{1}{e^{x}}+C</x:v>
       </x:c>
-      <x:c r="C100" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D100" t="str">
+      <x:c r="C107" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D107" t="str">
         <x:v>[REASONING]
 **Solution**
 \[
@@ -6793,17 +7258,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="101">
-      <x:c r="A101" t="str">
+    <x:row r="108">
+      <x:c r="A108" t="str">
         <x:v>y^{\prime}=\left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{atan}{\left(x \right)} + \frac{\cos{\left(x \right)}}{\operatorname{acos}{\left(2 x \right)}} + \frac{\tan{\left(x \right)}}{x^{2} + 1} + \frac{2 \sin{\left(x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{acos}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B101" t="str">
+      <x:c r="B108" t="str">
         <x:v>y=\arctg(x) \cdot \tg(x)+\sin(x) \cdot \frac{1}{\arccos(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C101" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D101" t="str">
+      <x:c r="C108" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D108" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 \[
@@ -6873,17 +7338,17 @@
 \boxed{\,y(x)=\tan x\,\arctan x+\dfrac{\sin x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="102">
-      <x:c r="A102" t="str">
+    <x:row r="109">
+      <x:c r="A109" t="str">
         <x:v>y^{\prime}=- x \sin{\left(x \right)} + \cos{\left(x \right)} - \frac{2 \operatorname{acos}{\left(2 x \right)}}{4 x^{2} + 1} + \frac{2 \operatorname{atan}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B102" t="str">
+      <x:c r="B109" t="str">
         <x:v>y=x \cdot \cos(x)-\arccos(2 \cdot x) \cdot \arctg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C102" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D102" t="str">
+      <x:c r="C109" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D109" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The differential equation is  
@@ -6929,17 +7394,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="103">
-      <x:c r="A103" t="str">
+    <x:row r="110">
+      <x:c r="A110" t="str">
         <x:v>y^{\prime}=- \frac{1}{\left(x^{2} + 1\right) \log{\left(2 x \right)}} - \frac{\operatorname{acot}{\left(x \right)}}{x \log{\left(2 x \right)}^{2}} + \frac{2 \cos{\left(2 x \right)}}{x^{3}} - \frac{3 \sin{\left(2 x \right)}}{x^{4}}</x:v>
       </x:c>
-      <x:c r="B103" t="str">
+      <x:c r="B110" t="str">
         <x:v>y=\arcctg(x) \cdot \frac{1}{\ln(2 \cdot x)}+\sin(2 \cdot x) \cdot \frac{1}{x^{3}}+C</x:v>
       </x:c>
-      <x:c r="C103" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D103" t="str">
+      <x:c r="C110" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D110" t="str">
         <x:v>[REASONING]
 **Reasoning**
 We have to find a function \(y(x)\) whose derivative equals  
@@ -6979,17 +7444,73 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="104">
-      <x:c r="A104" t="str">
+    <x:row r="111">
+      <x:c r="A111" t="str">
+        <x:v>y^{\prime}=- \frac{1}{\sqrt{1 - x^{2}} \log{\left(x \right)}} - \frac{\operatorname{acos}{\left(x \right)}}{x \log{\left(x \right)}^{2}}</x:v>
+      </x:c>
+      <x:c r="B111" t="str">
+        <x:v>y=\arccos(x) \cdot \frac{1}{\ln(x)}-x \cdot \cos(x)+C</x:v>
+      </x:c>
+      <x:c r="C111" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D111" t="str">
+        <x:v>[REASONING]
+**Reasoning**
+We are asked to solve  
+\[
+y'=- \frac{1}{\sqrt{1 - x^{2}}\,\log x}\;-\;\frac{\arccos x}{x\,(\log x)^{2}} .
+\]
+The right–hand side suggests a derivative of a quotient because it contains a term with \(\sqrt{1-x^{2}}\) (the derivative of \(\arccos x\)) and a term with \(1/x\) (the derivative of \(\log x\)).  
+Consider the function  
+\[
+f(x)=\frac{\arccos x}{\log x}.
+\]
+Using the quotient rule \(\displaystyle \left(\frac{u}{v}\right)'=\frac{u'v-u v'}{v^{2}}\) with  
+\[
+u(x)=\arccos x,\qquad v(x)=\log x,
+\]
+we have  
+\[
+u'(x)= -\frac{1}{\sqrt{1-x^{2}}},\qquad 
+v'(x)=\frac{1}{x}.
+\]
+Hence  
+\[
+\begin{aligned}
+f'(x) &amp;=\frac{u'v-u v'}{v^{2}}\\[4pt]
+&amp;=\frac{\displaystyle\left(-\frac{1}{\sqrt{1-x^{2}}}\right)\log x
+      -\arccos x\left(\frac{1}{x}\right)}
+      {(\log x)^{2}}\\[6pt]
+&amp;= -\frac{1}{\sqrt{1-x^{2}}\,\log x}
+   -\frac{\arccos x}{x(\log x)^{2}} .
+\end{aligned}
+\]
+The expression obtained for \(f'(x)\) is exactly the right‑hand side of the differential equation. Therefore  
+\[
+y' = f'(x) \quad\Longrightarrow\quad y = f(x) + C,
+\]
+where \(C\) is an arbitrary constant.
+---
+**Final Answer**
+\[
+\boxed{\,y(x)=\frac{\arccos x}{\log x}+C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y(x)=\frac{\arccos x}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" t="str">
         <x:v>y^{\prime}=\cos{\left(x \right)} \operatorname{acot}{\left(x \right)} + \frac{2 \operatorname{asin}{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{acot}^{2}{\left(2 x \right)}} - \frac{\sin{\left(x \right)}}{x^{2} + 1} + \frac{1}{\sqrt{1 - x^{2}} \operatorname{acot}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B104" t="str">
+      <x:c r="B112" t="str">
         <x:v>y=\arcctg(x) \cdot \sin(x)+\arcsin(x) \cdot \frac{1}{\arcctg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C104" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D104" t="str">
+      <x:c r="C112" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D112" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The differential equation is  
@@ -7063,17 +7584,17 @@
 \boxed{\,y = \sin(x)\,\operatorname{acot}</x:v>
       </x:c>
     </x:row>
-    <x:row r="105">
-      <x:c r="A105" t="str">
+    <x:row r="113">
+      <x:c r="A113" t="str">
         <x:v>y^{\prime}=2 \operatorname{acos}{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} - \frac{2 \operatorname{ctan}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}} + 2 e^{- 2 x} \log{\left(e \right)} \cos{\left(x \right)} + e^{- 2 x} \sin{\left(x \right)}</x:v>
       </x:c>
-      <x:c r="B105" t="str">
+      <x:c r="B113" t="str">
         <x:v>y=\ctg(2 \cdot x) \cdot \arccos(2 \cdot x)-\cos(x) \cdot \frac{1}{e^{2 \cdot x}}+C</x:v>
       </x:c>
-      <x:c r="C105" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D105" t="str">
+      <x:c r="C113" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D113" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -7109,17 +7630,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="106">
-      <x:c r="A106" t="str">
+    <x:row r="114">
+      <x:c r="A114" t="str">
         <x:v>y^{\prime}=\frac{2 \tan^{2}{\left(2 x \right)} + 2}{\cos{\left(x \right)}} + \frac{\sin{\left(x \right)} \tan{\left(2 x \right)}}{\cos^{2}{\left(x \right)}} - \frac{\frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{asin}{\left(2 x \right)}} + \frac{2 \operatorname{ctan}{\left(x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B106" t="str">
+      <x:c r="B114" t="str">
         <x:v>y=\tg(2 \cdot x) \cdot \frac{1}{\cos(x)}-\ctg(x) \cdot \frac{1}{\arcsin(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C106" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D106" t="str">
+      <x:c r="C114" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D114" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 \[
@@ -7165,17 +7686,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="107">
-      <x:c r="A107" t="str">
+    <x:row r="115">
+      <x:c r="A115" t="str">
         <x:v>y^{\prime}=- e^{2 x} \left(2 \tan^{2}{\left(2 x \right)} + 2\right) - 2 e^{2 x} \log{\left(e \right)} \tan{\left(2 x \right)} - \frac{x^{3}}{x^{2} + 1} + 3 x^{2} \operatorname{acot}{\left(x \right)}</x:v>
       </x:c>
-      <x:c r="B107" t="str">
+      <x:c r="B115" t="str">
         <x:v>y=x^{3} \cdot \arcctg(x)-\tg(2 \cdot x) \cdot e^{2 \cdot x}+C</x:v>
       </x:c>
-      <x:c r="C107" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D107" t="str">
+      <x:c r="C115" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D115" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -7258,17 +7779,17 @@
 \boxed{\,y(x)=x^{3}</x:v>
       </x:c>
     </x:row>
-    <x:row r="108">
-      <x:c r="A108" t="str">
+    <x:row r="116">
+      <x:c r="A116" t="str">
         <x:v>y^{\prime}=- \frac{2 \cos{\left(2 x \right)} \operatorname{asin}{\left(2 x \right)}}{\sin^{2}{\left(2 x \right)}} + \frac{2}{\sqrt{1 - 4 x^{2}} \sin{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B108" t="str">
+      <x:c r="B116" t="str">
         <x:v>y=\arcsin(2 \cdot x) \cdot \frac{1}{\sin(2 \cdot x)}+\arcsin(x) \cdot x^{2}+C</x:v>
       </x:c>
-      <x:c r="C108" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D108" t="str">
+      <x:c r="C116" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D116" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -7323,17 +7844,17 @@
 \boxed{\,y = \frac{\arcsin (2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="109">
-      <x:c r="A109" t="str">
+    <x:row r="117">
+      <x:c r="A117" t="str">
         <x:v>y^{\prime}=2 e^{2 x} \log{\left(e \right)} \operatorname{acot}{\left(2 x \right)} - \frac{2 e^{2 x}}{4 x^{2} + 1} - \frac{2 x^{3}}{\sqrt{1 - 4 x^{2}}} - 3 x^{2} \operatorname{asin}{\left(2 x \right)}</x:v>
       </x:c>
-      <x:c r="B109" t="str">
+      <x:c r="B117" t="str">
         <x:v>y=e^{2 \cdot x} \cdot \arcctg(2 \cdot x)-\arcsin(2 \cdot x) \cdot x^{3}+C</x:v>
       </x:c>
-      <x:c r="C109" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D109" t="str">
+      <x:c r="C117" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D117" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -7417,17 +7938,17 @@
 \boxed{\,y = e^{2x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="110">
-      <x:c r="A110" t="str">
+    <x:row r="118">
+      <x:c r="A118" t="str">
         <x:v>y^{\prime}=- \frac{2 \operatorname{asin}{\left(2 x \right)}}{\left(4 x^{2} + 1\right) \operatorname{atan}^{2}{\left(2 x \right)}} + \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{atan}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B110" t="str">
+      <x:c r="B118" t="str">
         <x:v>y=\arcsin(2 \cdot x) \cdot \frac{1}{\arctg(2 \cdot x)}+\arccos(2 \cdot x) \cdot \tg(x)+C</x:v>
       </x:c>
-      <x:c r="C110" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D110" t="str">
+      <x:c r="C118" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D118" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -7483,17 +8004,86 @@
 \boxed{\,y(x)=\frac{\displaystyle\arcsin (2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="111">
-      <x:c r="A111" t="str">
+    <x:row r="119">
+      <x:c r="A119" t="str">
+        <x:v>y^{\prime}=- \frac{\operatorname{acos}{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{asin}{\left(x \right)}}</x:v>
+      </x:c>
+      <x:c r="B119" t="str">
+        <x:v>y=\arccos(2 \cdot x) \cdot \frac{1}{\arcsin(x)}+x^{2} \cdot \ln(x)+C</x:v>
+      </x:c>
+      <x:c r="C119" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D119" t="str">
+        <x:v>[REASONING]
+**Solution**
+\[
+y'=- \frac{\arccos (2x)}{\sqrt{1-x^{2}}\;\bigl(\arcsin x\bigr)^{2}}
+      -\frac{2}{\sqrt{1-4x^{2}}\;\arcsin x},
+\qquad |x|&lt;\tfrac12 .
+\]
+---
+### 1.  Look for a function whose derivative gives the right‑hand side  
+Consider the quotient  
+\[
+u(x)=\frac{\arccos (2x)}{\arcsin x}.
+\]
+If \(y'=u'\), then \(y=u+C\).  
+Compute \(u'\) with the quotient rule.
+---
+### 2.  Derivatives of the numerator and denominator  
+\[
+\begin{aligned}
+A(x)&amp;=\arccos (2x), &amp;
+A'(x)&amp;=-\frac{2}{\sqrt{1-(2x)^{2}}}
+      =-\frac{2}{\sqrt{1-4x^{2}}},\\[4pt]
+B(x)&amp;=\arcsin x, &amp;
+B'(x)&amp;=\frac{1}{\sqrt{1-x^{2}}}.
+\end{aligned}
+\]
+---
+### 3.  Apply the quotient rule  
+\[
+u'=\frac{A'B-AB'}{B^{2}}.
+\]
+Insert the expressions found above:
+\[
+\begin{aligned}
+u'&amp;=\frac{\displaystyle
+\Bigl(-\frac{2}{\sqrt{1-4x^{2}}}\Bigr)\,\arcsin x
+      -\arccos (2x)\,\Bigl(\frac{1}{\sqrt{1-x^{2}}}\Bigr)}
+          {\bigl(\arcsin x\bigr)^{2}} \\[6pt]
+   &amp;= -\frac{2}{\sqrt{1-4x^{2}}\;\arcsin x}
+      -\frac{\arccos (2x)}{\sqrt{1-x^{2}}\;(\arcsin x)^{2}} .
+\end{aligned}
+\]
+The right‑hand side is exactly the given expression for \(y'\).
+Hence  
+\[
+y' = u' \quad\Longrightarrow\quad y = u + C.
+\]
+---
+### 4.  General solution  
+\[
+\boxed{\,y(x)=\frac{\arccos (2x)}{\arcsin x}+C\,},
+\qquad |x|&lt;\tfrac12 .
+\]
+The constant \(C\) is arbitrary, and the domain is the intersection of the domains of \(\arccos(2x)\) and \(\arcsin x\), i.e. \(|x|&lt;\tfrac12\).
+[FINAL ANSWER]
+\boxed{\,y(x)=\frac{\arccos (2x)}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="str">
         <x:v>y^{\prime}=- e^{- x} \log{\left(e \right)} \operatorname{atan}{\left(2 x \right)} + \frac{2 e^{- x}}{4 x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B111" t="str">
+      <x:c r="B120" t="str">
         <x:v>y=\arctg(2 \cdot x) \cdot \frac{1}{e^{x}}-e^{2 \cdot x} \cdot \sin(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C111" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D111" t="str">
+      <x:c r="C120" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D120" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -7562,17 +8152,17 @@
 \boxed{\,y = e^{-x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="112">
-      <x:c r="A112" t="str">
+    <x:row r="121">
+      <x:c r="A121" t="str">
         <x:v>y^{\prime}=- \frac{2 \sin{\left(2 x \right)}}{\log{\left(x \right)}} - \frac{\cos{\left(2 x \right)}}{x \log{\left(x \right)}^{2}}</x:v>
       </x:c>
-      <x:c r="B112" t="str">
+      <x:c r="B121" t="str">
         <x:v>y=\cos(2 \cdot x) \cdot \frac{1}{\ln(x)}-\tg(x) \cdot \arccos(x)+C</x:v>
       </x:c>
-      <x:c r="C112" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D112" t="str">
+      <x:c r="C121" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D121" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 The differential equation is  
@@ -7612,17 +8202,17 @@
 \boxed{\,y(x)=\frac{\cos (2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="113">
-      <x:c r="A113" t="str">
+    <x:row r="122">
+      <x:c r="A122" t="str">
         <x:v>y^{\prime}=\frac{\left(- \tan^{2}{\left(x \right)} - 1\right) \operatorname{acos}{\left(x \right)}}{\tan^{2}{\left(x \right)}} - \frac{2 \operatorname{asin}{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{atan}^{2}{\left(2 x \right)}} + \frac{1}{\sqrt{1 - x^{2}} \operatorname{atan}{\left(2 x \right)}} - \frac{1}{\sqrt{1 - x^{2}} \tan{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B113" t="str">
+      <x:c r="B122" t="str">
         <x:v>y=\arcsin(x) \cdot \frac{1}{\arctg(2 \cdot x)}+\arccos(x) \cdot \frac{1}{\tg(x)}+C</x:v>
       </x:c>
-      <x:c r="C113" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D113" t="str">
+      <x:c r="C122" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D122" t="str">
         <x:v>[REASONING]
 \[
 y'=\frac{(-\tan ^2x-1)\,\arccos x}{\tan ^2x}-\frac{2\arcsin x}{(4x^{2}+1)\,\arctan ^2(2x)}+\frac{1}{\sqrt{1-x^{2}}\,\arctan (2x)}-\frac{1}{\sqrt{1-x^{2}}\,\tan x}
@@ -7651,17 +8241,96 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="114">
-      <x:c r="A114" t="str">
+    <x:row r="123">
+      <x:c r="A123" t="str">
+        <x:v>y^{\prime}=- \frac{\operatorname{acos}{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{asin}{\left(x \right)}}</x:v>
+      </x:c>
+      <x:c r="B123" t="str">
+        <x:v>y=\arccos(2 \cdot x) \cdot \frac{1}{\arcsin(x)}-\arcsin(x) \cdot \ctg(x)+C</x:v>
+      </x:c>
+      <x:c r="C123" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D123" t="str">
+        <x:v>[REASONING]
+**[REASONING]**
+The differential equation is  
+\[
+y'=- \frac{\arccos (2x)}{\sqrt{1-x^{2}}\;\bigl(\arcsin x\bigr)^{2}}
+      -\frac{2}{\sqrt{1-4x^{2}}\;\arcsin x}.
+\]
+The right–hand side suggests the derivative of a quotient that contains  
+\(\arccos(2x)\) in the numerator and \(\arcsin x\) in the denominator.  
+Consider the function  
+\[
+f(x)=\frac{\arccos (2x)}{\arcsin x}.
+\]
+Compute its derivative using the quotient rule.
+---
+**Step 1 – Derivatives of the elementary functions**
+\[
+\frac{d}{dx}\arccos (2x)= -\frac{2}{\sqrt{1-(2x)^{2}}}= -\frac{2}{\sqrt{1-4x^{2}}},
+\]
+\[
+\frac{d}{dx}\arcsin x = \frac{1}{\sqrt{1-x^{2}}}.
+\]
+---
+**Step 2 – Apply the quotient rule**
+\[
+\begin{aligned}
+f'(x) &amp;=
+\frac{\displaystyle\bigl(\frac{d}{dx}\arccos (2x)\bigr)\,\arcsin x
+      -\arccos (2x)\,\displaystyle\frac{d}{dx}\arcsin x}
+     {\bigl(\arcsin x\bigr)^{2}} \\[4pt]
+&amp;=
+\frac{\displaystyle\left(-\frac{2}{\sqrt{1-4x^{2}}}\right)\arcsin x
+      -\arccos (2x)\,\frac{1}{\sqrt{1-x^{2}}}}
+     {\bigl(\arcsin x\bigr)^{2}} .
+\end{aligned}
+\]
+---
+**Step 3 – Separate the terms**
+\[
+\begin{aligned}
+f'(x) &amp;=
+-\frac{2\,\arcsin x}{\sqrt{1-4x^{2}}\;(\arcsin x)^{2}}
+      -\frac{\arccos (2x)}{\sqrt{1-x^{2}}\;(\arcsin x)^{2}} \\[4pt]
+&amp;=
+-\frac{2}{\sqrt{1-4x^{2}}\;\arcsin x}
+   -\frac{\arccos (2x)}{\sqrt{1-x^{2}}\;(\arcsin x)^{2}} .
+\end{aligned}
+\]
+The expression obtained for \(f'(x)\) is exactly the right‑hand side of the given differential equation. Hence  
+\[
+y' = f'(x).
+\]
+---
+**Step 4 – Integrate**
+Since the derivatives are equal, the antiderivatives differ only by an additive constant:
+\[
+y = f(x) + C = \frac{\arccos (2x)}{\arcsin x}+C,
+\]
+where \(C\) is an arbitrary constant.
+---
+**[FINAL ANSWER]**
+\[
+\boxed{\,y(x)=\frac{\arccos (2x)}{\arcsin x}+C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y(x)=\frac{\arccos (2x)}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" t="str">
         <x:v>y^{\prime}=- \frac{x^{2}}{\sqrt{1 - x^{2}}} - 2 x \operatorname{asin}{\left(x \right)} + \left(\tan^{2}{\left(x \right)} + 1\right) \cos{\left(x \right)} - \sin{\left(x \right)} \tan{\left(x \right)}</x:v>
       </x:c>
-      <x:c r="B114" t="str">
+      <x:c r="B124" t="str">
         <x:v>y=\tg(x) \cdot \cos(x)-\arcsin(x) \cdot x^{2}+C</x:v>
       </x:c>
-      <x:c r="C114" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D114" t="str">
+      <x:c r="C124" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D124" t="str">
         <x:v>[REASONING]
 **Solution**
 The differential equation is  
@@ -7719,17 +8388,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="115">
-      <x:c r="A115" t="str">
+    <x:row r="125">
+      <x:c r="A125" t="str">
         <x:v>y^{\prime}=e^{x} \log{\left(e \right)} \operatorname{acos}{\left(2 x \right)} - \frac{2 e^{x}}{\sqrt{1 - 4 x^{2}}} + \frac{2 \log{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{atan}^{2}{\left(2 x \right)}} - \frac{1}{x \operatorname{atan}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B115" t="str">
+      <x:c r="B125" t="str">
         <x:v>y=\arccos(2 \cdot x) \cdot e^{x}-\ln(x) \cdot \frac{1}{\arctg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C115" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D115" t="str">
+      <x:c r="C125" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D125" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -7789,17 +8458,17 @@
 \boxed{\,y = e^{x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="116">
-      <x:c r="A116" t="str">
+    <x:row r="126">
+      <x:c r="A126" t="str">
         <x:v>y^{\prime}=\frac{2 \operatorname{atan}{\left(x \right)}}{4 x^{2} + 1} + \frac{\operatorname{asin}{\left(x \right)}}{\left(x^{2} + 1\right) \operatorname{atan}^{2}{\left(x \right)}} + \frac{\operatorname{atan}{\left(2 x \right)}}{x^{2} + 1} - \frac{1}{\sqrt{1 - x^{2}} \operatorname{atan}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B116" t="str">
+      <x:c r="B126" t="str">
         <x:v>y=\arctg(x) \cdot \arctg(2 \cdot x)-\arcsin(x) \cdot \frac{1}{\arctg(x)}+C</x:v>
       </x:c>
-      <x:c r="C116" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D116" t="str">
+      <x:c r="C126" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D126" t="str">
         <x:v>[REASONING]
 \[
 \begin{aligned}
@@ -7829,17 +8498,17 @@
 \boxed{\,y=\arctan(x)\,\arctan(2x)-\dfrac{\arcsin(x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="117">
-      <x:c r="A117" t="str">
+    <x:row r="127">
+      <x:c r="A127" t="str">
         <x:v>y^{\prime}=x^{3} \left(\tan^{2}{\left(x \right)} + 1\right) - 2 x^{2} \sin{\left(2 x \right)} + 3 x^{2} \tan{\left(x \right)} + 2 x \cos{\left(2 x \right)}</x:v>
       </x:c>
-      <x:c r="B117" t="str">
+      <x:c r="B127" t="str">
         <x:v>y=x^{2} \cdot \cos(2 \cdot x)+x^{3} \cdot \tg(x)+C</x:v>
       </x:c>
-      <x:c r="C117" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D117" t="str">
+      <x:c r="C127" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D127" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 The differential equation is  
@@ -7904,17 +8573,17 @@
 \boxed{\,y = x^{3}</x:v>
       </x:c>
     </x:row>
-    <x:row r="118">
-      <x:c r="A118" t="str">
+    <x:row r="128">
+      <x:c r="A128" t="str">
         <x:v>y^{\prime}=e^{x} \log{\left(e \right)} \operatorname{acot}{\left(x \right)} - \frac{e^{x}}{x^{2} + 1} + \frac{\cos{\left(x \right)}}{\operatorname{acot}{\left(2 x \right)}} + \frac{2 \sin{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{acot}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B118" t="str">
+      <x:c r="B128" t="str">
         <x:v>y=\arcctg(x) \cdot e^{x}+\sin(x) \cdot \frac{1}{\arcctg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C118" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D118" t="str">
+      <x:c r="C128" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D128" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 \[
@@ -7980,17 +8649,17 @@
 \boxed{\,y = e^{x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="119">
-      <x:c r="A119" t="str">
+    <x:row r="129">
+      <x:c r="A129" t="str">
         <x:v>y^{\prime}=- \operatorname{ctan}{\left(x \right)} \sin{\left(x \right)} + \cos{\left(x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} - \frac{2 \cos{\left(2 x \right)}}{\operatorname{atan}{\left(x \right)}} + \frac{\sin{\left(2 x \right)}}{\left(x^{2} + 1\right) \operatorname{atan}^{2}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B119" t="str">
+      <x:c r="B129" t="str">
         <x:v>y=\cos(x) \cdot \ctg(x)-\sin(2 \cdot x) \cdot \frac{1}{\arctg(x)}+C</x:v>
       </x:c>
-      <x:c r="C119" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D119" t="str">
+      <x:c r="C129" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D129" t="str">
         <x:v>[REASONING]
 [REASONING]
 First rewrite the given differential equation using the usual notation  
@@ -8059,17 +8728,17 @@
 \boxed{\,y=\cos x\,\cot x-\dfrac{\sin(2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="120">
-      <x:c r="A120" t="str">
+    <x:row r="130">
+      <x:c r="A130" t="str">
         <x:v>y^{\prime}=\left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{acos}{\left(2 x \right)} + \frac{\cos{\left(x \right)}}{\log{\left(x \right)}} - \frac{2 \tan{\left(x \right)}}{\sqrt{1 - 4 x^{2}}} - \frac{\sin{\left(x \right)}}{x \log{\left(x \right)}^{2}}</x:v>
       </x:c>
-      <x:c r="B120" t="str">
+      <x:c r="B130" t="str">
         <x:v>y=\arccos(2 \cdot x) \cdot \tg(x)+\sin(x) \cdot \frac{1}{\ln(x)}+C</x:v>
       </x:c>
-      <x:c r="C120" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D120" t="str">
+      <x:c r="C130" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D130" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 The differential equation is  
@@ -8151,17 +8820,78 @@
 \boxed{\,y = \tan(x)\,\arccos(2x) + \frac{\sin(x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="121">
-      <x:c r="A121" t="str">
+    <x:row r="131">
+      <x:c r="A131" t="str">
+        <x:v>y^{\prime}=- \frac{1}{\sqrt{1 - x^{2}} \log{\left(x \right)}} - \frac{\operatorname{acos}{\left(x \right)}}{x \log{\left(x \right)}^{2}}</x:v>
+      </x:c>
+      <x:c r="B131" t="str">
+        <x:v>y=\arccos(x) \cdot \frac{1}{\ln(x)}-x^{3} \cdot \tg(2 \cdot x)+C</x:v>
+      </x:c>
+      <x:c r="C131" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D131" t="str">
+        <x:v>[REASONING]
+**Step‑by‑step solution**
+The differential equation is  
+\[
+y'=- \frac{1}{\sqrt{1-x^{2}}\;\ln x}\;-\;\frac{\arccos (x)}{x\;(\ln x)^{2}} .
+\]
+We look for a function whose derivative gives the right‑hand side.  
+Consider  
+\[
+f(x)=\frac{\arccos (x)}{\ln x}.
+\]
+---
+### 1. Differentiate \(f(x)\)
+Use the quotient rule:
+\[
+f'(x)=\frac{(\arccos x)'\,\ln x-\arccos x\;(\ln x)'}{(\ln x)^{2}} .
+\]
+Compute the two derivatives:
+* \((\arccos x)' = -\dfrac{1}{\sqrt{1-x^{2}}}\),
+* \((\ln x)' = \dfrac{1}{x}\).
+Insert them:
+\[
+\begin{aligned}
+f'(x)&amp;=\frac{\displaystyle\left(-\frac{1}{\sqrt{1-x^{2}}}\right)\ln x
+      -\arccos x\left(\frac{1}{x}\right)}{(\ln x)^{2}}\\[4pt]
+     &amp;=\frac{-\displaystyle\frac{\ln x}{\sqrt{1-x^{2}}}
+            -\displaystyle\frac{\arccos x}{x}}{(\ln x)^{2}}\\[4pt]
+     &amp;=-\frac{1}{\sqrt{1-x^{2}}\;\ln x}
+       -\frac{\arccos x}{x\;(\ln x)^{2}} .
+\end{aligned}
+\]
+The derivative \(f'(x)\) is exactly the right‑hand side of the given differential equation.
+---
+### 2. Identify the antiderivative
+Since \(y' = f'(x)\), an antiderivative of the right‑hand side is \(f(x)\) itself:
+\[
+y = f(x) + C = \frac{\arccos (x)}{\ln x}+C,
+\]
+where \(C\) is an arbitrary constant of integration.
+---
+### 3. Domain considerations (optional)
+For real‑valued functions we need \(x&gt;0\) (so \(\ln x\) is defined) and \(|x|\le 1\) (so \(\arccos x\) is real). Also \(x\neq 1\) because \(\ln 1 =0\). These restrictions are understood from the original equation.
+---
+\[
+\boxed{\,y=\dfrac{\arccos (x)}{\ln x}+C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y=\dfrac{\arccos (x)}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" t="str">
         <x:v>y^{\prime}=- \frac{2 \log{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{atan}^{2}{\left(2 x \right)}} + \frac{1}{x \operatorname{atan}{\left(2 x \right)}} + e^{- x} \log{\left(e \right)} \operatorname{asin}{\left(2 x \right)} - \frac{2 e^{- x}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B121" t="str">
+      <x:c r="B132" t="str">
         <x:v>y=\ln(x) \cdot \frac{1}{\arctg(2 \cdot x)}-\arcsin(2 \cdot x) \cdot \frac{1}{e^{x}}+C</x:v>
       </x:c>
-      <x:c r="C121" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D121" t="str">
+      <x:c r="C132" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D132" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The given differential equation is  
@@ -8214,17 +8944,82 @@
 \boxed{\,y(x)=\frac{\ln x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="122">
-      <x:c r="A122" t="str">
+    <x:row r="133">
+      <x:c r="A133" t="str">
+        <x:v>y^{\prime}=\frac{2}{\left(4 x^{2} + 1\right) \operatorname{asin}{\left(x \right)}} - \frac{\operatorname{atan}{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}}</x:v>
+      </x:c>
+      <x:c r="B133" t="str">
+        <x:v>y=\arctg(2 \cdot x) \cdot \frac{1}{\arcsin(x)}+\ctg(2 \cdot x) \cdot x^{3}+C</x:v>
+      </x:c>
+      <x:c r="C133" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D133" t="str">
+        <x:v>[REASONING]
+**Step‑by‑step solution**
+The differential equation is  
+\[
+y'=\frac{2}{\bigl(4x^{2}+1\bigr)\,\arcsin x}
+      -\frac{\arctan (2x)}{\sqrt{1-x^{2}}\;\bigl(\arcsin x\bigr)^{2}} .
+\]
+---
+### 1.  Look for a function whose derivative gives the right‑hand side  
+Consider  
+\[
+F(x)=\frac{\arctan (2x)}{\arcsin x}.
+\]
+Compute its derivative using the quotient rule:
+\[
+F'(x)=\frac{(\arctan (2x))'\,\arcsin x-\arctan (2x)\,(\arcsin x)'}{(\arcsin x)^{2}} .
+\]
+---
+### 2.  Derivatives of the numerator and denominator  
+\[
+(\arctan (2x))'=\frac{2}{1+(2x)^{2}}=\frac{2}{4x^{2}+1},
+\qquad
+(\arcsin x)'=\frac{1}{\sqrt{1-x^{2}}}.
+\]
+---
+### 3.  Substitute into the quotient rule  
+\[
+\begin{aligned}
+F'(x)&amp;=\frac{\displaystyle \frac{2}{4x^{2}+1}\,\arcsin x
+          -\arctan (2x)\,\frac{1}{\sqrt{1-x^{2}}}}
+          {(\arcsin x)^{2}} \\[4pt]
+     &amp;=\frac{2}{(4x^{2}+1)\,\arcsin x}
+       -\frac{\arctan (2x)}{\sqrt{1-x^{2}}\;(\arcsin x)^{2}} .
+\end{aligned}
+\]
+The expression obtained for \(F'(x)\) is exactly the right‑hand side of the given differential equation. Hence  
+\[
+y' = F'(x).
+\]
+---
+### 4.  Integrate  
+Since the derivative of \(F(x)\) equals \(y'\),
+\[
+y = F(x) + C = \frac{\arctan (2x)}{\arcsin x}+C,
+\]
+where \(C\) is an arbitrary constant of integration.
+---
+\[
+\boxed{\,y(x)=\frac{\displaystyle \arctan (2x)}{\displaystyle \arcsin x}+C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y(x)=\frac{\displaystyle \arctan (2x)}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" t="str">
         <x:v>y^{\prime}=- \frac{x^{2}}{\sqrt{1 - x^{2}} \operatorname{acos}^{2}{\left(x \right)}} - \frac{2 x}{\operatorname{acos}{\left(x \right)}} + \frac{\tan^{2}{\left(x \right)} + 1}{\sin{\left(x \right)}} - \frac{\cos{\left(x \right)} \tan{\left(x \right)}}{\sin^{2}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B122" t="str">
+      <x:c r="B134" t="str">
         <x:v>y=\tg(x) \cdot \frac{1}{\sin(x)}-x^{2} \cdot \frac{1}{\arccos(x)}+C</x:v>
       </x:c>
-      <x:c r="C122" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D122" t="str">
+      <x:c r="C134" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D134" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -8271,17 +9066,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="123">
-      <x:c r="A123" t="str">
+    <x:row r="135">
+      <x:c r="A135" t="str">
         <x:v>y^{\prime}=- \frac{2 \operatorname{ctan}{\left(x \right)} \cos{\left(2 x \right)}}{\sin^{2}{\left(2 x \right)}} + \frac{\frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\sin{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B123" t="str">
+      <x:c r="B135" t="str">
         <x:v>y=\ctg(x) \cdot \frac{1}{\sin(2 \cdot x)}+\sin(2 \cdot x) \cdot x+C</x:v>
       </x:c>
-      <x:c r="C123" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D123" t="str">
+      <x:c r="C135" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D135" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -8350,17 +9145,17 @@
 \boxed{\,y=\frac{1}</x:v>
       </x:c>
     </x:row>
-    <x:row r="124">
-      <x:c r="A124" t="str">
+    <x:row r="136">
+      <x:c r="A136" t="str">
         <x:v>y^{\prime}=\cos{\left(x \right)} \operatorname{acot}{\left(x \right)} - \frac{\sin{\left(x \right)}}{x^{2} + 1} - \frac{2 \log{\left(x \right)}}{\sqrt{1 - 4 x^{2}}} + \frac{\operatorname{acos}{\left(2 x \right)}}{x}</x:v>
       </x:c>
-      <x:c r="B124" t="str">
+      <x:c r="B136" t="str">
         <x:v>y=\ln(x) \cdot \arccos(2 \cdot x)+\sin(x) \cdot \arcctg(x)+C</x:v>
       </x:c>
-      <x:c r="C124" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D124" t="str">
+      <x:c r="C136" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D136" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The differential equation  
@@ -8408,17 +9203,17 @@
 \boxed{\sin x\,\operatorname{acot}</x:v>
       </x:c>
     </x:row>
-    <x:row r="125">
-      <x:c r="A125" t="str">
+    <x:row r="137">
+      <x:c r="A137" t="str">
         <x:v>y^{\prime}=\frac{\sin{\left(x \right)} \operatorname{acot}{\left(2 x \right)}}{\cos^{2}{\left(x \right)}} - \frac{2}{\left(4 x^{2} + 1\right) \cos{\left(x \right)}} - \frac{2}{x^{3}}</x:v>
       </x:c>
-      <x:c r="B125" t="str">
+      <x:c r="B137" t="str">
         <x:v>y=\arcctg(2 \cdot x) \cdot \frac{1}{\cos(x)}+x \cdot \frac{1}{x^{3}}+C</x:v>
       </x:c>
-      <x:c r="C125" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D125" t="str">
+      <x:c r="C137" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D137" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 \[
@@ -8476,17 +9271,17 @@
 \boxed{\,y(x)=\frac{\operatorname{acot}</x:v>
       </x:c>
     </x:row>
-    <x:row r="126">
-      <x:c r="A126" t="str">
+    <x:row r="138">
+      <x:c r="A138" t="str">
         <x:v>y^{\prime}=\operatorname{acot}{\left(2 x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} - \frac{2 \operatorname{ctan}{\left(x \right)}}{4 x^{2} + 1} + \frac{2 \operatorname{atan}{\left(x \right)}}{4 x^{2} + 1} - \frac{\operatorname{acot}{\left(2 x \right)}}{x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B126" t="str">
+      <x:c r="B138" t="str">
         <x:v>y=\arcctg(2 \cdot x) \cdot \ctg(x)-\arctg(x) \cdot \arcctg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C126" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D126" t="str">
+      <x:c r="C138" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D138" t="str">
         <x:v>[REASONING]
 [REASONING]  
 The differential equation is  
@@ -8548,17 +9343,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="127">
-      <x:c r="A127" t="str">
+    <x:row r="139">
+      <x:c r="A139" t="str">
         <x:v>y^{\prime}=2 \operatorname{ctan}{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} + \operatorname{ctan}{\left(2 x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} + e^{- x} \operatorname{ctan}{\left(x \right)} \log{\left(e \right)} - e^{- x} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}</x:v>
       </x:c>
-      <x:c r="B127" t="str">
+      <x:c r="B139" t="str">
         <x:v>y=\ctg(x) \cdot \ctg(2 \cdot x)-\ctg(x) \cdot \frac{1}{e^{x}}+C</x:v>
       </x:c>
-      <x:c r="C127" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D127" t="str">
+      <x:c r="C139" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D139" t="str">
         <x:v>[REASONING]
 **Step 1.  Rewrite the right‑hand side using elementary derivatives**
 \[
@@ -8598,17 +9393,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="128">
-      <x:c r="A128" t="str">
+    <x:row r="140">
+      <x:c r="A140" t="str">
         <x:v>y^{\prime}=\frac{\left(- \tan^{2}{\left(x \right)} - 1\right) \log{\left(x \right)}}{\tan^{2}{\left(x \right)}} + \frac{1}{x \tan{\left(x \right)}} - e^{- x} \log{\left(e \right)} \operatorname{atan}{\left(2 x \right)} + \frac{2 e^{- x}}{4 x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B128" t="str">
+      <x:c r="B140" t="str">
         <x:v>y=\ln(x) \cdot \frac{1}{\tg(x)}+\arctg(2 \cdot x) \cdot \frac{1}{e^{x}}+C</x:v>
       </x:c>
-      <x:c r="C128" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D128" t="str">
+      <x:c r="C140" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D140" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 \[
@@ -8669,17 +9464,17 @@
 \boxed{\,y=\cot x\,\ln x+e^{-x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="129">
-      <x:c r="A129" t="str">
+    <x:row r="141">
+      <x:c r="A141" t="str">
         <x:v>y^{\prime}=- \frac{2 x^{3}}{\sqrt{1 - 4 x^{2}}} + 3 x^{2} \operatorname{acos}{\left(2 x \right)} + 2 \cos{\left(2 x \right)} \operatorname{acos}{\left(x \right)} - \frac{\sin{\left(2 x \right)}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
-      <x:c r="B129" t="str">
+      <x:c r="B141" t="str">
         <x:v>y=\arccos(x) \cdot \sin(2 \cdot x)+x^{3} \cdot \arccos(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C129" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D129" t="str">
+      <x:c r="C141" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D141" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -8744,17 +9539,17 @@
 \boxed{\,y = x^{3}</x:v>
       </x:c>
     </x:row>
-    <x:row r="130">
-      <x:c r="A130" t="str">
+    <x:row r="142">
+      <x:c r="A142" t="str">
         <x:v>y^{\prime}=2 \operatorname{atan}{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} + \frac{\operatorname{ctan}{\left(2 x \right)}}{x^{2} + 1} - \frac{\log{\left(x \right)}}{x} - \frac{\log{\left(2 x \right)}}{x}</x:v>
       </x:c>
-      <x:c r="B130" t="str">
+      <x:c r="B142" t="str">
         <x:v>y=\ctg(2 \cdot x) \cdot \arctg(x)-\ln(x) \cdot \ln(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C130" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D130" t="str">
+      <x:c r="C142" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D142" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -8816,17 +9611,17 @@
 \boxed{\,y(x)=\arctan (x)\,\cot (2x)-(\log x)^{2}</x:v>
       </x:c>
     </x:row>
-    <x:row r="131">
-      <x:c r="A131" t="str">
+    <x:row r="143">
+      <x:c r="A143" t="str">
         <x:v>y^{\prime}=\left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{atan}{\left(x \right)} + \left(2 \tan^{2}{\left(2 x \right)} + 2\right) \operatorname{acot}{\left(2 x \right)} - \frac{2 \tan{\left(2 x \right)}}{4 x^{2} + 1} + \frac{\tan{\left(x \right)}}{x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B131" t="str">
+      <x:c r="B143" t="str">
         <x:v>y=\tg(2 \cdot x) \cdot \arcctg(2 \cdot x)+\arctg(x) \cdot \tg(x)+C</x:v>
       </x:c>
-      <x:c r="C131" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D131" t="str">
+      <x:c r="C143" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D143" t="str">
         <x:v>[REASONING]
 **Solution**
 \[
@@ -8882,17 +9677,17 @@
 \boxed{\,y=\tan x\,\arctan x+\tan (2x)\,\operatorname{arccot}</x:v>
       </x:c>
     </x:row>
-    <x:row r="132">
-      <x:c r="A132" t="str">
+    <x:row r="144">
+      <x:c r="A144" t="str">
         <x:v>y^{\prime}=\sin{\left(x \right)} \cos{\left(2 x \right)} + 2 \sin{\left(2 x \right)} \cos{\left(x \right)} + \operatorname{asin}{\left(x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} + \frac{\operatorname{ctan}{\left(x \right)}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
-      <x:c r="B132" t="str">
+      <x:c r="B144" t="str">
         <x:v>y=\arcsin(x) \cdot \ctg(x)-\cos(2 \cdot x) \cdot \cos(x)+C</x:v>
       </x:c>
-      <x:c r="C132" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D132" t="str">
+      <x:c r="C144" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D144" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 \[
@@ -8950,17 +9745,87 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="133">
-      <x:c r="A133" t="str">
+    <x:row r="145">
+      <x:c r="A145" t="str">
+        <x:v>y^{\prime}=\frac{2 \sin{\left(2 x \right)} \operatorname{asin}{\left(2 x \right)}}{\cos^{2}{\left(2 x \right)}} + \frac{2}{\sqrt{1 - 4 x^{2}} \cos{\left(2 x \right)}}</x:v>
+      </x:c>
+      <x:c r="B145" t="str">
+        <x:v>y=\arcsin(2 \cdot x) \cdot \frac{1}{\cos(2 \cdot x)}+\ctg(2 \cdot x) \cdot x^{2}+C</x:v>
+      </x:c>
+      <x:c r="C145" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D145" t="str">
+        <x:v>[REASONING]
+[REASONING]
+The differential equation is  
+\[
+y'=\frac{2\sin(2x)\,\arcsin(2x)}{\cos^{2}(2x)}+\frac{2}{\sqrt{1-4x^{2}}\;\cos(2x)} .
+\]
+---
+### 1.  Recognize derivatives inside the terms  
+*Derivative of \(\sec(2x)\):*  
+\[
+\frac{d}{dx}\sec(2x)=2\sec(2x)\tan(2x)=\frac{2\sin(2x)}{\cos^{2}(2x)} .
+\]
+Hence  
+\[
+\frac{2\sin(2x)}{\cos^{2}(2x)} = \bigl(\sec(2x)\bigr)' .
+\]
+*Derivative of \(\arcsin(2x)\):*  
+\[
+\frac{d}{dx}\arcsin(2x)=\frac{2}{\sqrt{1-(2x)^{2}}}= \frac{2}{\sqrt{1-4x^{2}}}.
+\]
+Thus  
+\[
+\frac{2}{\sqrt{1-4x^{2}}}= \bigl(\arcsin(2x)\bigr)' .
+\]
+---
+### 2.  Rewrite the right‑hand side using these derivatives  
+\[
+\begin{aligned}
+y' &amp;=\arcsin(2x)\,\frac{2\sin(2x)}{\cos^{2}(2x)}+\frac{2}{\sqrt{1-4x^{2}}}\,\frac{1}{\cos(2x)}\\[4pt]
+   &amp;=\arcsin(2x)\,(\sec(2x))' + (\arcsin(2x))'\,\sec(2x).
+\end{aligned}
+\]
+---
+### 3.  Identify the product rule  
+The expression obtained is exactly the derivative of the product \(\arcsin(2x)\,\sec(2x)\):
+\[
+\frac{d}{dx}\bigl[\arcsin(2x)\,\sec(2x)\bigr]
+      =\arcsin(2x)\,(\sec(2x))' + (\arcsin(2x))'\,\sec(2x).
+\]
+Therefore  
+\[
+y' = \frac{d}{dx}\bigl[\arcsin(2x)\,\sec(2x)\bigr].
+\]
+---
+### 4.  Integrate  
+Integrating both sides with respect to \(x\),
+\[
+y = \arcsin(2x)\,\sec(2x) + C,
+\]
+where \(C\) is an arbitrary constant.
+---
+[FINAL ANSWER]  
+\[
+\boxed{\,y = \sec(2x)\,\arcsin(2x) + C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y = \sec(2x)\,\arcsin(2x) + C\,}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" t="str">
         <x:v>y^{\prime}=- \frac{e^{x} \log{\left(e \right)}}{\operatorname{asin}{\left(x \right)}} + \frac{e^{x}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}} + \left(2 \tan^{2}{\left(2 x \right)} + 2\right) \log{\left(x \right)} + \frac{\tan{\left(2 x \right)}}{x}</x:v>
       </x:c>
-      <x:c r="B133" t="str">
+      <x:c r="B146" t="str">
         <x:v>y=\ln(x) \cdot \tg(2 \cdot x)-e^{x} \cdot \frac{1}{\arcsin(x)}+C</x:v>
       </x:c>
-      <x:c r="C133" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D133" t="str">
+      <x:c r="C146" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D146" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 \[
@@ -9030,17 +9895,17 @@
 \boxed{\,y(x)= -\frac{e^{x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="134">
-      <x:c r="A134" t="str">
+    <x:row r="147">
+      <x:c r="A147" t="str">
         <x:v>y^{\prime}=2 e^{2 x} \log{\left(e \right)} \log{\left(x \right)} + \frac{e^{2 x}}{x} + \frac{2 \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{asin}{\left(x \right)}} - \frac{\operatorname{ctan}{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B134" t="str">
+      <x:c r="B147" t="str">
         <x:v>y=\ln(x) \cdot e^{2 \cdot x}+\ctg(2 \cdot x) \cdot \frac{1}{\arcsin(x)}+C</x:v>
       </x:c>
-      <x:c r="C134" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D134" t="str">
+      <x:c r="C147" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D147" t="str">
         <x:v>[REASONING]
 \[
 \begin{aligned}
@@ -9101,17 +9966,17 @@
 \boxed{\,y(x)=e^{2x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="135">
-      <x:c r="A135" t="str">
+    <x:row r="148">
+      <x:c r="A148" t="str">
         <x:v>y^{\prime}=2 x - \frac{\sin{\left(x \right)} \operatorname{acot}{\left(2 x \right)}}{\cos^{2}{\left(x \right)}} + \frac{2}{\left(4 x^{2} + 1\right) \cos{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B135" t="str">
+      <x:c r="B148" t="str">
         <x:v>y=x^{3} \cdot \frac{1}{x}-\arcctg(2 \cdot x) \cdot \frac{1}{\cos(x)}+C</x:v>
       </x:c>
-      <x:c r="C135" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D135" t="str">
+      <x:c r="C148" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D148" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -9202,17 +10067,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="136">
-      <x:c r="A136" t="str">
+    <x:row r="149">
+      <x:c r="A149" t="str">
         <x:v>y^{\prime}=x \left(\tan^{2}{\left(x \right)} + 1\right) - \frac{x}{\sqrt{1 - x^{2}}} + \tan{\left(x \right)} - \operatorname{asin}{\left(x \right)}</x:v>
       </x:c>
-      <x:c r="B136" t="str">
+      <x:c r="B149" t="str">
         <x:v>y=x \cdot \tg(x)-\arcsin(x) \cdot x+C</x:v>
       </x:c>
-      <x:c r="C136" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D136" t="str">
+      <x:c r="C149" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D149" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 The differential equation is  
@@ -9289,17 +10154,17 @@
 \boxed{\,y = x\bigl(\tan x - \arcsin x\bigr) + C\,}</x:v>
       </x:c>
     </x:row>
-    <x:row r="137">
-      <x:c r="A137" t="str">
+    <x:row r="150">
+      <x:c r="A150" t="str">
         <x:v>y^{\prime}=\operatorname{atan}{\left(x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} + \frac{\operatorname{ctan}{\left(x \right)}}{x^{2} + 1} - \frac{\cos{\left(x \right)}}{x^{2}} + \frac{2 \sin{\left(x \right)}}{x^{3}}</x:v>
       </x:c>
-      <x:c r="B137" t="str">
+      <x:c r="B150" t="str">
         <x:v>y=\arctg(x) \cdot \ctg(x)-\sin(x) \cdot \frac{1}{x^{2}}+C</x:v>
       </x:c>
-      <x:c r="C137" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D137" t="str">
+      <x:c r="C150" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D150" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -9375,17 +10240,17 @@
 \boxed{\,y = \arctan(x)\,\cot(x) - \dfrac{\sin x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="138">
-      <x:c r="A138" t="str">
+    <x:row r="151">
+      <x:c r="A151" t="str">
         <x:v>y^{\prime}=- \frac{\sin{\left(x \right)}}{x^{2}} - \frac{2 \cos{\left(x \right)}}{x^{3}}</x:v>
       </x:c>
-      <x:c r="B138" t="str">
+      <x:c r="B151" t="str">
         <x:v>y=\cos(x) \cdot \frac{1}{x^{2}}+\tg(x) \cdot \arcsin(x)+C</x:v>
       </x:c>
-      <x:c r="C138" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D138" t="str">
+      <x:c r="C151" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D151" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -9433,17 +10298,17 @@
 \boxed{\,y(x)=\dfrac{\cos x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="139">
-      <x:c r="A139" t="str">
+    <x:row r="152">
+      <x:c r="A152" t="str">
         <x:v>y^{\prime}=e^{x} \log{\left(e \right)} \log{\left(2 x \right)} + \frac{e^{x}}{x} + x^{3} \left(2 \tan^{2}{\left(2 x \right)} + 2\right) + 3 x^{2} \tan{\left(2 x \right)}</x:v>
       </x:c>
-      <x:c r="B139" t="str">
+      <x:c r="B152" t="str">
         <x:v>y=\ln(2 \cdot x) \cdot e^{x}+x^{3} \cdot \tg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C139" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D139" t="str">
+      <x:c r="C152" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D152" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -9506,17 +10371,17 @@
 \boxed{\,y(x)=e^{x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="140">
-      <x:c r="A140" t="str">
+    <x:row r="153">
+      <x:c r="A153" t="str">
         <x:v>y^{\prime}=\frac{\left(- 2 \tan^{2}{\left(2 x \right)} - 2\right) \operatorname{acos}{\left(2 x \right)}}{\tan^{2}{\left(2 x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \tan{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B140" t="str">
+      <x:c r="B153" t="str">
         <x:v>y=\arccos(2 \cdot x) \cdot \frac{1}{\tg(2 \cdot x)}-\cos(2 \cdot x) \cdot \ctg(x)+C</x:v>
       </x:c>
-      <x:c r="C140" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D140" t="str">
+      <x:c r="C153" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D153" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 \[
@@ -9590,17 +10455,17 @@
 \boxed{\,y(x)=\arccos (2x)\,\cot (2x)+C\,}</x:v>
       </x:c>
     </x:row>
-    <x:row r="141">
-      <x:c r="A141" t="str">
+    <x:row r="154">
+      <x:c r="A154" t="str">
         <x:v>y^{\prime}=e^{x} \log{\left(e \right)} \operatorname{acot}{\left(x \right)} - \frac{e^{x}}{x^{2} + 1} - \sin{\left(x \right)} \operatorname{acos}{\left(x \right)} - \frac{\cos{\left(x \right)}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
-      <x:c r="B141" t="str">
+      <x:c r="B154" t="str">
         <x:v>y=\arcctg(x) \cdot e^{x}+\cos(x) \cdot \arccos(x)+C</x:v>
       </x:c>
-      <x:c r="C141" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D141" t="str">
+      <x:c r="C154" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D154" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The differential equation is  
@@ -9654,17 +10519,17 @@
 \boxed{\,y(x)=e^{x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="142">
-      <x:c r="A142" t="str">
+    <x:row r="155">
+      <x:c r="A155" t="str">
         <x:v>y^{\prime}=- \frac{2 x^{3}}{\sqrt{1 - 4 x^{2}}} + 3 x^{2} \operatorname{acos}{\left(2 x \right)} + \operatorname{acot}{\left(2 x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} - \frac{2 \operatorname{ctan}{\left(x \right)}}{4 x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B142" t="str">
+      <x:c r="B155" t="str">
         <x:v>y=\arccos(2 \cdot x) \cdot x^{3}+\ctg(x) \cdot \arcctg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C142" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D142" t="str">
+      <x:c r="C155" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D155" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The given differential equation is  
@@ -9709,17 +10574,17 @@
 \boxed{\,y = x^{3}</x:v>
       </x:c>
     </x:row>
-    <x:row r="143">
-      <x:c r="A143" t="str">
+    <x:row r="156">
+      <x:c r="A156" t="str">
         <x:v>y^{\prime}=2 \operatorname{asin}{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} + \frac{2 \operatorname{ctan}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}} - 2 e^{- 2 x} \operatorname{ctan}{\left(x \right)} \log{\left(e \right)} + e^{- 2 x} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}</x:v>
       </x:c>
-      <x:c r="B143" t="str">
+      <x:c r="B156" t="str">
         <x:v>y=\ctg(2 \cdot x) \cdot \arcsin(2 \cdot x)+\ctg(x) \cdot \frac{1}{e^{2 \cdot x}}+C</x:v>
       </x:c>
-      <x:c r="C143" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D143" t="str">
+      <x:c r="C156" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D156" t="str">
         <x:v>[REASONING]
 \[
 \begin{aligned}
@@ -9761,17 +10626,17 @@
 \boxed{\,y=\arcsin(2x)\,\cot(2x)+e^{-2x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="144">
-      <x:c r="A144" t="str">
+    <x:row r="157">
+      <x:c r="A157" t="str">
         <x:v>y^{\prime}=- 2 \operatorname{acos}{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} + \operatorname{acot}{\left(x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} - \frac{\operatorname{ctan}{\left(x \right)}}{x^{2} + 1} + \frac{2 \operatorname{ctan}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B144" t="str">
+      <x:c r="B157" t="str">
         <x:v>y=\ctg(x) \cdot \arcctg(x)-\ctg(2 \cdot x) \cdot \arccos(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C144" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D144" t="str">
+      <x:c r="C157" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D157" t="str">
         <x:v>[REASONING]
 **Reasoning**
 First rewrite the right–hand side using the usual trigonometric and inverse‑trigonometric functions.
@@ -9841,17 +10706,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="145">
-      <x:c r="A145" t="str">
+    <x:row r="158">
+      <x:c r="A158" t="str">
         <x:v>y^{\prime}=- 2 e^{- 2 x} \log{\left(e \right)} \operatorname{acos}{\left(x \right)} - \frac{e^{- 2 x}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
-      <x:c r="B145" t="str">
+      <x:c r="B158" t="str">
         <x:v>y=\arccos(x) \cdot \frac{1}{e^{2 \cdot x}}-\tg(x) \cdot \cos(x)+C</x:v>
       </x:c>
-      <x:c r="C145" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D145" t="str">
+      <x:c r="C158" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D158" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -9898,17 +10763,17 @@
 \boxed{\,y = e^{-2x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="146">
-      <x:c r="A146" t="str">
+    <x:row r="159">
+      <x:c r="A159" t="str">
         <x:v>y^{\prime}=\frac{\sin{\left(x \right)} \sin{\left(2 x \right)}}{\cos^{2}{\left(x \right)}} + \frac{2 \cos{\left(2 x \right)}}{\cos{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B146" t="str">
+      <x:c r="B159" t="str">
         <x:v>y=\sin(2 \cdot x) \cdot \frac{1}{\cos(x)}-\cos(x) \cdot e^{x}+C</x:v>
       </x:c>
-      <x:c r="C146" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D146" t="str">
+      <x:c r="C159" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D159" t="str">
         <x:v>[REASONING]
 **[REASONING]**  
 The differential equation is  
@@ -9966,17 +10831,17 @@
 \boxed{\,y = 2\sin x + C\,}</x:v>
       </x:c>
     </x:row>
-    <x:row r="147">
-      <x:c r="A147" t="str">
+    <x:row r="160">
+      <x:c r="A160" t="str">
         <x:v>y^{\prime}=\frac{2}{\left(4 x^{2} + 1\right) \operatorname{asin}{\left(x \right)}} + \frac{\operatorname{acos}{\left(2 x \right)}}{x^{2} + 1} + \frac{\operatorname{acot}{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}} - \frac{2 \operatorname{atan}{\left(x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B147" t="str">
+      <x:c r="B160" t="str">
         <x:v>y=\arccos(2 \cdot x) \cdot \arctg(x)-\arcctg(2 \cdot x) \cdot \frac{1}{\arcsin(x)}+C</x:v>
       </x:c>
-      <x:c r="C147" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D147" t="str">
+      <x:c r="C160" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D160" t="str">
         <x:v>[REASONING]
 **Step‑by‑step integration**
 The differential equation is  
@@ -10033,17 +10898,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="148">
-      <x:c r="A148" t="str">
+    <x:row r="161">
+      <x:c r="A161" t="str">
         <x:v>y^{\prime}=e^{- x} \operatorname{ctan}{\left(x \right)} \log{\left(e \right)} - e^{- x} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} - 2 e^{- 2 x} x^{3} \log{\left(e \right)} + 3 e^{- 2 x} x^{2}</x:v>
       </x:c>
-      <x:c r="B148" t="str">
+      <x:c r="B161" t="str">
         <x:v>y=x^{3} \cdot \frac{1}{e^{2 \cdot x}}-\ctg(x) \cdot \frac{1}{e^{x}}+C</x:v>
       </x:c>
-      <x:c r="C148" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D148" t="str">
+      <x:c r="C161" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D161" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -10107,17 +10972,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="149">
-      <x:c r="A149" t="str">
+    <x:row r="162">
+      <x:c r="A162" t="str">
         <x:v>y^{\prime}=- \frac{\sin{\left(x \right)}}{\operatorname{acot}{\left(x \right)}} + \frac{\cos{\left(x \right)}}{\left(x^{2} + 1\right) \operatorname{acot}^{2}{\left(x \right)}} - 2 e^{- 2 x} x^{3} \log{\left(e \right)} + 3 e^{- 2 x} x^{2}</x:v>
       </x:c>
-      <x:c r="B149" t="str">
+      <x:c r="B162" t="str">
         <x:v>y=x^{3} \cdot \frac{1}{e^{2 \cdot x}}+\cos(x) \cdot \frac{1}{\arcctg(x)}+C</x:v>
       </x:c>
-      <x:c r="C149" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D149" t="str">
+      <x:c r="C162" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D162" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 \[
@@ -10176,17 +11041,17 @@
 \boxed{\,y(x)=\dfrac{\cos x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="150">
-      <x:c r="A150" t="str">
+    <x:row r="163">
+      <x:c r="A163" t="str">
         <x:v>y^{\prime}=\frac{\cos{\left(x \right)}}{\operatorname{acos}{\left(2 x \right)}} + \frac{2 \sin{\left(x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{acos}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B150" t="str">
+      <x:c r="B163" t="str">
         <x:v>y=\sin(x) \cdot \frac{1}{\arccos(2 \cdot x)}-\tg(2 \cdot x) \cdot x^{3}+C</x:v>
       </x:c>
-      <x:c r="C150" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D150" t="str">
+      <x:c r="C163" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D163" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 The differential equation is  
@@ -10248,17 +11113,17 @@
 \boxed{\,y = \dfrac{\sin x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="151">
-      <x:c r="A151" t="str">
+    <x:row r="164">
+      <x:c r="A164" t="str">
         <x:v>y^{\prime}=\frac{\log{\left(2 x \right)}}{x^{2} + 1} + \frac{\operatorname{atan}{\left(x \right)}}{x} - e^{- x} \left(2 \tan^{2}{\left(2 x \right)} + 2\right) + e^{- x} \log{\left(e \right)} \tan{\left(2 x \right)}</x:v>
       </x:c>
-      <x:c r="B151" t="str">
+      <x:c r="B164" t="str">
         <x:v>y=\arctg(x) \cdot \ln(2 \cdot x)-\tg(2 \cdot x) \cdot \frac{1}{e^{x}}+C</x:v>
       </x:c>
-      <x:c r="C151" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D151" t="str">
+      <x:c r="C164" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D164" t="str">
         <x:v>[REASONING]
 **Reasoning**
 \[
@@ -10312,17 +11177,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="152">
-      <x:c r="A152" t="str">
+    <x:row r="165">
+      <x:c r="A165" t="str">
         <x:v>y^{\prime}=e^{x} \left(\tan^{2}{\left(x \right)} + 1\right) + e^{x} \log{\left(e \right)} \tan{\left(x \right)} + \frac{2}{\left(4 x^{2} + 1\right) \log{\left(2 x \right)}} - \frac{\operatorname{atan}{\left(2 x \right)}}{x \log{\left(2 x \right)}^{2}}</x:v>
       </x:c>
-      <x:c r="B152" t="str">
+      <x:c r="B165" t="str">
         <x:v>y=e^{x} \cdot \tg(x)+\arctg(2 \cdot x) \cdot \frac{1}{\ln(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C152" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D152" t="str">
+      <x:c r="C165" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D165" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 The differential equation is  
@@ -10391,17 +11256,17 @@
 \boxed{\,y = e^{x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="153">
-      <x:c r="A153" t="str">
+    <x:row r="166">
+      <x:c r="A166" t="str">
         <x:v>y^{\prime}=x \cos{\left(x \right)} + \sin{\left(x \right)} - 2 e^{- 2 x} \log{\left(e \right)} \cos{\left(x \right)} - e^{- 2 x} \sin{\left(x \right)}</x:v>
       </x:c>
-      <x:c r="B153" t="str">
+      <x:c r="B166" t="str">
         <x:v>y=\sin(x) \cdot x+\cos(x) \cdot \frac{1}{e^{2 \cdot x}}+C</x:v>
       </x:c>
-      <x:c r="C153" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D153" t="str">
+      <x:c r="C166" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D166" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -10470,17 +11335,17 @@
 \boxed{\,y = x\sin x + e^{-2x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="154">
-      <x:c r="A154" t="str">
+    <x:row r="167">
+      <x:c r="A167" t="str">
         <x:v>y^{\prime}=\frac{2 \cos{\left(2 x \right)}}{\log{\left(x \right)}} - \frac{\sin{\left(2 x \right)}}{x \log{\left(x \right)}^{2}}</x:v>
       </x:c>
-      <x:c r="B154" t="str">
+      <x:c r="B167" t="str">
         <x:v>y=\sin(2 \cdot x) \cdot \frac{1}{\ln(x)}+\tg(2 \cdot x) \cdot \tg(x)+C</x:v>
       </x:c>
-      <x:c r="C154" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D154" t="str">
+      <x:c r="C167" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D167" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -10530,17 +11395,17 @@
 \boxed{\,y(x)=\frac{\sin (2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="155">
-      <x:c r="A155" t="str">
+    <x:row r="168">
+      <x:c r="A168" t="str">
         <x:v>y^{\prime}=- \frac{2}{\left(4 x^{2} + 1\right) \log{\left(2 x \right)}} - \frac{\operatorname{acot}{\left(2 x \right)}}{x \log{\left(2 x \right)}^{2}}</x:v>
       </x:c>
-      <x:c r="B155" t="str">
+      <x:c r="B168" t="str">
         <x:v>y=\arcctg(2 \cdot x) \cdot \frac{1}{\ln(2 \cdot x)}+\tg(x) \cdot \cos(x)+C</x:v>
       </x:c>
-      <x:c r="C155" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D155" t="str">
+      <x:c r="C168" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D168" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -10595,17 +11460,17 @@
 \boxed{\,y(x)=\frac{\operatorname{acot}</x:v>
       </x:c>
     </x:row>
-    <x:row r="156">
-      <x:c r="A156" t="str">
+    <x:row r="169">
+      <x:c r="A169" t="str">
         <x:v>y^{\prime}=- \frac{2 \operatorname{acos}{\left(2 x \right)}}{4 x^{2} + 1} - \frac{\operatorname{asin}{\left(2 x \right)}}{\sqrt{1 - x^{2}}} + \frac{2 \operatorname{acos}{\left(x \right)}}{\sqrt{1 - 4 x^{2}}} - \frac{2 \operatorname{acot}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B156" t="str">
+      <x:c r="B169" t="str">
         <x:v>y=\arccos(2 \cdot x) \cdot \arcctg(2 \cdot x)+\arccos(x) \cdot \arcsin(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C156" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D156" t="str">
+      <x:c r="C169" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D169" t="str">
         <x:v>[REASONING]
 [REASONING]
 The right–hand side can be recognized as the derivative of a sum of two products.
@@ -10640,17 +11505,96 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="157">
-      <x:c r="A157" t="str">
+    <x:row r="170">
+      <x:c r="A170" t="str">
+        <x:v>y^{\prime}=\frac{e^{x} \left(- 2 \tan^{2}{\left(2 x \right)} - 2\right)}{\tan^{2}{\left(2 x \right)}} + \frac{e^{x} \log{\left(e \right)}}{\tan{\left(2 x \right)}}</x:v>
+      </x:c>
+      <x:c r="B170" t="str">
+        <x:v>y=e^{x} \cdot \frac{1}{\tg(2 \cdot x)}+\arcsin(x) \cdot \ln(x)+C</x:v>
+      </x:c>
+      <x:c r="C170" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D170" t="str">
+        <x:v>[REASONING]
+**Step 1 – Simplify the right‑hand side**
+\[
+y'=\frac{e^{x}\bigl(-2\tan^{2}(2x)-2\bigr)}{\tan^{2}(2x)}+\frac{e^{x}\log(e)}{\tan(2x)}
+\]
+Since \(\log(e)=1\),
+\[
+y' = e^{x}\Bigl[\frac{-2(\tan^{2}(2x)+1)}{\tan^{2}(2x)}+\frac{1}{\tan(2x)}\Bigr].
+\]
+Use \(\tan^{2}\theta+1=\sec^{2}\theta\) and \(\displaystyle\frac{\sec^{2}\theta}{\tan^{2}\theta}= \csc^{2}\theta\):
+\[
+\frac{-2(\tan^{2}(2x)+1)}{\tan^{2}(2x)} = -2\csc^{2}(2x),\qquad
+\frac{1}{\tan(2x)} = \cot(2x).
+\]
+Hence  
+\[
+\boxed{y' = e^{x}\bigl[-2\csc^{2}(2x)+\cot(2x)\bigr]}.
+\]
+---
+**Step 2 – Look for a factor \(e^{x}\)**  
+Write \(y\) as \(y=e^{x}f(x)\). Then  
+\[
+y' = e^{x}f + e^{x}f' = e^{x}\bigl(f+f'\bigr).
+\]
+Comparing with the expression for \(y'\),
+\[
+f'+f = -2\csc^{2}(2x)+\cot(2x).\tag{1}
+\]
+---
+**Step 3 – Solve the linear ODE for \(f\)**  
+Observe that  
+\[
+\frac{d}{dx}\cot(2x) = -2\csc^{2}(2x).
+\]
+Thus  
+\[
+-2\csc^{2}(2x)+\cot(2x)=\frac{d}{dx}\cot(2x)+\cot(2x).
+\]
+Therefore a particular solution of (1) is  
+\[
+f_{p}(x)=\cot(2x),
+\]
+because \(f_{p}'+f_{p}= (\cot(2x))'+\cot(2x)= -2\csc^{2}(2x)+\cot(2x)\).
+The homogeneous equation \(f'+f=0\) gives  
+\[
+f_{h}(x)=C e^{-x},
+\]
+with constant \(C\).
+Hence  
+\[
+f(x)=\cot(2x)+C e^{-x}.
+\]
+---
+**Step 4 – Obtain \(y\)**  
+\[
+y = e^{x}f(x)=e^{x}\bigl[\cot(2x)+C e^{-x}\bigr]
+      = e^{x}\cot(2x)+C.
+\]
+---
+**Final solution**
+\[
+\boxed{\,y(x)=e^{x}\cot(2x)+C\,}
+\] 
+where \(C\) is an arbitrary constant.
+[FINAL ANSWER]
+\boxed{\,y(x)=e^{x}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" t="str">
         <x:v>y^{\prime}=3 x^{2} + 2 \operatorname{ctan}{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} + \operatorname{ctan}{\left(2 x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}</x:v>
       </x:c>
-      <x:c r="B157" t="str">
+      <x:c r="B171" t="str">
         <x:v>y=x \cdot x^{2}+\ctg(x) \cdot \ctg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C157" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D157" t="str">
+      <x:c r="C171" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D171" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The differential equation is  
@@ -10706,17 +11650,17 @@
 \boxed{\,y(x)=x^{3}</x:v>
       </x:c>
     </x:row>
-    <x:row r="158">
-      <x:c r="A158" t="str">
+    <x:row r="172">
+      <x:c r="A172" t="str">
         <x:v>y^{\prime}=- \frac{1}{x^{3} \sqrt{1 - x^{2}}} - \frac{3 \operatorname{acos}{\left(x \right)}}{x^{4}}</x:v>
       </x:c>
-      <x:c r="B158" t="str">
+      <x:c r="B172" t="str">
         <x:v>y=\arccos(x) \cdot \frac{1}{x^{3}}-x^{2} \cdot \tg(x)+C</x:v>
       </x:c>
-      <x:c r="C158" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D158" t="str">
+      <x:c r="C172" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D172" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -10761,17 +11705,17 @@
 \boxed{\,y = \frac{\arccos (x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="159">
-      <x:c r="A159" t="str">
+    <x:row r="173">
+      <x:c r="A173" t="str">
         <x:v>y^{\prime}=- \frac{\sin{\left(x \right)}}{\cos{\left(2 x \right)}} + \frac{2 \sin{\left(2 x \right)} \cos{\left(x \right)}}{\cos^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B159" t="str">
+      <x:c r="B173" t="str">
         <x:v>y=\cos(x) \cdot \frac{1}{\cos(2 \cdot x)}+\arcsin(x) \cdot x^{2}+C</x:v>
       </x:c>
-      <x:c r="C159" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D159" t="str">
+      <x:c r="C173" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D173" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -10787,17 +11731,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="160">
-      <x:c r="A160" t="str">
+    <x:row r="174">
+      <x:c r="A174" t="str">
         <x:v>y^{\prime}=- 2 \sin{\left(2 x \right)} \operatorname{asin}{\left(x \right)} + \cos{\left(x \right)} \operatorname{acot}{\left(x \right)} - \frac{\sin{\left(x \right)}}{x^{2} + 1} + \frac{\cos{\left(2 x \right)}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
-      <x:c r="B160" t="str">
+      <x:c r="B174" t="str">
         <x:v>y=\arcsin(x) \cdot \cos(2 \cdot x)+\arcctg(x) \cdot \sin(x)+C</x:v>
       </x:c>
-      <x:c r="C160" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D160" t="str">
+      <x:c r="C174" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D174" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -10874,17 +11818,17 @@
 \boxed{\,y = \sin(x)\,\operatorname{acot}</x:v>
       </x:c>
     </x:row>
-    <x:row r="161">
-      <x:c r="A161" t="str">
+    <x:row r="175">
+      <x:c r="A175" t="str">
         <x:v>y^{\prime}=\frac{2 x^{3} \cos{\left(2 x \right)}}{\sin^{2}{\left(2 x \right)}} - \frac{3 x^{2}}{\sin{\left(2 x \right)}} + \frac{2}{\left(4 x^{2} + 1\right) \operatorname{acot}{\left(x \right)}} + \frac{\operatorname{atan}{\left(2 x \right)}}{\left(x^{2} + 1\right) \operatorname{acot}^{2}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B161" t="str">
+      <x:c r="B175" t="str">
         <x:v>y=\arctg(2 \cdot x) \cdot \frac{1}{\arcctg(x)}-x^{3} \cdot \frac{1}{\sin(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C161" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D161" t="str">
+      <x:c r="C175" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D175" t="str">
         <x:v>[REASONING]
 **Step 1 – Separate the right‑hand side**
 \[
@@ -10944,17 +11888,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="162">
-      <x:c r="A162" t="str">
+    <x:row r="176">
+      <x:c r="A176" t="str">
         <x:v>y^{\prime}=\frac{\sin{\left(x \right)} \sin{\left(2 x \right)}}{\cos^{2}{\left(x \right)}} + \cos{\left(x \right)} \operatorname{acos}{\left(2 x \right)} + \frac{2 \cos{\left(2 x \right)}}{\cos{\left(x \right)}} - \frac{2 \sin{\left(x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B162" t="str">
+      <x:c r="B176" t="str">
         <x:v>y=\arccos(2 \cdot x) \cdot \sin(x)+\sin(2 \cdot x) \cdot \frac{1}{\cos(x)}+C</x:v>
       </x:c>
-      <x:c r="C162" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D162" t="str">
+      <x:c r="C176" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D176" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -11002,17 +11946,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="163">
-      <x:c r="A163" t="str">
+    <x:row r="177">
+      <x:c r="A177" t="str">
         <x:v>y^{\prime}=e^{- x} x^{3} \log{\left(e \right)} - 3 e^{- x} x^{2} - e^{- x} \log{\left(e \right)} \operatorname{asin}{\left(2 x \right)} + \frac{2 e^{- x}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B163" t="str">
+      <x:c r="B177" t="str">
         <x:v>y=\arcsin(2 \cdot x) \cdot \frac{1}{e^{x}}-x^{3} \cdot \frac{1}{e^{x}}+C</x:v>
       </x:c>
-      <x:c r="C163" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D163" t="str">
+      <x:c r="C177" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D177" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -11068,17 +12012,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="164">
-      <x:c r="A164" t="str">
+    <x:row r="178">
+      <x:c r="A178" t="str">
         <x:v>y^{\prime}=\frac{\left(- \tan^{2}{\left(x \right)} - 1\right) \operatorname{acos}{\left(x \right)}}{\tan^{2}{\left(x \right)}} - \frac{\sin{\left(x \right)}}{\operatorname{atan}{\left(2 x \right)}} - \frac{2 \cos{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{atan}^{2}{\left(2 x \right)}} - \frac{1}{\sqrt{1 - x^{2}} \tan{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B164" t="str">
+      <x:c r="B178" t="str">
         <x:v>y=\arccos(x) \cdot \frac{1}{\tg(x)}+\cos(x) \cdot \frac{1}{\arctg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C164" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D164" t="str">
+      <x:c r="C178" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D178" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -11150,17 +12094,17 @@
 \boxed{\,y(x)=\frac{\displaystyle\arccos x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="165">
-      <x:c r="A165" t="str">
+    <x:row r="179">
+      <x:c r="A179" t="str">
         <x:v>y^{\prime}=\frac{\tan^{2}{\left(x \right)} + 1}{\operatorname{acot}{\left(2 x \right)}} + \frac{2 \tan{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{acot}^{2}{\left(2 x \right)}} - \frac{\operatorname{asin}{\left(x \right)}}{\left(x^{2} + 1\right) \operatorname{atan}^{2}{\left(x \right)}} + \frac{1}{\sqrt{1 - x^{2}} \operatorname{atan}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B165" t="str">
+      <x:c r="B179" t="str">
         <x:v>y=\arcsin(x) \cdot \frac{1}{\arctg(x)}+\tg(x) \cdot \frac{1}{\arcctg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C165" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D165" t="str">
+      <x:c r="C179" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D179" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 \[
@@ -11242,17 +12186,17 @@
 \boxed{\,y(x)=\frac{\tan x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="166">
-      <x:c r="A166" t="str">
+    <x:row r="180">
+      <x:c r="A180" t="str">
         <x:v>y^{\prime}=\left(2 \tan^{2}{\left(2 x \right)} + 2\right) \operatorname{acos}{\left(x \right)} - 2 \log{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} - \frac{\tan{\left(2 x \right)}}{\sqrt{1 - x^{2}}} - \frac{\operatorname{ctan}{\left(2 x \right)}}{x}</x:v>
       </x:c>
-      <x:c r="B166" t="str">
+      <x:c r="B180" t="str">
         <x:v>y=\arccos(x) \cdot \tg(2 \cdot x)-\ln(2 \cdot x) \cdot \ctg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C166" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D166" t="str">
+      <x:c r="C180" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D180" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 \[
@@ -11306,17 +12250,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="167">
-      <x:c r="A167" t="str">
+    <x:row r="181">
+      <x:c r="A181" t="str">
         <x:v>y^{\prime}=\frac{\sin{\left(x \right)}}{\log{\left(2 x \right)}} + \frac{\cos{\left(x \right)}}{x \log{\left(2 x \right)}^{2}} - e^{- x} \operatorname{ctan}{\left(x \right)} \log{\left(e \right)} + e^{- x} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}</x:v>
       </x:c>
-      <x:c r="B167" t="str">
+      <x:c r="B181" t="str">
         <x:v>y=\ctg(x) \cdot \frac{1}{e^{x}}-\cos(x) \cdot \frac{1}{\ln(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C167" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D167" t="str">
+      <x:c r="C181" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D181" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -11387,17 +12331,17 @@
 \boxed{\,y(x)=e^{-x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="168">
-      <x:c r="A168" t="str">
+    <x:row r="182">
+      <x:c r="A182" t="str">
         <x:v>y^{\prime}=- x^{2} \sin{\left(x \right)} + 2 x \cos{\left(x \right)} + \left(2 \tan^{2}{\left(2 x \right)} + 2\right) \cos{\left(2 x \right)} - 2 \sin{\left(2 x \right)} \tan{\left(2 x \right)}</x:v>
       </x:c>
-      <x:c r="B168" t="str">
+      <x:c r="B182" t="str">
         <x:v>y=\cos(2 \cdot x) \cdot \tg(2 \cdot x)+x^{2} \cdot \cos(x)+C</x:v>
       </x:c>
-      <x:c r="C168" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D168" t="str">
+      <x:c r="C182" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D182" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 \[
@@ -11457,17 +12401,17 @@
 \boxed{\,y = x^{2}</x:v>
       </x:c>
     </x:row>
-    <x:row r="169">
-      <x:c r="A169" t="str">
+    <x:row r="183">
+      <x:c r="A183" t="str">
         <x:v>y^{\prime}=- \frac{x^{3} \cos{\left(x \right)}}{\sin^{2}{\left(x \right)}} + \frac{3 x^{2}}{\sin{\left(x \right)}} - \operatorname{ctan}{\left(2 x \right)} \sin{\left(x \right)} + 2 \cos{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}</x:v>
       </x:c>
-      <x:c r="B169" t="str">
+      <x:c r="B183" t="str">
         <x:v>y=\cos(x) \cdot \ctg(2 \cdot x)+x^{3} \cdot \frac{1}{\sin(x)}+C</x:v>
       </x:c>
-      <x:c r="C169" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D169" t="str">
+      <x:c r="C183" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D183" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -11489,17 +12433,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="170">
-      <x:c r="A170" t="str">
+    <x:row r="184">
+      <x:c r="A184" t="str">
         <x:v>y^{\prime}=- e^{x} \log{\left(e \right)} \sin{\left(x \right)} - e^{x} \cos{\left(x \right)} + 2 \operatorname{ctan}{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} + \operatorname{ctan}{\left(2 x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}</x:v>
       </x:c>
-      <x:c r="B170" t="str">
+      <x:c r="B184" t="str">
         <x:v>y=\ctg(2 \cdot x) \cdot \ctg(x)-e^{x} \cdot \sin(x)+C</x:v>
       </x:c>
-      <x:c r="C170" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D170" t="str">
+      <x:c r="C184" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D184" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -11545,17 +12489,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="171">
-      <x:c r="A171" t="str">
+    <x:row r="185">
+      <x:c r="A185" t="str">
         <x:v>y^{\prime}=- \frac{\operatorname{asin}{\left(2 x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{ctan}^{2}{\left(x \right)}} + \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{ctan}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B171" t="str">
+      <x:c r="B185" t="str">
         <x:v>y=\arcsin(2 \cdot x) \cdot \frac{1}{\ctg(x)}+x \cdot x^{2}+C</x:v>
       </x:c>
-      <x:c r="C171" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D171" t="str">
+      <x:c r="C185" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D185" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 The given differential equation is  
@@ -11635,17 +12579,17 @@
 \boxed{\,y = \arcsin(2x)\,\tan x + C\,}</x:v>
       </x:c>
     </x:row>
-    <x:row r="172">
-      <x:c r="A172" t="str">
+    <x:row r="186">
+      <x:c r="A186" t="str">
         <x:v>y^{\prime}=\left(2 \tan^{2}{\left(2 x \right)} + 2\right) \log{\left(2 x \right)} - \frac{\operatorname{asin}{\left(x \right)}}{\left(x^{2} + 1\right) \operatorname{atan}^{2}{\left(x \right)}} + \frac{1}{\sqrt{1 - x^{2}} \operatorname{atan}{\left(x \right)}} + \frac{\tan{\left(2 x \right)}}{x}</x:v>
       </x:c>
-      <x:c r="B172" t="str">
+      <x:c r="B186" t="str">
         <x:v>y=\tg(2 \cdot x) \cdot \ln(2 \cdot x)+\arcsin(x) \cdot \frac{1}{\arctg(x)}+C</x:v>
       </x:c>
-      <x:c r="C172" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D172" t="str">
+      <x:c r="C186" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D186" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The differential equation is  
@@ -11710,17 +12654,17 @@
 \boxed{\,y(x)=\tan(2x)\,\log(2x)+\frac{\arcsin x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="173">
-      <x:c r="A173" t="str">
+    <x:row r="187">
+      <x:c r="A187" t="str">
         <x:v>y^{\prime}=\frac{2 \sin{\left(x \right)} \cos{\left(2 x \right)}}{\sin^{2}{\left(2 x \right)}} - \frac{\cos{\left(x \right)}}{\sin{\left(2 x \right)}} - \frac{\operatorname{asin}{\left(x \right)}}{x^{2} + 1} + \frac{\operatorname{acot}{\left(x \right)}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
-      <x:c r="B173" t="str">
+      <x:c r="B187" t="str">
         <x:v>y=\arcsin(x) \cdot \arcctg(x)-\sin(x) \cdot \frac{1}{\sin(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C173" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D173" t="str">
+      <x:c r="C187" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D187" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -11750,17 +12694,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="174">
-      <x:c r="A174" t="str">
+    <x:row r="188">
+      <x:c r="A188" t="str">
         <x:v>y^{\prime}=- \frac{2 x^{3} \cos{\left(2 x \right)}}{\sin^{2}{\left(2 x \right)}} + \frac{3 x^{2}}{\sin{\left(2 x \right)}} + \frac{\frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{acos}{\left(x \right)}} + \frac{\operatorname{ctan}{\left(x \right)}}{\sqrt{1 - x^{2}} \operatorname{acos}^{2}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B174" t="str">
+      <x:c r="B188" t="str">
         <x:v>y=\ctg(x) \cdot \frac{1}{\arccos(x)}+x^{3} \cdot \frac{1}{\sin(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C174" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D174" t="str">
+      <x:c r="C188" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D188" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -11846,17 +12790,17 @@
 \boxed{\,y(x)=\frac{x^{3}</x:v>
       </x:c>
     </x:row>
-    <x:row r="175">
-      <x:c r="A175" t="str">
+    <x:row r="189">
+      <x:c r="A189" t="str">
         <x:v>y^{\prime}=e^{x} \log{\left(e \right)} \operatorname{asin}{\left(2 x \right)} + \frac{2 e^{x}}{\sqrt{1 - 4 x^{2}}} + \frac{2 \sin{\left(2 x \right)}}{\sin{\left(x \right)}} + \frac{\cos{\left(x \right)} \cos{\left(2 x \right)}}{\sin^{2}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B175" t="str">
+      <x:c r="B189" t="str">
         <x:v>y=e^{x} \cdot \arcsin(2 \cdot x)-\cos(2 \cdot x) \cdot \frac{1}{\sin(x)}+C</x:v>
       </x:c>
-      <x:c r="C175" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D175" t="str">
+      <x:c r="C189" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D189" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 \[
@@ -11877,17 +12821,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="176">
-      <x:c r="A176" t="str">
+    <x:row r="190">
+      <x:c r="A190" t="str">
         <x:v>y^{\prime}=\left(2 \tan^{2}{\left(2 x \right)} + 2\right) \operatorname{acot}{\left(2 x \right)} + \cos{\left(x \right)} \operatorname{acos}{\left(2 x \right)} - \frac{2 \tan{\left(2 x \right)}}{4 x^{2} + 1} - \frac{2 \sin{\left(x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B176" t="str">
+      <x:c r="B190" t="str">
         <x:v>y=\arcctg(2 \cdot x) \cdot \tg(2 \cdot x)+\arccos(2 \cdot x) \cdot \sin(x)+C</x:v>
       </x:c>
-      <x:c r="C176" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D176" t="str">
+      <x:c r="C190" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D190" t="str">
         <x:v>[REASONING]
 **Solution**
 \[
@@ -11949,17 +12893,17 @@
 \boxed{\,y = \tan(2x)\,\operatorname{acot}</x:v>
       </x:c>
     </x:row>
-    <x:row r="177">
-      <x:c r="A177" t="str">
+    <x:row r="191">
+      <x:c r="A191" t="str">
         <x:v>y^{\prime}=- x^{3} \left(\tan^{2}{\left(x \right)} + 1\right) - 3 x^{2} \tan{\left(x \right)} + \log{\left(x \right)} + 1</x:v>
       </x:c>
-      <x:c r="B177" t="str">
+      <x:c r="B191" t="str">
         <x:v>y=x \cdot \ln(x)-x^{3} \cdot \tg(x)+C</x:v>
       </x:c>
-      <x:c r="C177" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D177" t="str">
+      <x:c r="C191" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D191" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -12006,17 +12950,17 @@
 \boxed{\,y(x)= -\,x^{3}</x:v>
       </x:c>
     </x:row>
-    <x:row r="178">
-      <x:c r="A178" t="str">
+    <x:row r="192">
+      <x:c r="A192" t="str">
         <x:v>y^{\prime}=- \frac{2 \operatorname{acot}{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - \frac{\operatorname{acos}{\left(x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{ctan}^{2}{\left(x \right)}} - \frac{1}{\left(x^{2} + 1\right) \operatorname{ctan}{\left(2 x \right)}} - \frac{1}{\sqrt{1 - x^{2}} \operatorname{ctan}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B178" t="str">
+      <x:c r="B192" t="str">
         <x:v>y=\arccos(x) \cdot \frac{1}{\ctg(x)}+\arcctg(x) \cdot \frac{1}{\ctg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C178" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D178" t="str">
+      <x:c r="C192" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D192" t="str">
         <x:v>[REASONING]
 **Reasoning**
 First rewrite the right–hand side using the usual trigonometric notation  
@@ -12076,17 +13020,17 @@
 \boxed{\,y(x)=\operatorname{acot}</x:v>
       </x:c>
     </x:row>
-    <x:row r="179">
-      <x:c r="A179" t="str">
+    <x:row r="193">
+      <x:c r="A193" t="str">
         <x:v>y^{\prime}=\frac{1}{\left(x^{2} + 1\right) \operatorname{acos}{\left(2 x \right)}} + \frac{2 \operatorname{atan}{\left(x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{acos}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B179" t="str">
+      <x:c r="B193" t="str">
         <x:v>y=\arctg(x) \cdot \frac{1}{\arccos(2 \cdot x)}-\arctg(x) \cdot \ln(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C179" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D179" t="str">
+      <x:c r="C193" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D193" t="str">
         <x:v>[REASONING]
 **Reasoning**
 We are asked to solve  
@@ -12141,17 +13085,17 @@
 \boxed{\,y=\frac{\displaystyle \arctan x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="180">
-      <x:c r="A180" t="str">
+    <x:row r="194">
+      <x:c r="A194" t="str">
         <x:v>y^{\prime}=\frac{x^{2}}{\sqrt{1 - x^{2}} \operatorname{acos}^{2}{\left(x \right)}} - \frac{2 x^{2}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}} + \frac{2 x}{\operatorname{asin}{\left(2 x \right)}} + \frac{2 x}{\operatorname{acos}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B180" t="str">
+      <x:c r="B194" t="str">
         <x:v>y=x^{2} \cdot \frac{1}{\arccos(x)}+x^{2} \cdot \frac{1}{\arcsin(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C180" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D180" t="str">
+      <x:c r="C194" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D194" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 \[
@@ -12198,17 +13142,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="181">
-      <x:c r="A181" t="str">
+    <x:row r="195">
+      <x:c r="A195" t="str">
         <x:v>y^{\prime}=- 2 \sin{\left(2 x \right)} \operatorname{acot}{\left(x \right)} + \frac{2 \operatorname{atan}{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - \frac{2}{\left(4 x^{2} + 1\right) \operatorname{ctan}{\left(2 x \right)}} - \frac{\cos{\left(2 x \right)}}{x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B181" t="str">
+      <x:c r="B195" t="str">
         <x:v>y=\arcctg(x) \cdot \cos(2 \cdot x)-\arctg(2 \cdot x) \cdot \frac{1}{\ctg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C181" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D181" t="str">
+      <x:c r="C195" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D195" t="str">
         <x:v>[REASONING]
 \[
 \boxed{\,y(x)=\cos (2x)\,\operatorname{acot}(x)\;-\;\tan (
@@ -12216,17 +13160,17 @@
 \boxed{\,y(x)=\cos (2x)\,\operatorname{acot}</x:v>
       </x:c>
     </x:row>
-    <x:row r="182">
-      <x:c r="A182" t="str">
+    <x:row r="196">
+      <x:c r="A196" t="str">
         <x:v>y^{\prime}=\left(2 \tan^{2}{\left(2 x \right)} + 2\right) \operatorname{ctan}{\left(x \right)} + \tan{\left(2 x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} - \operatorname{asin}{\left(x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} - \frac{\operatorname{ctan}{\left(x \right)}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
-      <x:c r="B182" t="str">
+      <x:c r="B196" t="str">
         <x:v>y=\ctg(x) \cdot \tg(2 \cdot x)-\ctg(x) \cdot \arcsin(x)+C</x:v>
       </x:c>
-      <x:c r="C182" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D182" t="str">
+      <x:c r="C196" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D196" t="str">
         <x:v>[REASONING]
 **Step 1 – Rewrite the given equation**
 \[
@@ -12296,17 +13240,17 @@
 \boxed{\,y = \bigl(\tan (2x)-\arcsin x\bigr)\cot x + C\,}</x:v>
       </x:c>
     </x:row>
-    <x:row r="183">
-      <x:c r="A183" t="str">
+    <x:row r="197">
+      <x:c r="A197" t="str">
         <x:v>y^{\prime}=- \frac{2 \sin{\left(2 x \right)}}{\operatorname{asin}{\left(2 x \right)}} - \frac{2 \cos{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B183" t="str">
+      <x:c r="B197" t="str">
         <x:v>y=\cos(2 \cdot x) \cdot \frac{1}{\arcsin(2 \cdot x)}-\arcsin(x) \cdot x^{2}+C</x:v>
       </x:c>
-      <x:c r="C183" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D183" t="str">
+      <x:c r="C197" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D197" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -12345,34 +13289,34 @@
 \boxed{\,y(x)=\frac{\cos (2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="184">
-      <x:c r="A184" t="str">
+    <x:row r="198">
+      <x:c r="A198" t="str">
         <x:v>y^{\prime}=- \frac{2 \operatorname{acot}{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - \frac{2}{\left(4 x^{2} + 1\right) \operatorname{ctan}{\left(2 x \right)}} - \frac{1}{x \sqrt{1 - x^{2}}} - \frac{\operatorname{acos}{\left(x \right)}}{x^{2}}</x:v>
       </x:c>
-      <x:c r="B184" t="str">
+      <x:c r="B198" t="str">
         <x:v>y=\arcctg(2 \cdot x) \cdot \frac{1}{\ctg(2 \cdot x)}+\arccos(x) \cdot \frac{1}{x}+C</x:v>
       </x:c>
-      <x:c r="C184" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D184" t="str">
+      <x:c r="C198" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D198" t="str">
         <x:v>[REASONING]
 ERROR: Empty response
 [FINAL ANSWER]
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="185">
-      <x:c r="A185" t="str">
+    <x:row r="199">
+      <x:c r="A199" t="str">
         <x:v>y^{\prime}=- \sin{\left(x \right)} \operatorname{acos}{\left(2 x \right)} - \frac{2 \operatorname{atan}{\left(x \right)}}{4 x^{2} + 1} - \frac{\operatorname{atan}{\left(2 x \right)}}{x^{2} + 1} - \frac{2 \cos{\left(x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B185" t="str">
+      <x:c r="B199" t="str">
         <x:v>y=\arccos(2 \cdot x) \cdot \cos(x)-\arctg(x) \cdot \arctg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C185" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D185" t="str">
+      <x:c r="C199" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D199" t="str">
         <x:v>[REASONING]
 **Step‑by‑step integration**
 The differential equation is  
@@ -12423,17 +13367,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="186">
-      <x:c r="A186" t="str">
+    <x:row r="200">
+      <x:c r="A200" t="str">
         <x:v>y^{\prime}=\frac{2 e^{2 x} \log{\left(e \right)}}{\operatorname{ctan}{\left(2 x \right)}} - \frac{2 e^{2 x} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B186" t="str">
+      <x:c r="B200" t="str">
         <x:v>y=e^{2 \cdot x} \cdot \frac{1}{\ctg(2 \cdot x)}+\ctg(x) \cdot \arctg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C186" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D186" t="str">
+      <x:c r="C200" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D200" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 1. **Simplify the right‑hand side**
@@ -12490,17 +13434,17 @@
 \boxed{\,y(x)=e^{2x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="187">
-      <x:c r="A187" t="str">
+    <x:row r="201">
+      <x:c r="A201" t="str">
         <x:v>y^{\prime}=- \frac{x}{x^{2} + 1} + \operatorname{acot}{\left(x \right)} - \frac{\operatorname{asin}{\left(2 x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{ctan}^{2}{\left(x \right)}} + \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{ctan}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B187" t="str">
+      <x:c r="B201" t="str">
         <x:v>y=\arcctg(x) \cdot x+\arcsin(2 \cdot x) \cdot \frac{1}{\ctg(x)}+C</x:v>
       </x:c>
-      <x:c r="C187" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D187" t="str">
+      <x:c r="C201" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D201" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -12550,17 +13494,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="188">
-      <x:c r="A188" t="str">
+    <x:row r="202">
+      <x:c r="A202" t="str">
         <x:v>y^{\prime}=- \frac{3 x^{2}}{\log{\left(2 x \right)}} + \frac{x^{2}}{\log{\left(2 x \right)}^{2}} - 2 - \frac{2 \cos^{2}{\left(2 x \right)}}{\sin^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B188" t="str">
+      <x:c r="B202" t="str">
         <x:v>y=\cos(2 \cdot x) \cdot \frac{1}{\sin(2 \cdot x)}-x^{3} \cdot \frac{1}{\ln(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C188" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D188" t="str">
+      <x:c r="C202" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D202" t="str">
         <x:v>[REASONING]
 [REASONING]
 \[
@@ -12603,17 +13547,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="189">
-      <x:c r="A189" t="str">
+    <x:row r="203">
+      <x:c r="A203" t="str">
         <x:v>y^{\prime}=\left(2 \tan^{2}{\left(2 x \right)} + 2\right) \log{\left(x \right)} - \frac{1}{\sqrt{1 - x^{2}} \operatorname{asin}{\left(2 x \right)}} + \frac{2 \operatorname{asin}{\left(x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}} + \frac{\tan{\left(2 x \right)}}{x}</x:v>
       </x:c>
-      <x:c r="B189" t="str">
+      <x:c r="B203" t="str">
         <x:v>y=\tg(2 \cdot x) \cdot \ln(x)-\arcsin(x) \cdot \frac{1}{\arcsin(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C189" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D189" t="str">
+      <x:c r="C203" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D203" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -12652,17 +13596,17 @@
 \boxed{\log x\,\tan(2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="190">
-      <x:c r="A190" t="str">
+    <x:row r="204">
+      <x:c r="A204" t="str">
         <x:v>y^{\prime}=e^{x} \log{\left(e \right)} \sin{\left(x \right)} + e^{x} \cos{\left(x \right)} - \cos{\left(x \right)} \operatorname{acos}{\left(x \right)} + \frac{\sin{\left(x \right)}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
-      <x:c r="B190" t="str">
+      <x:c r="B204" t="str">
         <x:v>y=e^{x} \cdot \sin(x)-\arccos(x) \cdot \sin(x)+C</x:v>
       </x:c>
-      <x:c r="C190" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D190" t="str">
+      <x:c r="C204" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D204" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -12703,17 +13647,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="191">
-      <x:c r="A191" t="str">
+    <x:row r="205">
+      <x:c r="A205" t="str">
         <x:v>y^{\prime}=2 e^{2 x} \log{\left(e \right)} \operatorname{atan}{\left(x \right)} + \frac{e^{2 x}}{x^{2} + 1} + 1</x:v>
       </x:c>
-      <x:c r="B191" t="str">
+      <x:c r="B205" t="str">
         <x:v>y=e^{2 \cdot x} \cdot \arctg(x)+x^{2} \cdot \frac{1}{x}+C</x:v>
       </x:c>
-      <x:c r="C191" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D191" t="str">
+      <x:c r="C205" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D205" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -12762,17 +13706,17 @@
 \boxed{\,y(x)=e^{2x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="192">
-      <x:c r="A192" t="str">
+    <x:row r="206">
+      <x:c r="A206" t="str">
         <x:v>y^{\prime}=\cos{\left(x \right)} \operatorname{acot}{\left(x \right)} - \frac{\frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{atan}{\left(x \right)}} + \frac{\operatorname{ctan}{\left(x \right)}}{\left(x^{2} + 1\right) \operatorname{atan}^{2}{\left(x \right)}} - \frac{\sin{\left(x \right)}}{x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B192" t="str">
+      <x:c r="B206" t="str">
         <x:v>y=\arcctg(x) \cdot \sin(x)-\ctg(x) \cdot \frac{1}{\arctg(x)}+C</x:v>
       </x:c>
-      <x:c r="C192" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D192" t="str">
+      <x:c r="C206" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D206" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -12827,17 +13771,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="193">
-      <x:c r="A193" t="str">
+    <x:row r="207">
+      <x:c r="A207" t="str">
         <x:v>y^{\prime}=\frac{\frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{acos}{\left(x \right)}} + \frac{\operatorname{ctan}{\left(x \right)}}{\sqrt{1 - x^{2}} \operatorname{acos}^{2}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B193" t="str">
+      <x:c r="B207" t="str">
         <x:v>y=\ctg(x) \cdot \frac{1}{\arccos(x)}-\tg(2 \cdot x) \cdot \arccos(x)+C</x:v>
       </x:c>
-      <x:c r="C193" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D193" t="str">
+      <x:c r="C207" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D207" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -12898,17 +13842,17 @@
 \boxed{\,y(x)=\frac{\cot x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="194">
-      <x:c r="A194" t="str">
+    <x:row r="208">
+      <x:c r="A208" t="str">
         <x:v>y^{\prime}=2 e^{2 x} x \log{\left(e \right)} + e^{2 x} - 2 \sin{\left(2 x \right)} \operatorname{acot}{\left(x \right)} - \frac{\cos{\left(2 x \right)}}{x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B194" t="str">
+      <x:c r="B208" t="str">
         <x:v>y=x \cdot e^{2 \cdot x}+\arcctg(x) \cdot \cos(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C194" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D194" t="str">
+      <x:c r="C208" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D208" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 The differential equation is  
@@ -12969,17 +13913,17 @@
 \boxed{\,y(x)=x\,e^{2x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="195">
-      <x:c r="A195" t="str">
+    <x:row r="209">
+      <x:c r="A209" t="str">
         <x:v>y^{\prime}=\frac{2 e^{2 x} \log{\left(e \right)}}{\operatorname{asin}{\left(x \right)}} - \frac{e^{2 x}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}} - \sin{\left(x \right)} \operatorname{acos}{\left(2 x \right)} - \frac{2 \cos{\left(x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B195" t="str">
+      <x:c r="B209" t="str">
         <x:v>y=\arccos(2 \cdot x) \cdot \cos(x)+e^{2 \cdot x} \cdot \frac{1}{\arcsin(x)}+C</x:v>
       </x:c>
-      <x:c r="C195" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D195" t="str">
+      <x:c r="C209" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D209" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 The differential equation is  
@@ -13041,17 +13985,17 @@
 \boxed{\,y = \frac{e^{2x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="196">
-      <x:c r="A196" t="str">
+    <x:row r="210">
+      <x:c r="A210" t="str">
         <x:v>y^{\prime}=2 e^{2 x} \log{\left(e \right)} \log{\left(2 x \right)} + \frac{e^{2 x}}{x} - \frac{\tan^{2}{\left(x \right)} + 1}{\sin{\left(2 x \right)}} + \frac{2 \cos{\left(2 x \right)} \tan{\left(x \right)}}{\sin^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B196" t="str">
+      <x:c r="B210" t="str">
         <x:v>y=\ln(2 \cdot x) \cdot e^{2 \cdot x}-\tg(x) \cdot \frac{1}{\sin(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C196" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D196" t="str">
+      <x:c r="C210" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D210" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 The differential equation is  
@@ -13123,17 +14067,70 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="197">
-      <x:c r="A197" t="str">
+    <x:row r="211">
+      <x:c r="A211" t="str">
+        <x:v>y^{\prime}=\frac{2 \sin{\left(2 x \right)} \operatorname{asin}{\left(2 x \right)}}{\cos^{2}{\left(2 x \right)}} + \frac{2}{\sqrt{1 - 4 x^{2}} \cos{\left(2 x \right)}}</x:v>
+      </x:c>
+      <x:c r="B211" t="str">
+        <x:v>y=\arcsin(2 \cdot x) \cdot \frac{1}{\cos(2 \cdot x)}-\ln(2 \cdot x) \cdot \arctg(2 \cdot x)+C</x:v>
+      </x:c>
+      <x:c r="C211" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D211" t="str">
+        <x:v>[REASONING]
+**Reasoning**
+\[
+y'=\frac{2\sin(2x)\,\arcsin(2x)}{\cos^{2}(2x)}+\frac{2}{\sqrt{1-4x^{2}}\;\cos(2x)}
+\]
+Observe that the right–hand side can be written as a derivative of a product.
+Let  
+\[
+f(x)=\arcsin(2x)\qquad\text{and}\qquad g(x)=\sec(2x)=\frac{1}{\cos(2x)} .
+\]
+Then  
+\[
+\frac{d}{dx}f(x)=\frac{2}{\sqrt{1-4x^{2}}},\qquad 
+\frac{d}{dx}g(x)=\frac{d}{dx}\bigl(\sec(2x)\bigr)=2\sec(2x)\tan(2x)
+      =\frac{2\sin(2x)}{\cos^{2}(2x)} .
+\]
+Using the product rule,
+\[
+\frac{d}{dx}\bigl[f(x)g(x)\bigr]
+   =f'(x)g(x)+f(x)g'(x)
+   =\frac{2}{\sqrt{1-4x^{2}}}\,\frac{1}{\cos(2x)}
+     +\arcsin(2x)\,\frac{2\sin(2x)}{\cos^{2}(2x)} .
+\]
+The right‑hand side is exactly the given expression for \(y'\).  
+Hence
+\[
+y'=\frac{d}{dx}\!\left(\frac{\arcsin(2x)}{\cos(2x)}\right).
+\]
+Integrating both sides with respect to \(x\),
+\[
+y=\frac{\arcsin(2x)}{\cos(2x)}+C,
+\]
+where \(C\) is an arbitrary constant.
+---
+**Final Answer**
+\[
+\boxed{\,y=\frac{\arcsin(2x)}{\cos(2x)}+C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y=\frac{\arcsin(2x)}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" t="str">
         <x:v>y^{\prime}=- \frac{\log{\left(x \right)} \sin{\left(x \right)}}{\cos^{2}{\left(x \right)}} - \frac{\log{\left(2 x \right)}}{\sqrt{1 - x^{2}}} + \frac{\operatorname{acos}{\left(x \right)}}{x} - \frac{1}{x \cos{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B197" t="str">
+      <x:c r="B212" t="str">
         <x:v>y=\ln(2 \cdot x) \cdot \arccos(x)-\ln(x) \cdot \frac{1}{\cos(x)}+C</x:v>
       </x:c>
-      <x:c r="C197" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D197" t="str">
+      <x:c r="C212" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D212" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -13195,17 +14192,17 @@
 \boxed{\,y = \log (2x)\,\arccos (x)\;-\;\log (x)\,\sec (x)\;+\;C\,}</x:v>
       </x:c>
     </x:row>
-    <x:row r="198">
-      <x:c r="A198" t="str">
+    <x:row r="213">
+      <x:c r="A213" t="str">
         <x:v>y^{\prime}=- e^{x} \log{\left(e \right)} \operatorname{asin}{\left(x \right)} - \frac{e^{x}}{\sqrt{1 - x^{2}}} + \frac{2 \operatorname{acos}{\left(2 x \right)}}{4 x^{2} + 1} - \frac{2 \operatorname{atan}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B198" t="str">
+      <x:c r="B213" t="str">
         <x:v>y=\arccos(2 \cdot x) \cdot \arctg(2 \cdot x)-\arcsin(x) \cdot e^{x}+C</x:v>
       </x:c>
-      <x:c r="C198" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D198" t="str">
+      <x:c r="C213" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D213" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The differential equation is  
@@ -13258,17 +14255,17 @@
 \boxed{\,y = \arccos(2x)\,\arctan(2x)\;-\;e^{x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="199">
-      <x:c r="A199" t="str">
+    <x:row r="214">
+      <x:c r="A214" t="str">
         <x:v>y^{\prime}=- \frac{\operatorname{acos}{\left(x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{ctan}^{2}{\left(x \right)}} - \frac{\log{\left(2 x \right)}}{\sqrt{1 - x^{2}}} - \frac{1}{\sqrt{1 - x^{2}} \operatorname{ctan}{\left(x \right)}} + \frac{\operatorname{acos}{\left(x \right)}}{x}</x:v>
       </x:c>
-      <x:c r="B199" t="str">
+      <x:c r="B214" t="str">
         <x:v>y=\ln(2 \cdot x) \cdot \arccos(x)+\arccos(x) \cdot \frac{1}{\ctg(x)}+C</x:v>
       </x:c>
-      <x:c r="C199" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D199" t="str">
+      <x:c r="C214" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D214" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -13361,34 +14358,34 @@
 \boxed{\,y = \arccos x\bigl(\tan x+\log(2x)\bigr)+C\,}</x:v>
       </x:c>
     </x:row>
-    <x:row r="200">
-      <x:c r="A200" t="str">
+    <x:row r="215">
+      <x:c r="A215" t="str">
         <x:v>y^{\prime}=\frac{x^{3}}{\sqrt{1 - x^{2}} \operatorname{acos}^{2}{\left(x \right)}} + \frac{3 x^{2}}{\operatorname{acos}{\left(x \right)}} - \frac{\log{\left(x \right)} \cos{\left(x \right)}}{\sin^{2}{\left(x \right)}} + \frac{1}{x \sin{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B200" t="str">
+      <x:c r="B215" t="str">
         <x:v>y=\ln(x) \cdot \frac{1}{\sin(x)}+x^{3} \cdot \frac{1}{\arccos(x)}+C</x:v>
       </x:c>
-      <x:c r="C200" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D200" t="str">
+      <x:c r="C215" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D215" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution
 [FINAL ANSWER]
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="201">
-      <x:c r="A201" t="str">
+    <x:row r="216">
+      <x:c r="A216" t="str">
         <x:v>y^{\prime}=\left(2 \tan^{2}{\left(2 x \right)} + 2\right) \sin{\left(x \right)} + \cos{\left(x \right)} \tan{\left(2 x \right)} + \frac{\cos{\left(x \right)}}{\log{\left(x \right)}} - \frac{\sin{\left(x \right)}}{x \log{\left(x \right)}^{2}}</x:v>
       </x:c>
-      <x:c r="B201" t="str">
+      <x:c r="B216" t="str">
         <x:v>y=\sin(x) \cdot \tg(2 \cdot x)+\sin(x) \cdot \frac{1}{\ln(x)}+C</x:v>
       </x:c>
-      <x:c r="C201" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D201" t="str">
+      <x:c r="C216" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D216" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -13444,17 +14441,17 @@
 \boxed{\,y(x)=\sin x\,\tan(2x)+\frac{\sin x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="202">
-      <x:c r="A202" t="str">
+    <x:row r="217">
+      <x:c r="A217" t="str">
         <x:v>y^{\prime}=- \frac{2 \operatorname{atan}{\left(x \right)}}{4 x^{2} + 1} - \frac{\operatorname{atan}{\left(2 x \right)}}{x^{2} + 1} + \frac{2 \operatorname{acos}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}} - \frac{2 \operatorname{asin}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B202" t="str">
+      <x:c r="B217" t="str">
         <x:v>y=\arcsin(2 \cdot x) \cdot \arccos(2 \cdot x)-\arctg(x) \cdot \arctg(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C202" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D202" t="str">
+      <x:c r="C217" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D217" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -13469,17 +14466,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="203">
-      <x:c r="A203" t="str">
+    <x:row r="218">
+      <x:c r="A218" t="str">
         <x:v>y^{\prime}=- e^{x} \log{\left(e \right)} \operatorname{asin}{\left(2 x \right)} - \frac{2 e^{x}}{\sqrt{1 - 4 x^{2}}} + \frac{2 \operatorname{acos}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}} - \frac{2 \operatorname{asin}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B203" t="str">
+      <x:c r="B218" t="str">
         <x:v>y=\arcsin(2 \cdot x) \cdot \arccos(2 \cdot x)-e^{x} \cdot \arcsin(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C203" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D203" t="str">
+      <x:c r="C218" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D218" t="str">
         <x:v>[REASONING]
 [REASONING]
 First simplify the given differential equation.  
@@ -13505,17 +14502,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="204">
-      <x:c r="A204" t="str">
+    <x:row r="219">
+      <x:c r="A219" t="str">
         <x:v>y^{\prime}=\frac{\left(- 2 \tan^{2}{\left(2 x \right)} - 2\right) \sin{\left(2 x \right)}}{\tan^{2}{\left(2 x \right)}} + \frac{2 \cos{\left(2 x \right)}}{\tan{\left(2 x \right)}} - \frac{2 \operatorname{acos}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{asin}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B204" t="str">
+      <x:c r="B219" t="str">
         <x:v>y=\arccos(2 \cdot x) \cdot \frac{1}{\arcsin(2 \cdot x)}+\sin(2 \cdot x) \cdot \frac{1}{\tg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C204" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D204" t="str">
+      <x:c r="C219" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D219" t="str">
         <x:v>[REASONING]
 **Step 1 – Simplify the trigonometric part**
 \[
@@ -13556,17 +14553,72 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="205">
-      <x:c r="A205" t="str">
+    <x:row r="220">
+      <x:c r="A220" t="str">
+        <x:v>y^{\prime}=- \frac{\log{\left(2 x \right)} \cos{\left(x \right)}}{\sin^{2}{\left(x \right)}} + \frac{1}{x \sin{\left(x \right)}}</x:v>
+      </x:c>
+      <x:c r="B220" t="str">
+        <x:v>y=\ln(2 \cdot x) \cdot \frac{1}{\sin(x)}-\cos(2 \cdot x) \cdot \cos(x)+C</x:v>
+      </x:c>
+      <x:c r="C220" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D220" t="str">
+        <x:v>[REASONING]
+[REASONING]  
+The differential equation is  
+\[
+y'=- \frac{\log (2x)\,\cos x}{\sin ^2 x}+ \frac{1}{x\sin x}.
+\]
+Observe that  
+\[
+\frac{d}{dx}\bigl(\csc x\bigr)=\frac{d}{dx}\!\left(\frac{1}{\sin x}\right)= -\frac{\cos x}{\sin ^2 x}.
+\]
+Hence  
+\[
+-\frac{\log (2x)\,\cos x}{\sin ^2 x}= \log (2x)\,\frac{d}{dx}(\csc x).
+\]
+The second term can be written as  
+\[
+\frac{1}{x\sin x}= \frac{1}{x}\,\csc x.
+\]
+Therefore the right‑hand side of the ODE is exactly the derivative of the product \(\log(2x)\,\csc x\) by the product rule:
+\[
+\frac{d}{dx}\bigl[\log (2x)\,\csc x\bigr]
+   =\frac{1}{x}\csc x+\log (2x)\,\frac{d}{dx}(\csc x)
+   =\frac{1}{x\sin x}-\frac{\log (2x)\cos x}{\sin ^2 x}.
+\]
+Thus  
+\[
+y' = \frac{d}{dx}\bigl[\log (2x)\,\csc x\bigr].
+\]
+Integrating both sides with respect to \(x\),
+\[
+y = \log (2x)\,\csc x + C,
+\]
+where \(C\) is an arbitrary constant.  Since \(\csc x = 1/\sin x\),
+\[
+y = \frac{\log (2x)}{\sin x}+C.
+\]
+[FINAL ANSWER]  
+\[
+\boxed{\,y = \frac{\log (2x)}{\sin x}+C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y = \frac{\log (2x)}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" t="str">
         <x:v>y^{\prime}=\left(2 \tan^{2}{\left(2 x \right)} + 2\right) \operatorname{acos}{\left(x \right)} - \sin{\left(x \right)} \operatorname{asin}{\left(2 x \right)} - \frac{\tan{\left(2 x \right)}}{\sqrt{1 - x^{2}}} + \frac{2 \cos{\left(x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B205" t="str">
+      <x:c r="B221" t="str">
         <x:v>y=\cos(x) \cdot \arcsin(2 \cdot x)+\tg(2 \cdot x) \cdot \arccos(x)+C</x:v>
       </x:c>
-      <x:c r="C205" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D205" t="str">
+      <x:c r="C221" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D221" t="str">
         <x:v>[REASONING]
 **Solution**
 \[
@@ -13628,17 +14680,17 @@
 \boxed{\,y(x)=\tan (2x)\,\arccos x+\cos x\,\arcsin (2x)+C\,}</x:v>
       </x:c>
     </x:row>
-    <x:row r="206">
-      <x:c r="A206" t="str">
+    <x:row r="222">
+      <x:c r="A222" t="str">
         <x:v>y^{\prime}=- \frac{2 x^{2} \cos{\left(2 x \right)}}{\sin^{2}{\left(2 x \right)}} + \frac{2 x}{\sin{\left(2 x \right)}} + \frac{\left(- 2 \tan^{2}{\left(2 x \right)} - 2\right) \operatorname{acos}{\left(2 x \right)}}{\tan^{2}{\left(2 x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \tan{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B206" t="str">
+      <x:c r="B222" t="str">
         <x:v>y=x^{2} \cdot \frac{1}{\sin(2 \cdot x)}+\arccos(2 \cdot x) \cdot \frac{1}{\tg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C206" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D206" t="str">
+      <x:c r="C222" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D222" t="str">
         <x:v>[REASONING]
 **Step 1 – Recognise a part of the derivative**
 Consider  
@@ -13703,17 +14755,17 @@
 \boxed{\,y=\frac{x^{2}</x:v>
       </x:c>
     </x:row>
-    <x:row r="207">
-      <x:c r="A207" t="str">
+    <x:row r="223">
+      <x:c r="A223" t="str">
         <x:v>y^{\prime}=\frac{2}{\left(4 x^{2} + 1\right) \operatorname{acos}{\left(x \right)}} + \frac{\operatorname{atan}{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{acos}^{2}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B207" t="str">
+      <x:c r="B223" t="str">
         <x:v>y=\arctg(2 \cdot x) \cdot \frac{1}{\arccos(x)}+\arcctg(2 \cdot x) \cdot \arcsin(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C207" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D207" t="str">
+      <x:c r="C223" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D223" t="str">
         <x:v>[REASONING]
 **Solution**
 \[
@@ -13779,17 +14831,17 @@
 \boxed{\,y(x)=\dfrac{\displaystyle\arctan(2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="208">
-      <x:c r="A208" t="str">
+    <x:row r="224">
+      <x:c r="A224" t="str">
         <x:v>y^{\prime}=\log{\left(2 x \right)} \cos{\left(x \right)} + \frac{\operatorname{acot}{\left(x \right)}}{x^{2} + 1} - \frac{\operatorname{atan}{\left(x \right)}}{x^{2} + 1} + \frac{\sin{\left(x \right)}}{x}</x:v>
       </x:c>
-      <x:c r="B208" t="str">
+      <x:c r="B224" t="str">
         <x:v>y=\sin(x) \cdot \ln(2 \cdot x)+\arctg(x) \cdot \arcctg(x)+C</x:v>
       </x:c>
-      <x:c r="C208" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D208" t="str">
+      <x:c r="C224" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D224" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -13877,17 +14929,17 @@
 \boxed{\,y(x)=\sin x\,\log (2x)+\frac{\pi}</x:v>
       </x:c>
     </x:row>
-    <x:row r="209">
-      <x:c r="A209" t="str">
+    <x:row r="225">
+      <x:c r="A225" t="str">
         <x:v>y^{\prime}=\frac{x^{3} \cos{\left(x \right)}}{\sin^{2}{\left(x \right)}} - \frac{3 x^{2}}{\sin{\left(x \right)}} - e^{- x} x^{3} \log{\left(e \right)} + 3 e^{- x} x^{2}</x:v>
       </x:c>
-      <x:c r="B209" t="str">
+      <x:c r="B225" t="str">
         <x:v>y=x^{3} \cdot \frac{1}{e^{x}}-x^{3} \cdot \frac{1}{\sin(x)}+C</x:v>
       </x:c>
-      <x:c r="C209" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D209" t="str">
+      <x:c r="C225" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D225" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -13951,17 +15003,17 @@
 \boxed{\,y = x^{3}</x:v>
       </x:c>
     </x:row>
-    <x:row r="210">
-      <x:c r="A210" t="str">
+    <x:row r="226">
+      <x:c r="A226" t="str">
         <x:v>y^{\prime}=- \frac{2 \log{\left(x \right)} \sin{\left(2 x \right)}}{\cos^{2}{\left(2 x \right)}} + \frac{\operatorname{asin}{\left(2 x \right)}}{\left(x^{2} + 1\right) \operatorname{acot}^{2}{\left(x \right)}} + \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{acot}{\left(x \right)}} - \frac{1}{x \cos{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B210" t="str">
+      <x:c r="B226" t="str">
         <x:v>y=\arcsin(2 \cdot x) \cdot \frac{1}{\arcctg(x)}-\ln(x) \cdot \frac{1}{\cos(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C210" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D210" t="str">
+      <x:c r="C226" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D226" t="str">
         <x:v>[REASONING]
 The right–hand side can be recognized as the derivative of a combination of elementary functions.
 ---
@@ -14041,17 +15093,71 @@
 \boxed{\,y(x)=\displaystyle\frac{\arcsin(2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="211">
-      <x:c r="A211" t="str">
+    <x:row r="227">
+      <x:c r="A227" t="str">
+        <x:v>y^{\prime}=\frac{2 \cos{\left(2 x \right)}}{\operatorname{asin}{\left(2 x \right)}} - \frac{2 \sin{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}}</x:v>
+      </x:c>
+      <x:c r="B227" t="str">
+        <x:v>y=\sin(2 \cdot x) \cdot \frac{1}{\arcsin(2 \cdot x)}+\sin(2 \cdot x) \cdot \sin(x)+C</x:v>
+      </x:c>
+      <x:c r="C227" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D227" t="str">
+        <x:v>[REASONING]
+**Step‑by‑step solution**
+\[
+y'=\frac{2\cos (2x)}{\arcsin (2x)}-\frac{2\sin (2x)}{\sqrt{1-4x^{2}}\;\bigl(\arcsin (2x)\bigr)^{2}}
+\]
+---
+1. **Introduce a convenient notation**
+   Let  
+   \[
+   u(x)=\arcsin (2x).
+   \]
+   Then  
+   \[
+   u'(x)=\frac{d}{dx}\arcsin (2x)=\frac{2}{\sqrt{1-(2x)^{2}}}
+          =\frac{2}{\sqrt{1-4x^{2}}}.
+   \]
+2. **Observe the structure of the right‑hand side**
+   Consider the derivative of the quotient \(\displaystyle \frac{\sin (2x)}{u}\):
+   \[
+   \frac{d}{dx}\!\left(\frac{\sin (2x)}{u}\right)
+   =\frac{(2\cos (2x))\,u-\sin (2x)\,u'}{u^{2}}
+   =\frac{2\cos (2x)}{u}-\frac{2\sin (2x)}{\sqrt{1-4x^{2}}\;u^{2}} .
+   \]
+   The expression obtained is **exactly** the right‑hand side of the given differential equation.
+3. **Identify the derivative**
+   Hence  
+   \[
+   y'=\frac{d}{dx}\!\left(\frac{\sin (2x)}{\arcsin (2x)}\right).
+   \]
+4. **Integrate**
+   Integrating both sides with respect to \(x\),
+   \[
+   y=\frac{\sin (2x)}{\arcsin (2x)}+C,
+   \]
+   where \(C\) is an arbitrary constant of integration.
+---
+\[
+\boxed{\,y(x)=\frac{\sin (2x)}{\arcsin (2x)}+C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y(x)=\frac{\sin (2x)}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228" t="str">
         <x:v>y^{\prime}=\log{\left(x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} - \sin{\left(x \right)} \cos{\left(2 x \right)} - 2 \sin{\left(2 x \right)} \cos{\left(x \right)} + \frac{\operatorname{ctan}{\left(x \right)}}{x}</x:v>
       </x:c>
-      <x:c r="B211" t="str">
+      <x:c r="B228" t="str">
         <x:v>y=\cos(2 \cdot x) \cdot \cos(x)+\ln(x) \cdot \ctg(x)+C</x:v>
       </x:c>
-      <x:c r="C211" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D211" t="str">
+      <x:c r="C228" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D228" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -14109,17 +15215,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="212">
-      <x:c r="A212" t="str">
+    <x:row r="229">
+      <x:c r="A229" t="str">
         <x:v>y^{\prime}=\frac{2 x^{3}}{4 x^{2} + 1} - 3 x^{2} \operatorname{acot}{\left(2 x \right)} + 2 \cos{\left(2 x \right)} \operatorname{atan}{\left(x \right)} + \frac{\sin{\left(2 x \right)}}{x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B212" t="str">
+      <x:c r="B229" t="str">
         <x:v>y=\arctg(x) \cdot \sin(2 \cdot x)-\arcctg(2 \cdot x) \cdot x^{3}+C</x:v>
       </x:c>
-      <x:c r="C212" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D212" t="str">
+      <x:c r="C229" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D229" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -14181,17 +15287,17 @@
 \boxed{\,y(x)= -\,x^{3}</x:v>
       </x:c>
     </x:row>
-    <x:row r="213">
-      <x:c r="A213" t="str">
+    <x:row r="230">
+      <x:c r="A230" t="str">
         <x:v>y^{\prime}=2 \operatorname{ctan}{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} + \operatorname{ctan}{\left(2 x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} - \sin{\left(x \right)} \operatorname{acos}{\left(2 x \right)} - \frac{2 \cos{\left(x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B213" t="str">
+      <x:c r="B230" t="str">
         <x:v>y=\ctg(2 \cdot x) \cdot \ctg(x)+\arccos(2 \cdot x) \cdot \cos(x)+C</x:v>
       </x:c>
-      <x:c r="C213" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D213" t="str">
+      <x:c r="C230" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D230" t="str">
         <x:v>[REASONING]
 **Step 1 – Rewrite the right‑hand side**
 \[
@@ -14258,17 +15364,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="214">
-      <x:c r="A214" t="str">
+    <x:row r="231">
+      <x:c r="A231" t="str">
         <x:v>y^{\prime}=- \frac{e^{x} \log{\left(e \right)}}{x^{2}} + \frac{2 e^{x}}{x^{3}} + \cos{\left(x \right)} \operatorname{asin}{\left(x \right)} + \frac{\sin{\left(x \right)}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
-      <x:c r="B214" t="str">
+      <x:c r="B231" t="str">
         <x:v>y=\sin(x) \cdot \arcsin(x)-e^{x} \cdot \frac{1}{x^{2}}+C</x:v>
       </x:c>
-      <x:c r="C214" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D214" t="str">
+      <x:c r="C231" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D231" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The differential equation is  
@@ -14322,17 +15428,17 @@
 \boxed{\,y(x)= -\frac{e^{x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="215">
-      <x:c r="A215" t="str">
+    <x:row r="232">
+      <x:c r="A232" t="str">
         <x:v>y^{\prime}=- \frac{\operatorname{ctan}{\left(2 x \right)} \cos{\left(x \right)}}{\sin^{2}{\left(x \right)}} + \frac{2 \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\sin{\left(x \right)}} + \frac{\frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\log{\left(2 x \right)}} - \frac{\operatorname{ctan}{\left(x \right)}}{x \log{\left(2 x \right)}^{2}}</x:v>
       </x:c>
-      <x:c r="B215" t="str">
+      <x:c r="B232" t="str">
         <x:v>y=\ctg(2 \cdot x) \cdot \frac{1}{\sin(x)}+\ctg(x) \cdot \frac{1}{\ln(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C215" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D215" t="str">
+      <x:c r="C232" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D232" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -14405,17 +15511,86 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="216">
-      <x:c r="A216" t="str">
+    <x:row r="233">
+      <x:c r="A233" t="str">
+        <x:v>y^{\prime}=- \frac{\operatorname{acot}{\left(x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{ctan}^{2}{\left(x \right)}} - \frac{1}{\left(x^{2} + 1\right) \operatorname{ctan}{\left(x \right)}}</x:v>
+      </x:c>
+      <x:c r="B233" t="str">
+        <x:v>y=\arcctg(x) \cdot \frac{1}{\ctg(x)}-\sin(x) \cdot x+C</x:v>
+      </x:c>
+      <x:c r="C233" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D233" t="str">
+        <x:v>[REASONING]
+**[REASONING]**
+The given differential equation is  
+\[
+y'=- \frac{\operatorname{acot}(x)\,\dfrac{d}{dx}\operatorname{ctan}(x)}{\operatorname{ctan}^{2}(x)}-\frac{1}{(x^{2}+1)\operatorname{ctan}(x)} .
+\]
+Here \(\operatorname{ctan}(x)=\cot x\) and \(\operatorname{acot}(x)=\arccot x\).
+---
+### 1. Simplify the right‑hand side  
+\[
+\frac{d}{dx}\cot x = -\csc^{2}x .
+\]
+Hence  
+\[
+\begin{aligned}
+y' &amp;= -\frac{\arccot x\;(-\csc^{2}x)}{\cot^{2}x}-\frac{1}{(x^{2}+1)\cot x}\\[2mm]
+   &amp;= \frac{\arccot x\,\csc^{2}x}{\cot^{2}x}-\frac{1}{(x^{2}+1)\cot x}.
+\end{aligned}
+\]
+Use \(\csc^{2}x = 1/\sin^{2}x\) and \(\cot^{2}x = \cos^{2}x/\sin^{2}x\):
+\[
+\frac{\csc^{2}x}{\cot^{2}x}= \frac{1/\sin^{2}x}{\cos^{2}x/\sin^{2}x}= \frac{1}{\cos^{2}x}= \sec^{2}x .
+\]
+Also \(\displaystyle \frac{1}{\cot x}= \tan x\). Therefore  
+\[
+y' = \arccot x\,\sec^{2}x-\frac{\tan x}{x^{2}+1}.
+\]
+---
+### 2. Recognise a total derivative  
+Consider the product \(u(x)v(x)=\arccot x\;\tan x\).
+\[
+\begin{aligned}
+\frac{d}{dx}\bigl(\arccot x\;\tan x\bigr)
+&amp;= (\arccot x)'\tan x + \arccot x\;(\tan x)'\\[2mm]
+&amp;= \left(-\frac{1}{1+x^{2}}\right)\tan x + \arccot x\;\sec^{2}x\\[2mm]
+&amp;= \arccot x\;\sec^{2}x - \frac{\tan x}{x^{2}+1}.
+\end{aligned}
+\]
+The right‑hand side is exactly the expression we obtained for \(y'\). Hence  
+\[
+y' = \frac{d}{dx}\bigl(\arccot x\;\tan x\bigr).
+\]
+---
+### 3. Integrate  
+Integrating both sides with respect to \(x\),
+\[
+y = \arccot x\;\tan x + C,
+\]
+where \(C\) is an arbitrary constant.
+---
+**[FINAL ANSWER]**
+\[
+\boxed{\,y = \tan x \,\operatorname{acot} x + C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y = \tan x \,\operatorname{acot}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" t="str">
         <x:v>y^{\prime}=\frac{\tan^{2}{\left(x \right)} + 1}{\operatorname{acot}{\left(x \right)}} + \frac{\tan{\left(x \right)}}{\left(x^{2} + 1\right) \operatorname{acot}^{2}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B216" t="str">
+      <x:c r="B234" t="str">
         <x:v>y=\tg(x) \cdot \frac{1}{\arcctg(x)}-\arctg(2 \cdot x) \cdot \tg(x)+C</x:v>
       </x:c>
-      <x:c r="C216" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D216" t="str">
+      <x:c r="C234" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D234" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 The given differential equation is  
@@ -14476,17 +15651,79 @@
 \boxed{\,y(x)=\frac{\tan x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="217">
-      <x:c r="A217" t="str">
+    <x:row r="235">
+      <x:c r="A235" t="str">
+        <x:v>y^{\prime}=- \frac{2 \operatorname{acos}{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{ctan}{\left(2 x \right)}}</x:v>
+      </x:c>
+      <x:c r="B235" t="str">
+        <x:v>y=\arccos(2 \cdot x) \cdot \frac{1}{\ctg(2 \cdot x)}+x \cdot \tg(x)+C</x:v>
+      </x:c>
+      <x:c r="C235" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D235" t="str">
+        <x:v>[REASONING]
+[REASONING]
+First rewrite the given differential equation using the standard meanings of the special functions.
+\[
+y'=- \frac{2\arccos (2x)\,\Bigl.\dfrac{d}{d\xi_1}\cot (\xi_1)\Bigr|_{\xi_1=2x}}{\cot ^2(2x)}-\frac{2}{\sqrt{1-4x^{2}}\;\cot (2x)} .
+\]
+The derivative of the cotangent is  
+\[
+\frac{d}{d\xi}\cot \xi = -\csc ^2\xi .
+\]
+Hence  
+\[
+\Bigl.\frac{d}{d\xi_1}\cot (\xi_1)\Bigr|_{\xi_1=2x}= -\csc ^2(2x).
+\]
+Insert this into the first term:
+\[
+-\frac{2\arccos (2x)(-\csc ^2(2x))}{\cot ^2(2x)}
+   =\frac{2\arccos (2x)\csc ^2(2x)}{\cot ^2(2x)} .
+\]
+Since \(\displaystyle\frac{\csc ^2\theta}{\cot ^2\theta}= \frac{1/\sin ^2\theta}{\cos ^2\theta/\sin ^2\theta}= \frac{1}{\cos ^2\theta}= \sec ^2\theta\),
+\[
+\frac{2\arccos (2x)\csc ^2(2x)}{\cot ^2(2x)} = 2\arccos (2x)\sec ^2(2x).
+\]
+The second term simplifies because \(1/\cot(2x)=\tan(2x)\):
+\[
+-\frac{2}{\sqrt{1-4x^{2}}\;\cot (2x)} = -\frac{2\tan(2x)}{\sqrt{1-4x^{2}}}.
+\]
+Recall that  
+\[
+\frac{d}{dx}\arccos (2x)= -\frac{2}{\sqrt{1-4x^{2}}},\qquad 
+\frac{d}{dx}\tan(2x)=2\sec ^2(2x).
+\]
+Therefore the right‑hand side can be written as  
+\[
+\begin{aligned}
+y' &amp;= 2\arccos (2x)\sec ^2(2x)-\frac{2\tan(2x)}{\sqrt{1-4x^{2}}}\\[2mm]
+   &amp;= \arccos (2x)\,\frac{d}{dx}\tan(2x)+\tan(2x)\,\frac{d}{dx}\arccos (2x).
+\end{aligned}
+\]
+The expression on the right is exactly the derivative of the product
+\(\arccos (2x)\tan(2x)\) (product rule). Hence
+\[
+y' = \frac{d}{dx}\bigl[\arccos (2x)\tan(2x)\bigr].
+\]
+Integrating both sides with respect to \(x\),
+\[
+y = \ar
+[FINAL ANSWER]
+\boxed{NOT_FOUND}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" t="str">
         <x:v>y^{\prime}=\frac{x^{2}}{\sqrt{1 - x^{2}} \operatorname{acos}^{2}{\left(x \right)}} + \frac{2 x}{\operatorname{acos}{\left(x \right)}} - \frac{1}{\sqrt{1 - x^{2}} \operatorname{acos}{\left(2 x \right)}} + \frac{2 \operatorname{acos}{\left(x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{acos}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B217" t="str">
+      <x:c r="B236" t="str">
         <x:v>y=x^{2} \cdot \frac{1}{\arccos(x)}+\arccos(x) \cdot \frac{1}{\arccos(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C217" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D217" t="str">
+      <x:c r="C236" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D236" t="str">
         <x:v>[REASONING]
 \[
 y'=\frac{x^{2}}{\sqrt{1-x^{2}}\;\arccos^{2}x}+\frac{2x}{\arccos x}
@@ -14547,17 +15784,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="218">
-      <x:c r="A218" t="str">
+    <x:row r="237">
+      <x:c r="A237" t="str">
         <x:v>y^{\prime}=- \frac{2 \operatorname{asin}{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - \frac{2}{\left(4 x^{2} + 1\right) \log{\left(x \right)}} + \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{ctan}{\left(2 x \right)}} + \frac{\operatorname{atan}{\left(2 x \right)}}{x \log{\left(x \right)}^{2}}</x:v>
       </x:c>
-      <x:c r="B218" t="str">
+      <x:c r="B237" t="str">
         <x:v>y=\arcsin(2 \cdot x) \cdot \frac{1}{\ctg(2 \cdot x)}-\arctg(2 \cdot x) \cdot \frac{1}{\ln(x)}+C</x:v>
       </x:c>
-      <x:c r="C218" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D218" t="str">
+      <x:c r="C237" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D237" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -14611,17 +15848,17 @@
 \boxed{\,2\arcsin (2x)\sec ^2(2x)\,}</x:v>
       </x:c>
     </x:row>
-    <x:row r="219">
-      <x:c r="A219" t="str">
+    <x:row r="238">
+      <x:c r="A238" t="str">
         <x:v>y^{\prime}=- \frac{x \frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{ctan}^{2}{\left(x \right)}} + \frac{1}{\operatorname{ctan}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B219" t="str">
+      <x:c r="B238" t="str">
         <x:v>y=x \cdot \frac{1}{\ctg(x)}+e^{x} \cdot \arcsin(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C219" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D219" t="str">
+      <x:c r="C238" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D238" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 The given differential equation is  
@@ -14677,17 +15914,17 @@
 \boxed{\,y = x \tan x + C\,}</x:v>
       </x:c>
     </x:row>
-    <x:row r="220">
-      <x:c r="A220" t="str">
+    <x:row r="239">
+      <x:c r="A239" t="str">
         <x:v>y^{\prime}=\frac{1}{\left(x^{2} + 1\right) \operatorname{acos}{\left(2 x \right)}} + \frac{2 \operatorname{atan}{\left(x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{acos}^{2}{\left(2 x \right)}} - \frac{1}{x \sqrt{1 - x^{2}}} - \frac{\operatorname{acos}{\left(x \right)}}{x^{2}}</x:v>
       </x:c>
-      <x:c r="B220" t="str">
+      <x:c r="B239" t="str">
         <x:v>y=\arccos(x) \cdot \frac{1}{x}+\arctg(x) \cdot \frac{1}{\arccos(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C220" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D220" t="str">
+      <x:c r="C239" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D239" t="str">
         <x:v>[REASONING]
 [REASONING]
 The right–hand side of the differential equation  
@@ -14748,17 +15985,17 @@
 \boxed{\,y(x)=\frac{\displaystyle\arctan x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="221">
-      <x:c r="A221" t="str">
+    <x:row r="240">
+      <x:c r="A240" t="str">
         <x:v>y^{\prime}=\frac{\frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{atan}{\left(x \right)}} - \frac{\operatorname{ctan}{\left(x \right)}}{\left(x^{2} + 1\right) \operatorname{atan}^{2}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B221" t="str">
+      <x:c r="B240" t="str">
         <x:v>y=\ctg(x) \cdot \frac{1}{\arctg(x)}-\cos(x) \cdot x^{3}+C</x:v>
       </x:c>
-      <x:c r="C221" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D221" t="str">
+      <x:c r="C240" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D240" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The differential equation is  
@@ -14818,17 +16055,17 @@
 \boxed{\,y(x)=\frac{\cot x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="222">
-      <x:c r="A222" t="str">
+    <x:row r="241">
+      <x:c r="A241" t="str">
         <x:v>y^{\prime}=2 x \cos{\left(2 x \right)} + \sin{\left(2 x \right)} - \frac{2 \sin{\left(2 x \right)}}{x^{2}} - \frac{2 \cos{\left(2 x \right)}}{x^{3}}</x:v>
       </x:c>
-      <x:c r="B222" t="str">
+      <x:c r="B241" t="str">
         <x:v>y=\sin(2 \cdot x) \cdot x+\cos(2 \cdot x) \cdot \frac{1}{x^{2}}+C</x:v>
       </x:c>
-      <x:c r="C222" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D222" t="str">
+      <x:c r="C241" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D241" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -14903,17 +16140,17 @@
 \boxed{\,y(x)=x\sin(2x)+\dfrac{\cos(2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="223">
-      <x:c r="A223" t="str">
+    <x:row r="242">
+      <x:c r="A242" t="str">
         <x:v>y^{\prime}=- \frac{x}{\sqrt{1 - x^{2}} \operatorname{acos}^{2}{\left(x \right)}} - \frac{1}{\operatorname{acos}{\left(x \right)}} - \frac{2 \log{\left(x \right)}}{4 x^{2} + 1} + \frac{\operatorname{acot}{\left(2 x \right)}}{x}</x:v>
       </x:c>
-      <x:c r="B223" t="str">
+      <x:c r="B242" t="str">
         <x:v>y=\arcctg(2 \cdot x) \cdot \ln(x)-x \cdot \frac{1}{\arccos(x)}+C</x:v>
       </x:c>
-      <x:c r="C223" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D223" t="str">
+      <x:c r="C242" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D242" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -14947,17 +16184,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="224">
-      <x:c r="A224" t="str">
+    <x:row r="243">
+      <x:c r="A243" t="str">
         <x:v>y^{\prime}=e^{x} \log{\left(e \right)} \operatorname{acot}{\left(x \right)} - \frac{e^{x}}{x^{2} + 1} + 2 \operatorname{ctan}{\left(2 x \right)} \cos{\left(2 x \right)} + 2 \sin{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}</x:v>
       </x:c>
-      <x:c r="B224" t="str">
+      <x:c r="B243" t="str">
         <x:v>y=\ctg(2 \cdot x) \cdot \sin(2 \cdot x)+e^{x} \cdot \arcctg(x)+C</x:v>
       </x:c>
-      <x:c r="C224" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D224" t="str">
+      <x:c r="C243" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D243" t="str">
         <x:v>[REASONING]
 [REASONING]
 The differential equation is  
@@ -15019,51 +16256,51 @@
 \boxed{\,y = e^{x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="225">
-      <x:c r="A225" t="str">
+    <x:row r="244">
+      <x:c r="A244" t="str">
         <x:v>y^{\prime}=- \frac{e^{2 x} \left(- 2 \tan^{2}{\left(2 x \right)} - 2\right)}{\tan^{2}{\left(2 x \right)}} - \frac{2 e^{2 x} \log{\left(e \right)}}{\tan{\left(2 x \right)}} + \frac{2 \tan^{2}{\left(2 x \right)} + 2}{\operatorname{asin}{\left(x \right)}} - \frac{\tan{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}}</x:v>
       </x:c>
-      <x:c r="B225" t="str">
+      <x:c r="B244" t="str">
         <x:v>y=\tg(2 \cdot x) \cdot \frac{1}{\arcsin(x)}-e^{2 \cdot x} \cdot \frac{1}{\tg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C225" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D225" t="str">
+      <x:c r="C244" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D244" t="str">
         <x:v>[REASONING]
 ERROR: Empty response
 [FINAL ANSWER]
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="226">
-      <x:c r="A226" t="str">
+    <x:row r="245">
+      <x:c r="A245" t="str">
         <x:v>y^{\prime}=- \frac{2 x^{3}}{4 x^{2} + 1} + 3 x^{2} \operatorname{acot}{\left(2 x \right)} + \frac{3 x^{2}}{\log{\left(2 x \right)}} - \frac{x^{2}}{\log{\left(2 x \right)}^{2}}</x:v>
       </x:c>
-      <x:c r="B226" t="str">
+      <x:c r="B245" t="str">
         <x:v>y=\arcctg(2 \cdot x) \cdot x^{3}+x^{3} \cdot \frac{1}{\ln(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C226" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D226" t="str">
+      <x:c r="C245" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D245" t="str">
         <x:v>[REASONING]
 ERROR: Empty response
 [FINAL ANSWER]
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="227">
-      <x:c r="A227" t="str">
+    <x:row r="246">
+      <x:c r="A246" t="str">
         <x:v>y^{\prime}=e^{x} \log{\left(e \right)} \operatorname{atan}{\left(x \right)} + \frac{e^{x}}{x^{2} + 1} + \frac{2 x^{3}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}} - \frac{3 x^{2}}{\operatorname{asin}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B227" t="str">
+      <x:c r="B246" t="str">
         <x:v>y=e^{x} \cdot \arctg(x)-x^{3} \cdot \frac{1}{\arcsin(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C227" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D227" t="str">
+      <x:c r="C246" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D246" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 The differential equation is  
@@ -15147,17 +16384,17 @@
 \boxed{\,y = e^{x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="228">
-      <x:c r="A228" t="str">
+    <x:row r="247">
+      <x:c r="A247" t="str">
         <x:v>y^{\prime}=e^{x} \log{\left(e \right)} \operatorname{atan}{\left(x \right)} + \frac{e^{x}}{x^{2} + 1} - \sin{\left(x \right)} \operatorname{asin}{\left(2 x \right)} + \frac{2 \cos{\left(x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B228" t="str">
+      <x:c r="B247" t="str">
         <x:v>y=e^{x} \cdot \arctg(x)+\cos(x) \cdot \arcsin(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C228" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D228" t="str">
+      <x:c r="C247" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D247" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 The differential equation is  
@@ -15209,17 +16446,17 @@
 \boxed{\,y = e^{x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="229">
-      <x:c r="A229" t="str">
+    <x:row r="248">
+      <x:c r="A248" t="str">
         <x:v>y^{\prime}=\frac{x}{\sqrt{1 - x^{2}}} + \operatorname{asin}{\left(x \right)} - 2 e^{- 2 x} \log{\left(e \right)} \sin{\left(x \right)} + e^{- 2 x} \cos{\left(x \right)}</x:v>
       </x:c>
-      <x:c r="B229" t="str">
+      <x:c r="B248" t="str">
         <x:v>y=\arcsin(x) \cdot x+\sin(x) \cdot \frac{1}{e^{2 \cdot x}}+C</x:v>
       </x:c>
-      <x:c r="C229" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D229" t="str">
+      <x:c r="C248" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D248" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 The differential equation is  
@@ -15276,17 +16513,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="230">
-      <x:c r="A230" t="str">
+    <x:row r="249">
+      <x:c r="A249" t="str">
         <x:v>y^{\prime}=- \frac{2 \cos{\left(2 x \right)} \operatorname{acot}{\left(x \right)}}{\sin^{2}{\left(2 x \right)}} - \frac{1}{\left(x^{2} + 1\right) \sin{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B230" t="str">
+      <x:c r="B249" t="str">
         <x:v>y=\arcctg(x) \cdot \frac{1}{\sin(2 \cdot x)}+\tg(2 \cdot x) \cdot x^{3}+C</x:v>
       </x:c>
-      <x:c r="C230" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D230" t="str">
+      <x:c r="C249" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D249" t="str">
         <x:v>[REASONING]
 **Solution**
 The differential equation is  
@@ -15347,17 +16584,17 @@
 \boxed{\,y(x)=\frac{\operatorname{acot}</x:v>
       </x:c>
     </x:row>
-    <x:row r="231">
-      <x:c r="A231" t="str">
+    <x:row r="250">
+      <x:c r="A250" t="str">
         <x:v>y^{\prime}=- \frac{x^{3}}{x^{2} + 1} + 3 x^{2} \operatorname{acot}{\left(x \right)} - \left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{ctan}{\left(x \right)} - \tan{\left(x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}</x:v>
       </x:c>
-      <x:c r="B231" t="str">
+      <x:c r="B250" t="str">
         <x:v>y=x^{3} \cdot \arcctg(x)-\tg(x) \cdot \ctg(x)+C</x:v>
       </x:c>
-      <x:c r="C231" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D231" t="str">
+      <x:c r="C250" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D250" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -15417,17 +16654,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="232">
-      <x:c r="A232" t="str">
+    <x:row r="251">
+      <x:c r="A251" t="str">
         <x:v>y^{\prime}=e^{x} \log{\left(e \right)} \operatorname{acos}{\left(x \right)} - \frac{e^{x}}{\sqrt{1 - x^{2}}} - \frac{2 \operatorname{acos}{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{ctan}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B232" t="str">
+      <x:c r="B251" t="str">
         <x:v>y=e^{x} \cdot \arccos(x)+\arccos(2 \cdot x) \cdot \frac{1}{\ctg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C232" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D232" t="str">
+      <x:c r="C251" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D251" t="str">
         <x:v>[REASONING]
 **Step 1 – Simplify the right‑hand side**
 \[
@@ -15494,34 +16731,106 @@
 \boxed{\,y(x)=e^{x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="233">
-      <x:c r="A233" t="str">
+    <x:row r="252">
+      <x:c r="A252" t="str">
+        <x:v>y^{\prime}=- e^{- x} \operatorname{ctan}{\left(x \right)} \log{\left(e \right)} + e^{- x} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}</x:v>
+      </x:c>
+      <x:c r="B252" t="str">
+        <x:v>y=\ctg(x) \cdot \frac{1}{e^{x}}-x^{2} \cdot \ctg(2 \cdot x)+C</x:v>
+      </x:c>
+      <x:c r="C252" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D252" t="str">
+        <x:v>[REASONING]
+[REASONING]
+The given differential equation is  
+\[
+y'=- e^{- x}\,\operatorname{ctan}(x)\,\log(e)+e^{- x}\,\frac{d}{dx}\operatorname{ctan}(x).
+\]
+---
+### 1.  Simplify the right‑hand side  
+* \(\log(e)=1\) because the natural logarithm of \(e\) equals 1.  
+* \(\operatorname{ctan}(x)\) denotes the cotangent function, i.e. \(\cot x\).  
+Hence  
+\[
+y'=- e^{-x}\cot x+e^{-x}\frac{d}{dx}\cot x .
+\]
+The derivative of \(\cot x\) is  
+\[
+\frac{d}{dx}\cot x = -\csc^{2}x .
+\]
+Substituting this derivative gives  
+\[
+y'=- e^{-x}\cot x+e^{-x}\bigl(-\csc^{2}x\bigr)
+   =-e^{-x}\cot x-e^{-x}\csc^{2}x
+   =-e^{-x}\bigl(\cot x+\csc^{2}x\bigr).
+\]
+---
+### 2.  Recognise the expression as a total derivative  
+Consider the function  
+\[
+F(x)=e^{-x}\cot x .
+\]
+Differentiate \(F(x)\) using the product rule:
+\[
+\begin{aligned}
+F'(x)&amp;=\frac{d}{dx}\bigl(e^{-x}\bigr)\cot x+e^{-x}\frac{d}{dx}\cot x\\
+     &amp;=(-e^{-x})\cot x+e^{-x}\bigl(-\csc^{2}x\bigr)\\
+     &amp;=-e^{-x}\cot x-e^{-x}\csc^{2}x\\
+     &amp;=-e^{-x}\bigl(\cot x+\csc^{2}x\bigr).
+\end{aligned}
+\]
+Thus  
+\[
+y' = F'(x)=\frac{d}{dx}\bigl(e^{-x}\cot x\bigr).
+\]
+---
+### 3.  Integrate  
+Since the derivative of \(e^{-x}\cot x\) equals the right‑hand side, integrate both sides:
+\[
+\int y'\,dx = \int \frac{d}{dx}\bigl(e^{-x}\cot x\bigr)\,dx
+\quad\Longrightarrow\quad
+y = e^{-x}\cot x + C,
+\]
+where \(C\) is the constant of integration.
+---
+### 4.  Final solution  
+\[
+\boxed{\,y = e^{-x}\cot x + C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y = e^{-x}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253" t="str">
         <x:v>y^{\prime}=\frac{\cos{\left(x \right)}}{\operatorname{ctan}{\left(2 x \right)}} - \frac{2 \sin{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B233" t="str">
+      <x:c r="B253" t="str">
         <x:v>y=\sin(x) \cdot \frac{1}{\ctg(2 \cdot x)}+x^{2} \cdot \cos(x)+C</x:v>
       </x:c>
-      <x:c r="C233" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D233" t="str">
+      <x:c r="C253" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D253" t="str">
         <x:v>[REASONING]
 ERROR: Empty response
 [FINAL ANSWER]
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="234">
-      <x:c r="A234" t="str">
+    <x:row r="254">
+      <x:c r="A254" t="str">
         <x:v>y^{\prime}=\left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{acos}{\left(2 x \right)} + \frac{2}{\left(4 x^{2} + 1\right) \operatorname{asin}{\left(x \right)}} - \frac{\operatorname{atan}{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}} - \frac{2 \tan{\left(x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B234" t="str">
+      <x:c r="B254" t="str">
         <x:v>y=\arccos(2 \cdot x) \cdot \tg(x)+\arctg(2 \cdot x) \cdot \frac{1}{\arcsin(x)}+C</x:v>
       </x:c>
-      <x:c r="C234" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D234" t="str">
+      <x:c r="C254" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D254" t="str">
         <x:v>[REASONING]
 The right–hand side can be recognised as a total derivative.
 ---
@@ -15592,17 +16901,17 @@
 \boxed{\,y = \tan x\,\arccos (2x) + \dfrac{\arctan (2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="235">
-      <x:c r="A235" t="str">
+    <x:row r="255">
+      <x:c r="A255" t="str">
         <x:v>y^{\prime}=\frac{2 x^{3}}{4 x^{2} + 1} - 3 x^{2} \operatorname{acot}{\left(2 x \right)} - 2 \sin{\left(2 x \right)} \operatorname{acot}{\left(2 x \right)} - \frac{2 \cos{\left(2 x \right)}}{4 x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B235" t="str">
+      <x:c r="B255" t="str">
         <x:v>y=\cos(2 \cdot x) \cdot \arcctg(2 \cdot x)-\arcctg(2 \cdot x) \cdot x^{3}+C</x:v>
       </x:c>
-      <x:c r="C235" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D235" t="str">
+      <x:c r="C255" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D255" t="str">
         <x:v>[REASONING]
 **Step 1 –  Write the right‑hand side in a convenient form**
 \[
@@ -15656,17 +16965,17 @@
 \boxed{\,y(x)=\bigl(\cos(2x)-x^{3}</x:v>
       </x:c>
     </x:row>
-    <x:row r="236">
-      <x:c r="A236" t="str">
+    <x:row r="256">
+      <x:c r="A256" t="str">
         <x:v>y^{\prime}=\frac{2 \operatorname{acos}{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{acot}^{2}{\left(2 x \right)}} - \frac{2}{\left(4 x^{2} + 1\right) \log{\left(2 x \right)}} - \frac{1}{\sqrt{1 - x^{2}} \operatorname{acot}{\left(2 x \right)}} - \frac{\operatorname{acot}{\left(2 x \right)}}{x \log{\left(2 x \right)}^{2}}</x:v>
       </x:c>
-      <x:c r="B236" t="str">
+      <x:c r="B256" t="str">
         <x:v>y=\arccos(x) \cdot \frac{1}{\arcctg(2 \cdot x)}+\arcctg(2 \cdot x) \cdot \frac{1}{\ln(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C236" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D236" t="str">
+      <x:c r="C256" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D256" t="str">
         <x:v>[REASONING]
 **Step 1 – Identify the structure of the right‑hand side**
 \[
@@ -15675,17 +16984,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="237">
-      <x:c r="A237" t="str">
+    <x:row r="257">
+      <x:c r="A257" t="str">
         <x:v>y^{\prime}=- \frac{x^{2}}{\left(x^{2} + 1\right) \operatorname{atan}^{2}{\left(x \right)}} + \frac{2 x}{\operatorname{atan}{\left(x \right)}} + \frac{1}{x^{2}}</x:v>
       </x:c>
-      <x:c r="B237" t="str">
+      <x:c r="B257" t="str">
         <x:v>y=x^{2} \cdot \frac{1}{\arctg(x)}-x^{2} \cdot \frac{1}{x^{3}}+C</x:v>
       </x:c>
-      <x:c r="C237" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D237" t="str">
+      <x:c r="C257" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D257" t="str">
         <x:v>[REASONING]
 **[REASONING]**
 The differential equation is  
@@ -15743,17 +17052,17 @@
 \boxed{\,y(x)=\frac{x^{2}</x:v>
       </x:c>
     </x:row>
-    <x:row r="238">
-      <x:c r="A238" t="str">
+    <x:row r="258">
+      <x:c r="A258" t="str">
         <x:v>y^{\prime}=e^{x} \log{\left(e \right)} \operatorname{acot}{\left(2 x \right)} - \frac{2 e^{x}}{4 x^{2} + 1} - \frac{\log{\left(x \right)}}{x} - \frac{\log{\left(2 x \right)}}{x}</x:v>
       </x:c>
-      <x:c r="B238" t="str">
+      <x:c r="B258" t="str">
         <x:v>y=e^{x} \cdot \arcctg(2 \cdot x)-\ln(2 \cdot x) \cdot \ln(x)+C</x:v>
       </x:c>
-      <x:c r="C238" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D238" t="str">
+      <x:c r="C258" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D258" t="str">
         <x:v>[REASONING]
 **Step‑by‑step integration**
 The differential equation is  
@@ -15795,17 +17104,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="239">
-      <x:c r="A239" t="str">
+    <x:row r="259">
+      <x:c r="A259" t="str">
         <x:v>y^{\prime}=- \frac{\tan^{2}{\left(x \right)} + 1}{\operatorname{ctan}{\left(2 x \right)}} - \sin{\left(x \right)} \operatorname{acos}{\left(2 x \right)} + \frac{2 \tan{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - \frac{2 \cos{\left(x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B239" t="str">
+      <x:c r="B259" t="str">
         <x:v>y=\arccos(2 \cdot x) \cdot \cos(x)-\tg(x) \cdot \frac{1}{\ctg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C239" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D239" t="str">
+      <x:c r="C259" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D259" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -15855,17 +17164,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="240">
-      <x:c r="A240" t="str">
+    <x:row r="260">
+      <x:c r="A260" t="str">
         <x:v>y^{\prime}=- \frac{\cos{\left(x \right)}}{\operatorname{ctan}{\left(2 x \right)}} + \frac{2 \sin{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - \frac{2 \operatorname{acos}{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{asin}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B240" t="str">
+      <x:c r="B260" t="str">
         <x:v>y=\arccos(2 \cdot x) \cdot \frac{1}{\arcsin(2 \cdot x)}-\sin(x) \cdot \frac{1}{\ctg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C240" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D240" t="str">
+      <x:c r="C260" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D260" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The given differential equation is  
@@ -15901,17 +17210,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="241">
-      <x:c r="A241" t="str">
+    <x:row r="261">
+      <x:c r="A261" t="str">
         <x:v>y^{\prime}=\left(\tan^{2}{\left(x \right)} + 1\right) \operatorname{acos}{\left(x \right)} - \operatorname{acot}{\left(x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)} + \frac{\operatorname{ctan}{\left(x \right)}}{x^{2} + 1} - \frac{\tan{\left(x \right)}}{\sqrt{1 - x^{2}}}</x:v>
       </x:c>
-      <x:c r="B241" t="str">
+      <x:c r="B261" t="str">
         <x:v>y=\tg(x) \cdot \arccos(x)-\ctg(x) \cdot \arcctg(x)+C</x:v>
       </x:c>
-      <x:c r="C241" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D241" t="str">
+      <x:c r="C261" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D261" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The given differential equation is  
@@ -15976,17 +17285,17 @@
 \boxed{\,y = \tan(x)\,\arccos(x)\;-\;\cot(x)\,\operatorname{arccot}</x:v>
       </x:c>
     </x:row>
-    <x:row r="242">
-      <x:c r="A242" t="str">
+    <x:row r="262">
+      <x:c r="A262" t="str">
         <x:v>y^{\prime}=- \frac{x^{3}}{x^{2} + 1} + 3 x^{2} \operatorname{acot}{\left(x \right)} + \frac{\sin{\left(x \right)}}{\operatorname{atan}{\left(2 x \right)}} + \frac{2 \cos{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{atan}^{2}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B242" t="str">
+      <x:c r="B262" t="str">
         <x:v>y=x^{3} \cdot \arcctg(x)-\cos(x) \cdot \frac{1}{\arctg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C242" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D242" t="str">
+      <x:c r="C262" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D262" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The differential equation is  
@@ -16058,17 +17367,17 @@
 \boxed{\,y(x)=x^{3}</x:v>
       </x:c>
     </x:row>
-    <x:row r="243">
-      <x:c r="A243" t="str">
+    <x:row r="263">
+      <x:c r="A263" t="str">
         <x:v>y^{\prime}=2 x \log{\left(2 x \right)} + x - 2 \operatorname{atan}{\left(x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} - \frac{\operatorname{ctan}{\left(2 x \right)}}{x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B243" t="str">
+      <x:c r="B263" t="str">
         <x:v>y=x^{2} \cdot \ln(2 \cdot x)-\ctg(2 \cdot x) \cdot \arctg(x)+C</x:v>
       </x:c>
-      <x:c r="C243" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D243" t="str">
+      <x:c r="C263" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D263" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -16130,17 +17439,82 @@
 \boxed{\,y' = 2x\log (2x)+x+2\arctan (x)\csc ^2(2x)-\frac{\cot (2x)}</x:v>
       </x:c>
     </x:row>
-    <x:row r="244">
-      <x:c r="A244" t="str">
+    <x:row r="264">
+      <x:c r="A264" t="str">
+        <x:v>y^{\prime}=\frac{2 \log{\left(x \right)} \sin{\left(2 x \right)}}{\cos^{2}{\left(2 x \right)}} + \frac{1}{x \cos{\left(2 x \right)}}</x:v>
+      </x:c>
+      <x:c r="B264" t="str">
+        <x:v>y=\ln(x) \cdot \frac{1}{\cos(2 \cdot x)}-\tg(2 \cdot x) \cdot \ln(x)+C</x:v>
+      </x:c>
+      <x:c r="C264" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D264" t="str">
+        <x:v>[REASONING]
+**Step‑by‑step solution**
+\[
+y'=\frac{2\log x\,\sin (2x)}{\cos ^2(2x)}+\frac{1}{x\cos (2x)}
+\qquad (x&gt;0,\; \cos 2x\neq 0)
+\]
+---
+### 1.  Look for a function whose derivative gives the right‑hand side  
+Consider  
+\[
+u(x)=\frac{\log x}{\cos (2x)}=\log x\;\sec (2x).
+\]
+Using the product rule  
+\[
+u'(x)=\bigl(\log x\bigr)'\,\sec (2x)+\log x\;\bigl(\sec (2x)\bigr)' .
+\]
+Compute each derivative:
+* \((\log x)'=\dfrac{1}{x}\).
+* \(\displaystyle \bigl(\sec (2x)\bigr)'=
+\sec (2x)\tan (2x)\cdot (2)=2\sec (2x)\tan (2x).\)
+Recall \(\sec (2x)=\dfrac{1}{\cos (2x)}\) and \(\tan (2x)=\dfrac{\sin (2x)}{\cos (2x)}\); therefore  
+\[
+2\sec (2x)\tan (2x)=2\frac{1}{\cos (2x)}\frac{\sin (2x)}{\cos (2x)}
+= \frac{2\sin (2x)}{\cos ^2(2x)} .
+\]
+Now substitute back:
+\[
+\begin{aligned}
+u'(x) &amp;=
+\frac{1}{x}\,\frac{1}{\cos (2x)}
++\log x\;\frac{2\sin (2x)}{\cos ^2(2x)}  \\
+&amp;= \frac{1}{x\cos (2x)}+\frac{2\log x\,\sin (2x)}{\cos ^2(2x)} .
+\end{aligned}
+\]
+The expression obtained for \(u'(x)\) is exactly the right‑hand side of the given differential equation.
+Hence  
+\[
+y' = u'(x)=\frac{d}{dx}\!\left(\frac{\log x}{\cos (2x)}\right).
+\]
+---
+### 2.  Integrate  
+\[
+y = \int y'\,dx = \int u'(x)\,dx = u(x)+C
+      = \frac{\log x}{\cos (2x)}+C .
+\]
+---
+\[
+\boxed{\,y(x)=\dfrac{\ln x}{\cos (2x)}+C\,}
+\]
+where \(C\) is an arbitrary constant, and the solution is valid for \(x&gt;0\) with \(\cos(2x)\neq 0\).
+[FINAL ANSWER]
+\boxed{\,y(x)=\dfrac{\ln x}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265">
+      <x:c r="A265" t="str">
         <x:v>y^{\prime}=2 e^{2 x} x \log{\left(e \right)} + e^{2 x} - \frac{2 \operatorname{acos}{\left(x \right)}}{\left(4 x^{2} + 1\right) \operatorname{atan}^{2}{\left(2 x \right)}} - \frac{1}{\sqrt{1 - x^{2}} \operatorname{atan}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B244" t="str">
+      <x:c r="B265" t="str">
         <x:v>y=x \cdot e^{2 \cdot x}+\arccos(x) \cdot \frac{1}{\arctg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C244" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D244" t="str">
+      <x:c r="C265" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D265" t="str">
         <x:v>[REASONING]
 **Step‑by‑step solution**
 \[
@@ -16217,17 +17591,17 @@
 \boxed{\,y(x)=xe^{2x}</x:v>
       </x:c>
     </x:row>
-    <x:row r="245">
-      <x:c r="A245" t="str">
+    <x:row r="266">
+      <x:c r="A266" t="str">
         <x:v>y^{\prime}=- \frac{2 x}{4 x^{2} + 1} + \operatorname{acot}{\left(2 x \right)} + \frac{2 \operatorname{asin}{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{ctan}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B245" t="str">
+      <x:c r="B266" t="str">
         <x:v>y=x \cdot \arcctg(2 \cdot x)-\arcsin(2 \cdot x) \cdot \frac{1}{\ctg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C245" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D245" t="str">
+      <x:c r="C266" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D266" t="str">
         <x:v>[REASONING]
 \[
 y'=- \frac{2 x}{4 x^{2}+1}+ \operatorname{acot}(2x)
@@ -16257,17 +17631,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="246">
-      <x:c r="A246" t="str">
+    <x:row r="267">
+      <x:c r="A267" t="str">
         <x:v>y^{\prime}=- 2 \sin{\left(2 x \right)} \operatorname{acot}{\left(x \right)} - \frac{\cos{\left(2 x \right)}}{x^{2} + 1} + \frac{\operatorname{asin}{\left(2 x \right)}}{x^{2} + 1} + \frac{2 \operatorname{atan}{\left(x \right)}}{\sqrt{1 - 4 x^{2}}}</x:v>
       </x:c>
-      <x:c r="B246" t="str">
+      <x:c r="B267" t="str">
         <x:v>y=\arcsin(2 \cdot x) \cdot \arctg(x)+\arcctg(x) \cdot \cos(2 \cdot x)+C</x:v>
       </x:c>
-      <x:c r="C246" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D246" t="str">
+      <x:c r="C267" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D267" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The differential equation is  
@@ -16333,17 +17707,17 @@
 \boxed{\,y(x)=\cos (2x)\,\operatorname{acot}</x:v>
       </x:c>
     </x:row>
-    <x:row r="247">
-      <x:c r="A247" t="str">
+    <x:row r="268">
+      <x:c r="A268" t="str">
         <x:v>y^{\prime}=\frac{2 x^{2}}{\left(4 x^{2} + 1\right) \operatorname{acot}^{2}{\left(2 x \right)}} + \frac{2 x}{\operatorname{acot}{\left(2 x \right)}} - 2 \sin{\left(2 x \right)} \operatorname{atan}{\left(2 x \right)} + \frac{2 \cos{\left(2 x \right)}}{4 x^{2} + 1}</x:v>
       </x:c>
-      <x:c r="B247" t="str">
+      <x:c r="B268" t="str">
         <x:v>y=\cos(2 \cdot x) \cdot \arctg(2 \cdot x)+x^{2} \cdot \frac{1}{\arcctg(2 \cdot x)}+C</x:v>
       </x:c>
-      <x:c r="C247" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D247" t="str">
+      <x:c r="C268" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D268" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -16415,17 +17789,99 @@
 \boxed{\,y(x)=\frac{x^{2}</x:v>
       </x:c>
     </x:row>
-    <x:row r="248">
-      <x:c r="A248" t="str">
+    <x:row r="269">
+      <x:c r="A269" t="str">
+        <x:v>y^{\prime}=\frac{2 \log{\left(x \right)} \sin{\left(2 x \right)}}{\cos^{2}{\left(2 x \right)}} + \frac{1}{x \cos{\left(2 x \right)}}</x:v>
+      </x:c>
+      <x:c r="B269" t="str">
+        <x:v>y=\ln(x) \cdot \frac{1}{\cos(2 \cdot x)}-\ctg(x) \cdot \sin(x)+C</x:v>
+      </x:c>
+      <x:c r="C269" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D269" t="str">
+        <x:v>[REASONING]
+[REASONING]
+The differential equation is  
+\[
+y'=\frac{2\log x\,\sin (2x)}{\cos ^2(2x)}+\frac{1}{x\cos (2x)} .
+\]
+We need an antiderivative of the right–hand side.
+---
+### 1.  Rewrite the first term  
+\[
+\frac{\sin (2x)}{\cos ^2(2x)}=\frac{\sin (2x)}{\cos (2x)}\cdot\frac{1}{\cos (2x)}
+      =\tan (2x)\sec (2x).
+\]
+Recall  
+\[
+\frac{d}{dx}\sec (2x)=2\sec (2x)\tan (2x).
+\]
+Hence  
+\[
+\tan (2x)\sec (2x)=\frac12\frac{d}{dx}\sec (2x).
+\]
+Therefore  
+\[
+\frac{2\log x\,\sin (2x)}{\cos ^2(2x)}
+      =2\log x\;\tan (2x)\sec (2x)
+      =\log x\;\frac{d}{dx}\sec (2x).
+\]
+---
+### 2.  Integrate the first term by parts  
+\[
+\int \log x\;\frac{d}{dx}\sec (2x)\,dx
+   =\log x\;\sec (2x)-\int \sec (2x)\,\frac{dx}{x}.
+\]
+---
+### 3.  Add the second term of the original RHS  
+The second term of the differential equation is  
+\[
+\frac{1}{x\cos (2x)}=\frac{\sec (2x)}{x}.
+\]
+Thus the total integral \(I\) becomes  
+\[
+\begin{aligned}
+I &amp;=\Bigl[\log x\;\sec (2x)-\int \frac{\sec (2x)}{x}\,dx\Bigr]
+     +\int \frac{\sec (2x)}{x}\,dx \\[2mm]
+  &amp;=\log x\;\sec (2x).
+\end{aligned}
+\]
+The two integrals cancel exactly.
+---
+### 4.  Write the solution  
+Since \(y' =\) RHS, integrating gives  
+\[
+y = \log x\;\sec (2x)+C,
+\]
+where \(C\) is an arbitrary constant.
+A quick verification using the product rule:
+\[
+\frac{d}{dx}\bigl[\log x\;\sec (2x)\bigr]
+   =\frac{1}{x}\sec (2x)+\log x\cdot 2\sec (2x)\tan (2x)
+   =\frac{1}{x\cos (2x)}+\frac{2\log x\,\sin (2x)}{\cos ^2(2x)},
+\]
+which reproduces the given right‑hand side.
+---
+[FINAL ANSWER]
+\[
+\boxed{\,y(x)=\log x\;\sec (2x)+C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y(x)=\log x\;\sec (2x)+C\,}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270">
+      <x:c r="A270" t="str">
         <x:v>y^{\prime}=2 x^{2} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }} + 2 x \operatorname{ctan}{\left(2 x \right)} - \left(\tan^{2}{\left(x \right)} + 1\right) \sin{\left(2 x \right)} - 2 \cos{\left(2 x \right)} \tan{\left(x \right)}</x:v>
       </x:c>
-      <x:c r="B248" t="str">
+      <x:c r="B270" t="str">
         <x:v>y=x^{2} \cdot \ctg(2 \cdot x)-\sin(2 \cdot x) \cdot \tg(x)+C</x:v>
       </x:c>
-      <x:c r="C248" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D248" t="str">
+      <x:c r="C270" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D270" t="str">
         <x:v>[REASONING]
 **Reasoning**
 The differential equation is  
@@ -16456,17 +17912,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="249">
-      <x:c r="A249" t="str">
+    <x:row r="271">
+      <x:c r="A271" t="str">
         <x:v>y^{\prime}=- \frac{2 \operatorname{atan}{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} + \frac{2}{\left(4 x^{2} + 1\right) \operatorname{ctan}{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B249" t="str">
+      <x:c r="B271" t="str">
         <x:v>y=\arctg(2 \cdot x) \cdot \frac{1}{\ctg(2 \cdot x)}+\arctg(x) \cdot x+C</x:v>
       </x:c>
-      <x:c r="C249" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D249" t="str">
+      <x:c r="C271" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D271" t="str">
         <x:v>[REASONING]
 [REASONING]
 The given differential equation is  
@@ -16543,17 +17999,17 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="250">
-      <x:c r="A250" t="str">
+    <x:row r="272">
+      <x:c r="A272" t="str">
         <x:v>y^{\prime}=- \frac{\operatorname{ctan}{\left(2 x \right)} \cos{\left(x \right)}}{\sin^{2}{\left(x \right)}} - \frac{2 \cos{\left(2 x \right)} \operatorname{asin}{\left(2 x \right)}}{\sin^{2}{\left(2 x \right)}} + \frac{2 \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\sin{\left(x \right)}} + \frac{2}{\sqrt{1 - 4 x^{2}} \sin{\left(2 x \right)}}</x:v>
       </x:c>
-      <x:c r="B250" t="str">
+      <x:c r="B272" t="str">
         <x:v>y=\arcsin(2 \cdot x) \cdot \frac{1}{\sin(2 \cdot x)}+\ctg(2 \cdot x) \cdot \frac{1}{\sin(x)}+C</x:v>
       </x:c>
-      <x:c r="C250" t="str">
-        <x:v>separable variables</x:v>
-      </x:c>
-      <x:c r="D250" t="str">
+      <x:c r="C272" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
+      <x:c r="D272" t="str">
         <x:v>[REASONING]
 **Step 1 – Rewrite the right‑hand side**
 \[
@@ -16571,138 +18027,6 @@
 \boxed{NOT_FOUND}</x:v>
       </x:c>
     </x:row>
-    <x:row r="251">
-      <x:c r="A251"/>
-      <x:c r="B251"/>
-      <x:c r="C251"/>
-      <x:c r="D251"/>
-    </x:row>
-    <x:row r="252">
-      <x:c r="A252"/>
-      <x:c r="B252"/>
-      <x:c r="C252"/>
-      <x:c r="D252"/>
-    </x:row>
-    <x:row r="253">
-      <x:c r="A253"/>
-      <x:c r="B253"/>
-      <x:c r="C253"/>
-      <x:c r="D253"/>
-    </x:row>
-    <x:row r="254">
-      <x:c r="A254"/>
-      <x:c r="B254"/>
-      <x:c r="C254"/>
-      <x:c r="D254"/>
-    </x:row>
-    <x:row r="255">
-      <x:c r="A255"/>
-      <x:c r="B255"/>
-      <x:c r="C255"/>
-      <x:c r="D255"/>
-    </x:row>
-    <x:row r="256">
-      <x:c r="A256"/>
-      <x:c r="B256"/>
-      <x:c r="C256"/>
-      <x:c r="D256"/>
-    </x:row>
-    <x:row r="257">
-      <x:c r="A257"/>
-      <x:c r="B257"/>
-      <x:c r="C257"/>
-      <x:c r="D257"/>
-    </x:row>
-    <x:row r="258">
-      <x:c r="A258"/>
-      <x:c r="B258"/>
-      <x:c r="C258"/>
-      <x:c r="D258"/>
-    </x:row>
-    <x:row r="259">
-      <x:c r="A259"/>
-      <x:c r="B259"/>
-      <x:c r="C259"/>
-      <x:c r="D259"/>
-    </x:row>
-    <x:row r="260">
-      <x:c r="A260"/>
-      <x:c r="B260"/>
-      <x:c r="C260"/>
-      <x:c r="D260"/>
-    </x:row>
-    <x:row r="261">
-      <x:c r="A261"/>
-      <x:c r="B261"/>
-      <x:c r="C261"/>
-      <x:c r="D261"/>
-    </x:row>
-    <x:row r="262">
-      <x:c r="A262"/>
-      <x:c r="B262"/>
-      <x:c r="C262"/>
-      <x:c r="D262"/>
-    </x:row>
-    <x:row r="263">
-      <x:c r="A263"/>
-      <x:c r="B263"/>
-      <x:c r="C263"/>
-      <x:c r="D263"/>
-    </x:row>
-    <x:row r="264">
-      <x:c r="A264"/>
-      <x:c r="B264"/>
-      <x:c r="C264"/>
-      <x:c r="D264"/>
-    </x:row>
-    <x:row r="265">
-      <x:c r="A265"/>
-      <x:c r="B265"/>
-      <x:c r="C265"/>
-      <x:c r="D265"/>
-    </x:row>
-    <x:row r="266">
-      <x:c r="A266"/>
-      <x:c r="B266"/>
-      <x:c r="C266"/>
-      <x:c r="D266"/>
-    </x:row>
-    <x:row r="267">
-      <x:c r="A267"/>
-      <x:c r="B267"/>
-      <x:c r="C267"/>
-      <x:c r="D267"/>
-    </x:row>
-    <x:row r="268">
-      <x:c r="A268"/>
-      <x:c r="B268"/>
-      <x:c r="C268"/>
-      <x:c r="D268"/>
-    </x:row>
-    <x:row r="269">
-      <x:c r="A269"/>
-      <x:c r="B269"/>
-      <x:c r="C269"/>
-      <x:c r="D269"/>
-    </x:row>
-    <x:row r="270">
-      <x:c r="A270"/>
-      <x:c r="B270"/>
-      <x:c r="C270"/>
-      <x:c r="D270"/>
-    </x:row>
-    <x:row r="271">
-      <x:c r="A271"/>
-      <x:c r="B271"/>
-      <x:c r="C271"/>
-      <x:c r="D271"/>
-    </x:row>
-    <x:row r="272">
-      <x:c r="A272"/>
-      <x:c r="B272"/>
-      <x:c r="C272"/>
-      <x:c r="D272"/>
-    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
